--- a/kivampro_iddsi/iddsi1/iddsi1_iddsi1-60ml-2/iddsi1_iddsi1-60ml-2_weights.xlsx
+++ b/kivampro_iddsi/iddsi1/iddsi1_iddsi1-60ml-2/iddsi1_iddsi1-60ml-2_weights.xlsx
@@ -282,7 +282,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Sheet1'!I1</f>
+              <f>'Sheet1'!G1</f>
             </strRef>
           </tx>
           <spPr>
@@ -308,12 +308,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'Sheet1'!$K$2:$K$116</f>
+              <f>'Sheet1'!$I$2:$I$116</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'Sheet1'!$I$2:$I$116</f>
+              <f>'Sheet1'!$G$2:$G$116</f>
             </numRef>
           </yVal>
         </ser>
@@ -908,34 +908,26 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>trend_ref_g</t>
+          <t>excluded</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>reset_drop_g</t>
+          <t>weight_kept_g</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>excluded</t>
+          <t>is_started</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>weight_kept_g</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_started</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
           <t>time_corrected_s</t>
         </is>
       </c>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
       <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Parametreler</t>
@@ -958,31 +950,23 @@
         <v>8.880000000000001</v>
       </c>
       <c r="E2">
-        <f>MEDIAN(D2:D22)</f>
+        <f>IFERROR(MEDIAN(D2:D22),D2)</f>
         <v/>
       </c>
       <c r="F2">
-        <f>E2</f>
+        <f>IF(OR(NOT(ISNUMBER(D2)),ABS(D2-E2)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G2">
-        <f>F2-E2</f>
+        <f>IF(F2=1,NA(),D2)</f>
         <v/>
       </c>
       <c r="H2">
-        <f>IF(OR(NOT(ISNUMBER(D2)),ABS(D2-E2)&gt;$O$3,AND($O$11=1,B2&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D2),D2&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I2">
-        <f>IF(H2=1,NA(),D2)</f>
-        <v/>
-      </c>
-      <c r="J2">
-        <f>IF(AND(ISNUMBER(D2),D2&gt;=$O$4,OR($O$11=0,B2&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K2">
-        <f>B2-$O$14</f>
+        <f>B2-$O$8</f>
         <v/>
       </c>
       <c r="N2" t="inlineStr">
@@ -1010,31 +994,23 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <f>MEDIAN(D2:D23)</f>
+        <f>IFERROR(MEDIAN(D2:D23),D3)</f>
         <v/>
       </c>
       <c r="F3">
-        <f>E3</f>
+        <f>IF(OR(NOT(ISNUMBER(D3)),ABS(D3-E3)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G3">
-        <f>F3-E3</f>
+        <f>IF(F3=1,NA(),D3)</f>
         <v/>
       </c>
       <c r="H3">
-        <f>IF(OR(NOT(ISNUMBER(D3)),ABS(D3-E3)&gt;$O$3,AND($O$11=1,B3&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D3),D3&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I3">
-        <f>IF(H3=1,NA(),D3)</f>
-        <v/>
-      </c>
-      <c r="J3">
-        <f>IF(AND(ISNUMBER(D3),D3&gt;=$O$4,OR($O$11=0,B3&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K3">
-        <f>B3-$O$14</f>
+        <f>B3-$O$8</f>
         <v/>
       </c>
       <c r="N3" t="inlineStr">
@@ -1062,31 +1038,23 @@
         <v>8.880000000000001</v>
       </c>
       <c r="E4">
-        <f>MEDIAN(D2:D24)</f>
+        <f>IFERROR(MEDIAN(D2:D24),D4)</f>
         <v/>
       </c>
       <c r="F4">
-        <f>E4</f>
+        <f>IF(OR(NOT(ISNUMBER(D4)),ABS(D4-E4)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G4">
-        <f>F4-E4</f>
+        <f>IF(F4=1,NA(),D4)</f>
         <v/>
       </c>
       <c r="H4">
-        <f>IF(OR(NOT(ISNUMBER(D4)),ABS(D4-E4)&gt;$O$3,AND($O$11=1,B4&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D4),D4&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I4">
-        <f>IF(H4=1,NA(),D4)</f>
-        <v/>
-      </c>
-      <c r="J4">
-        <f>IF(AND(ISNUMBER(D4),D4&gt;=$O$4,OR($O$11=0,B4&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K4">
-        <f>B4-$O$14</f>
+        <f>B4-$O$8</f>
         <v/>
       </c>
       <c r="N4" t="inlineStr">
@@ -1114,31 +1082,23 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <f>MEDIAN(D2:D25)</f>
+        <f>IFERROR(MEDIAN(D2:D25),D5)</f>
         <v/>
       </c>
       <c r="F5">
-        <f>E5</f>
+        <f>IF(OR(NOT(ISNUMBER(D5)),ABS(D5-E5)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G5">
-        <f>F5-E5</f>
+        <f>IF(F5=1,NA(),D5)</f>
         <v/>
       </c>
       <c r="H5">
-        <f>IF(OR(NOT(ISNUMBER(D5)),ABS(D5-E5)&gt;$O$3,AND($O$11=1,B5&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D5),D5&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I5">
-        <f>IF(H5=1,NA(),D5)</f>
-        <v/>
-      </c>
-      <c r="J5">
-        <f>IF(AND(ISNUMBER(D5),D5&gt;=$O$4,OR($O$11=0,B5&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K5">
-        <f>B5-$O$14</f>
+        <f>B5-$O$8</f>
         <v/>
       </c>
       <c r="N5" t="inlineStr">
@@ -1166,31 +1126,23 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <f>MEDIAN(D2:D26)</f>
+        <f>IFERROR(MEDIAN(D2:D26),D6)</f>
         <v/>
       </c>
       <c r="F6">
-        <f>E6</f>
+        <f>IF(OR(NOT(ISNUMBER(D6)),ABS(D6-E6)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G6">
-        <f>F6-E6</f>
+        <f>IF(F6=1,NA(),D6)</f>
         <v/>
       </c>
       <c r="H6">
-        <f>IF(OR(NOT(ISNUMBER(D6)),ABS(D6-E6)&gt;$O$3,AND($O$11=1,B6&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D6),D6&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I6">
-        <f>IF(H6=1,NA(),D6)</f>
-        <v/>
-      </c>
-      <c r="J6">
-        <f>IF(AND(ISNUMBER(D6),D6&gt;=$O$4,OR($O$11=0,B6&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K6">
-        <f>B6-$O$14</f>
+        <f>B6-$O$8</f>
         <v/>
       </c>
       <c r="N6" t="inlineStr">
@@ -1218,40 +1170,24 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <f>MEDIAN(D2:D27)</f>
+        <f>IFERROR(MEDIAN(D2:D27),D7)</f>
         <v/>
       </c>
       <c r="F7">
-        <f>E7</f>
+        <f>IF(OR(NOT(ISNUMBER(D7)),ABS(D7-E7)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G7">
-        <f>F7-E7</f>
+        <f>IF(F7=1,NA(),D7)</f>
         <v/>
       </c>
       <c r="H7">
-        <f>IF(OR(NOT(ISNUMBER(D7)),ABS(D7-E7)&gt;$O$3,AND($O$11=1,B7&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D7),D7&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I7">
-        <f>IF(H7=1,NA(),D7)</f>
-        <v/>
-      </c>
-      <c r="J7">
-        <f>IF(AND(ISNUMBER(D7),D7&gt;=$O$4,OR($O$11=0,B7&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K7">
-        <f>B7-$O$14</f>
-        <v/>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Reset bakis penceresi (satir)</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>20</v>
+        <f>B7-$O$8</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -1270,40 +1206,33 @@
         <v>8.880000000000001</v>
       </c>
       <c r="E8">
-        <f>MEDIAN(D2:D28)</f>
+        <f>IFERROR(MEDIAN(D2:D28),D8)</f>
         <v/>
       </c>
       <c r="F8">
-        <f>E8</f>
+        <f>IF(OR(NOT(ISNUMBER(D8)),ABS(D8-E8)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G8">
-        <f>F8-E8</f>
+        <f>IF(F8=1,NA(),D8)</f>
         <v/>
       </c>
       <c r="H8">
-        <f>IF(OR(NOT(ISNUMBER(D8)),ABS(D8-E8)&gt;$O$3,AND($O$11=1,B8&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D8),D8&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I8">
-        <f>IF(H8=1,NA(),D8)</f>
-        <v/>
-      </c>
-      <c r="J8">
-        <f>IF(AND(ISNUMBER(D8),D8&gt;=$O$4,OR($O$11=0,B8&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K8">
-        <f>B8-$O$14</f>
+        <f>B8-$O$8</f>
         <v/>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Reset esigi (g)</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>5</v>
+          <t>Baslangic zamani (s)</t>
+        </is>
+      </c>
+      <c r="O8">
+        <f>IFERROR(INDEX(B2:B116,MATCH(1,H2:H116,0)),0)</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -1322,31 +1251,23 @@
         <v>8.880000000000001</v>
       </c>
       <c r="E9">
-        <f>MEDIAN(D2:D29)</f>
+        <f>IFERROR(MEDIAN(D2:D29),D9)</f>
         <v/>
       </c>
       <c r="F9">
-        <f>E9</f>
+        <f>IF(OR(NOT(ISNUMBER(D9)),ABS(D9-E9)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G9">
-        <f>F9-E9</f>
+        <f>IF(F9=1,NA(),D9)</f>
         <v/>
       </c>
       <c r="H9">
-        <f>IF(OR(NOT(ISNUMBER(D9)),ABS(D9-E9)&gt;$O$3,AND($O$11=1,B9&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D9),D9&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I9">
-        <f>IF(H9=1,NA(),D9)</f>
-        <v/>
-      </c>
-      <c r="J9">
-        <f>IF(AND(ISNUMBER(D9),D9&gt;=$O$4,OR($O$11=0,B9&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K9">
-        <f>B9-$O$14</f>
+        <f>B9-$O$8</f>
         <v/>
       </c>
     </row>
@@ -1366,40 +1287,23 @@
         <v>8.08</v>
       </c>
       <c r="E10">
-        <f>MEDIAN(D2:D30)</f>
+        <f>IFERROR(MEDIAN(D2:D30),D10)</f>
         <v/>
       </c>
       <c r="F10">
-        <f>E10</f>
+        <f>IF(OR(NOT(ISNUMBER(D10)),ABS(D10-E10)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G10">
-        <f>F10-E10</f>
+        <f>IF(F10=1,NA(),D10)</f>
         <v/>
       </c>
       <c r="H10">
-        <f>IF(OR(NOT(ISNUMBER(D10)),ABS(D10-E10)&gt;$O$3,AND($O$11=1,B10&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D10),D10&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I10">
-        <f>IF(H10=1,NA(),D10)</f>
-        <v/>
-      </c>
-      <c r="J10">
-        <f>IF(AND(ISNUMBER(D10),D10&gt;=$O$4,OR($O$11=0,B10&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K10">
-        <f>B10-$O$14</f>
-        <v/>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>En buyuk dusus (g)</t>
-        </is>
-      </c>
-      <c r="O10">
-        <f>MAX(G2:G116)</f>
+        <f>B10-$O$8</f>
         <v/>
       </c>
     </row>
@@ -1419,40 +1323,23 @@
         <v>8.08</v>
       </c>
       <c r="E11">
-        <f>MEDIAN(D2:D31)</f>
+        <f>IFERROR(MEDIAN(D2:D31),D11)</f>
         <v/>
       </c>
       <c r="F11">
-        <f>E11</f>
+        <f>IF(OR(NOT(ISNUMBER(D11)),ABS(D11-E11)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G11">
-        <f>F11-E11</f>
+        <f>IF(F11=1,NA(),D11)</f>
         <v/>
       </c>
       <c r="H11">
-        <f>IF(OR(NOT(ISNUMBER(D11)),ABS(D11-E11)&gt;$O$3,AND($O$11=1,B11&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D11),D11&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I11">
-        <f>IF(H11=1,NA(),D11)</f>
-        <v/>
-      </c>
-      <c r="J11">
-        <f>IF(AND(ISNUMBER(D11),D11&gt;=$O$4,OR($O$11=0,B11&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K11">
-        <f>B11-$O$14</f>
-        <v/>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Reset tespit edildi mi (1/0)</t>
-        </is>
-      </c>
-      <c r="O11">
-        <f>IF(O10&gt;$O$8,1,0)</f>
+        <f>B11-$O$8</f>
         <v/>
       </c>
     </row>
@@ -1472,40 +1359,23 @@
         <v>8.880000000000001</v>
       </c>
       <c r="E12">
-        <f>MEDIAN(D2:D32)</f>
+        <f>IFERROR(MEDIAN(D2:D32),D12)</f>
         <v/>
       </c>
       <c r="F12">
-        <f>E12</f>
+        <f>IF(OR(NOT(ISNUMBER(D12)),ABS(D12-E12)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G12">
-        <f>F12-E12</f>
+        <f>IF(F12=1,NA(),D12)</f>
         <v/>
       </c>
       <c r="H12">
-        <f>IF(OR(NOT(ISNUMBER(D12)),ABS(D12-E12)&gt;$O$3,AND($O$11=1,B12&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D12),D12&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I12">
-        <f>IF(H12=1,NA(),D12)</f>
-        <v/>
-      </c>
-      <c r="J12">
-        <f>IF(AND(ISNUMBER(D12),D12&gt;=$O$4,OR($O$11=0,B12&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K12">
-        <f>B12-$O$14</f>
-        <v/>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Reset zamani (s)</t>
-        </is>
-      </c>
-      <c r="O12">
-        <f>IF(O11=1,INDEX(B2:B116,MATCH(O10,G2:G116,0)),-1000000)</f>
+        <f>B12-$O$8</f>
         <v/>
       </c>
     </row>
@@ -1525,31 +1395,23 @@
         <v>8.880000000000001</v>
       </c>
       <c r="E13">
-        <f>MEDIAN(D2:D33)</f>
+        <f>IFERROR(MEDIAN(D2:D33),D13)</f>
         <v/>
       </c>
       <c r="F13">
-        <f>E13</f>
+        <f>IF(OR(NOT(ISNUMBER(D13)),ABS(D13-E13)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G13">
-        <f>F13-E13</f>
+        <f>IF(F13=1,NA(),D13)</f>
         <v/>
       </c>
       <c r="H13">
-        <f>IF(OR(NOT(ISNUMBER(D13)),ABS(D13-E13)&gt;$O$3,AND($O$11=1,B13&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D13),D13&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I13">
-        <f>IF(H13=1,NA(),D13)</f>
-        <v/>
-      </c>
-      <c r="J13">
-        <f>IF(AND(ISNUMBER(D13),D13&gt;=$O$4,OR($O$11=0,B13&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K13">
-        <f>B13-$O$14</f>
+        <f>B13-$O$8</f>
         <v/>
       </c>
     </row>
@@ -1569,40 +1431,23 @@
         <v>8.16</v>
       </c>
       <c r="E14">
-        <f>MEDIAN(D2:D34)</f>
+        <f>IFERROR(MEDIAN(D2:D34),D14)</f>
         <v/>
       </c>
       <c r="F14">
-        <f>E14</f>
+        <f>IF(OR(NOT(ISNUMBER(D14)),ABS(D14-E14)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G14">
-        <f>F14-E14</f>
+        <f>IF(F14=1,NA(),D14)</f>
         <v/>
       </c>
       <c r="H14">
-        <f>IF(OR(NOT(ISNUMBER(D14)),ABS(D14-E14)&gt;$O$3,AND($O$11=1,B14&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D14),D14&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I14">
-        <f>IF(H14=1,NA(),D14)</f>
-        <v/>
-      </c>
-      <c r="J14">
-        <f>IF(AND(ISNUMBER(D14),D14&gt;=$O$4,OR($O$11=0,B14&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K14">
-        <f>B14-$O$14</f>
-        <v/>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Baslangic zamani (s)</t>
-        </is>
-      </c>
-      <c r="O14">
-        <f>INDEX(B2:B116,MATCH(1,J2:J116,0))</f>
+        <f>B14-$O$8</f>
         <v/>
       </c>
     </row>
@@ -1622,31 +1467,23 @@
         <v>8.56</v>
       </c>
       <c r="E15">
-        <f>MEDIAN(D2:D35)</f>
+        <f>IFERROR(MEDIAN(D2:D35),D15)</f>
         <v/>
       </c>
       <c r="F15">
-        <f>E15</f>
+        <f>IF(OR(NOT(ISNUMBER(D15)),ABS(D15-E15)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G15">
-        <f>F15-E15</f>
+        <f>IF(F15=1,NA(),D15)</f>
         <v/>
       </c>
       <c r="H15">
-        <f>IF(OR(NOT(ISNUMBER(D15)),ABS(D15-E15)&gt;$O$3,AND($O$11=1,B15&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D15),D15&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I15">
-        <f>IF(H15=1,NA(),D15)</f>
-        <v/>
-      </c>
-      <c r="J15">
-        <f>IF(AND(ISNUMBER(D15),D15&gt;=$O$4,OR($O$11=0,B15&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K15">
-        <f>B15-$O$14</f>
+        <f>B15-$O$8</f>
         <v/>
       </c>
     </row>
@@ -1666,31 +1503,23 @@
         <v>11.18</v>
       </c>
       <c r="E16">
-        <f>MEDIAN(D2:D36)</f>
+        <f>IFERROR(MEDIAN(D2:D36),D16)</f>
         <v/>
       </c>
       <c r="F16">
-        <f>E16</f>
+        <f>IF(OR(NOT(ISNUMBER(D16)),ABS(D16-E16)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G16">
-        <f>F16-E16</f>
+        <f>IF(F16=1,NA(),D16)</f>
         <v/>
       </c>
       <c r="H16">
-        <f>IF(OR(NOT(ISNUMBER(D16)),ABS(D16-E16)&gt;$O$3,AND($O$11=1,B16&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D16),D16&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I16">
-        <f>IF(H16=1,NA(),D16)</f>
-        <v/>
-      </c>
-      <c r="J16">
-        <f>IF(AND(ISNUMBER(D16),D16&gt;=$O$4,OR($O$11=0,B16&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K16">
-        <f>B16-$O$14</f>
+        <f>B16-$O$8</f>
         <v/>
       </c>
     </row>
@@ -1710,31 +1539,23 @@
         <v>1.11</v>
       </c>
       <c r="E17">
-        <f>MEDIAN(D2:D37)</f>
+        <f>IFERROR(MEDIAN(D2:D37),D17)</f>
         <v/>
       </c>
       <c r="F17">
-        <f>E17</f>
+        <f>IF(OR(NOT(ISNUMBER(D17)),ABS(D17-E17)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G17">
-        <f>F17-E17</f>
+        <f>IF(F17=1,NA(),D17)</f>
         <v/>
       </c>
       <c r="H17">
-        <f>IF(OR(NOT(ISNUMBER(D17)),ABS(D17-E17)&gt;$O$3,AND($O$11=1,B17&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D17),D17&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I17">
-        <f>IF(H17=1,NA(),D17)</f>
-        <v/>
-      </c>
-      <c r="J17">
-        <f>IF(AND(ISNUMBER(D17),D17&gt;=$O$4,OR($O$11=0,B17&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K17">
-        <f>B17-$O$14</f>
+        <f>B17-$O$8</f>
         <v/>
       </c>
     </row>
@@ -1754,31 +1575,23 @@
         <v>2.56</v>
       </c>
       <c r="E18">
-        <f>MEDIAN(D2:D38)</f>
+        <f>IFERROR(MEDIAN(D2:D38),D18)</f>
         <v/>
       </c>
       <c r="F18">
-        <f>E18</f>
+        <f>IF(OR(NOT(ISNUMBER(D18)),ABS(D18-E18)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G18">
-        <f>F18-E18</f>
+        <f>IF(F18=1,NA(),D18)</f>
         <v/>
       </c>
       <c r="H18">
-        <f>IF(OR(NOT(ISNUMBER(D18)),ABS(D18-E18)&gt;$O$3,AND($O$11=1,B18&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D18),D18&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I18">
-        <f>IF(H18=1,NA(),D18)</f>
-        <v/>
-      </c>
-      <c r="J18">
-        <f>IF(AND(ISNUMBER(D18),D18&gt;=$O$4,OR($O$11=0,B18&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K18">
-        <f>B18-$O$14</f>
+        <f>B18-$O$8</f>
         <v/>
       </c>
     </row>
@@ -1798,31 +1611,23 @@
         <v>3.48</v>
       </c>
       <c r="E19">
-        <f>MEDIAN(D2:D39)</f>
+        <f>IFERROR(MEDIAN(D2:D39),D19)</f>
         <v/>
       </c>
       <c r="F19">
-        <f>E19</f>
+        <f>IF(OR(NOT(ISNUMBER(D19)),ABS(D19-E19)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G19">
-        <f>F19-E19</f>
+        <f>IF(F19=1,NA(),D19)</f>
         <v/>
       </c>
       <c r="H19">
-        <f>IF(OR(NOT(ISNUMBER(D19)),ABS(D19-E19)&gt;$O$3,AND($O$11=1,B19&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D19),D19&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I19">
-        <f>IF(H19=1,NA(),D19)</f>
-        <v/>
-      </c>
-      <c r="J19">
-        <f>IF(AND(ISNUMBER(D19),D19&gt;=$O$4,OR($O$11=0,B19&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K19">
-        <f>B19-$O$14</f>
+        <f>B19-$O$8</f>
         <v/>
       </c>
     </row>
@@ -1842,31 +1647,23 @@
         <v>4.51</v>
       </c>
       <c r="E20">
-        <f>MEDIAN(D2:D40)</f>
+        <f>IFERROR(MEDIAN(D2:D40),D20)</f>
         <v/>
       </c>
       <c r="F20">
-        <f>E20</f>
+        <f>IF(OR(NOT(ISNUMBER(D20)),ABS(D20-E20)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G20">
-        <f>F20-E20</f>
+        <f>IF(F20=1,NA(),D20)</f>
         <v/>
       </c>
       <c r="H20">
-        <f>IF(OR(NOT(ISNUMBER(D20)),ABS(D20-E20)&gt;$O$3,AND($O$11=1,B20&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D20),D20&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I20">
-        <f>IF(H20=1,NA(),D20)</f>
-        <v/>
-      </c>
-      <c r="J20">
-        <f>IF(AND(ISNUMBER(D20),D20&gt;=$O$4,OR($O$11=0,B20&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K20">
-        <f>B20-$O$14</f>
+        <f>B20-$O$8</f>
         <v/>
       </c>
     </row>
@@ -1886,31 +1683,23 @@
         <v>6.87</v>
       </c>
       <c r="E21">
-        <f>MEDIAN(D2:D41)</f>
+        <f>IFERROR(MEDIAN(D2:D41),D21)</f>
         <v/>
       </c>
       <c r="F21">
-        <f>E21</f>
+        <f>IF(OR(NOT(ISNUMBER(D21)),ABS(D21-E21)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G21">
-        <f>F21-E21</f>
+        <f>IF(F21=1,NA(),D21)</f>
         <v/>
       </c>
       <c r="H21">
-        <f>IF(OR(NOT(ISNUMBER(D21)),ABS(D21-E21)&gt;$O$3,AND($O$11=1,B21&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D21),D21&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I21">
-        <f>IF(H21=1,NA(),D21)</f>
-        <v/>
-      </c>
-      <c r="J21">
-        <f>IF(AND(ISNUMBER(D21),D21&gt;=$O$4,OR($O$11=0,B21&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K21">
-        <f>B21-$O$14</f>
+        <f>B21-$O$8</f>
         <v/>
       </c>
     </row>
@@ -1930,31 +1719,23 @@
         <v>6.99</v>
       </c>
       <c r="E22">
-        <f>MEDIAN(D2:D42)</f>
+        <f>IFERROR(MEDIAN(D2:D42),D22)</f>
         <v/>
       </c>
       <c r="F22">
-        <f>E2</f>
+        <f>IF(OR(NOT(ISNUMBER(D22)),ABS(D22-E22)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G22">
-        <f>F22-E22</f>
+        <f>IF(F22=1,NA(),D22)</f>
         <v/>
       </c>
       <c r="H22">
-        <f>IF(OR(NOT(ISNUMBER(D22)),ABS(D22-E22)&gt;$O$3,AND($O$11=1,B22&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D22),D22&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I22">
-        <f>IF(H22=1,NA(),D22)</f>
-        <v/>
-      </c>
-      <c r="J22">
-        <f>IF(AND(ISNUMBER(D22),D22&gt;=$O$4,OR($O$11=0,B22&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K22">
-        <f>B22-$O$14</f>
+        <f>B22-$O$8</f>
         <v/>
       </c>
     </row>
@@ -1974,31 +1755,23 @@
         <v>8.34</v>
       </c>
       <c r="E23">
-        <f>MEDIAN(D3:D43)</f>
+        <f>IFERROR(MEDIAN(D3:D43),D23)</f>
         <v/>
       </c>
       <c r="F23">
-        <f>E3</f>
+        <f>IF(OR(NOT(ISNUMBER(D23)),ABS(D23-E23)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G23">
-        <f>F23-E23</f>
+        <f>IF(F23=1,NA(),D23)</f>
         <v/>
       </c>
       <c r="H23">
-        <f>IF(OR(NOT(ISNUMBER(D23)),ABS(D23-E23)&gt;$O$3,AND($O$11=1,B23&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D23),D23&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I23">
-        <f>IF(H23=1,NA(),D23)</f>
-        <v/>
-      </c>
-      <c r="J23">
-        <f>IF(AND(ISNUMBER(D23),D23&gt;=$O$4,OR($O$11=0,B23&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K23">
-        <f>B23-$O$14</f>
+        <f>B23-$O$8</f>
         <v/>
       </c>
     </row>
@@ -2018,31 +1791,23 @@
         <v>9.890000000000001</v>
       </c>
       <c r="E24">
-        <f>MEDIAN(D4:D44)</f>
+        <f>IFERROR(MEDIAN(D4:D44),D24)</f>
         <v/>
       </c>
       <c r="F24">
-        <f>E4</f>
+        <f>IF(OR(NOT(ISNUMBER(D24)),ABS(D24-E24)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G24">
-        <f>F24-E24</f>
+        <f>IF(F24=1,NA(),D24)</f>
         <v/>
       </c>
       <c r="H24">
-        <f>IF(OR(NOT(ISNUMBER(D24)),ABS(D24-E24)&gt;$O$3,AND($O$11=1,B24&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D24),D24&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I24">
-        <f>IF(H24=1,NA(),D24)</f>
-        <v/>
-      </c>
-      <c r="J24">
-        <f>IF(AND(ISNUMBER(D24),D24&gt;=$O$4,OR($O$11=0,B24&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K24">
-        <f>B24-$O$14</f>
+        <f>B24-$O$8</f>
         <v/>
       </c>
     </row>
@@ -2062,31 +1827,23 @@
         <v>14.32</v>
       </c>
       <c r="E25">
-        <f>MEDIAN(D5:D45)</f>
+        <f>IFERROR(MEDIAN(D5:D45),D25)</f>
         <v/>
       </c>
       <c r="F25">
-        <f>E5</f>
+        <f>IF(OR(NOT(ISNUMBER(D25)),ABS(D25-E25)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G25">
-        <f>F25-E25</f>
+        <f>IF(F25=1,NA(),D25)</f>
         <v/>
       </c>
       <c r="H25">
-        <f>IF(OR(NOT(ISNUMBER(D25)),ABS(D25-E25)&gt;$O$3,AND($O$11=1,B25&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D25),D25&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I25">
-        <f>IF(H25=1,NA(),D25)</f>
-        <v/>
-      </c>
-      <c r="J25">
-        <f>IF(AND(ISNUMBER(D25),D25&gt;=$O$4,OR($O$11=0,B25&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K25">
-        <f>B25-$O$14</f>
+        <f>B25-$O$8</f>
         <v/>
       </c>
     </row>
@@ -2106,31 +1863,23 @@
         <v>12.87</v>
       </c>
       <c r="E26">
-        <f>MEDIAN(D6:D46)</f>
+        <f>IFERROR(MEDIAN(D6:D46),D26)</f>
         <v/>
       </c>
       <c r="F26">
-        <f>E6</f>
+        <f>IF(OR(NOT(ISNUMBER(D26)),ABS(D26-E26)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G26">
-        <f>F26-E26</f>
+        <f>IF(F26=1,NA(),D26)</f>
         <v/>
       </c>
       <c r="H26">
-        <f>IF(OR(NOT(ISNUMBER(D26)),ABS(D26-E26)&gt;$O$3,AND($O$11=1,B26&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D26),D26&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I26">
-        <f>IF(H26=1,NA(),D26)</f>
-        <v/>
-      </c>
-      <c r="J26">
-        <f>IF(AND(ISNUMBER(D26),D26&gt;=$O$4,OR($O$11=0,B26&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K26">
-        <f>B26-$O$14</f>
+        <f>B26-$O$8</f>
         <v/>
       </c>
     </row>
@@ -2150,31 +1899,23 @@
         <v>19.97</v>
       </c>
       <c r="E27">
-        <f>MEDIAN(D7:D47)</f>
+        <f>IFERROR(MEDIAN(D7:D47),D27)</f>
         <v/>
       </c>
       <c r="F27">
-        <f>E7</f>
+        <f>IF(OR(NOT(ISNUMBER(D27)),ABS(D27-E27)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G27">
-        <f>F27-E27</f>
+        <f>IF(F27=1,NA(),D27)</f>
         <v/>
       </c>
       <c r="H27">
-        <f>IF(OR(NOT(ISNUMBER(D27)),ABS(D27-E27)&gt;$O$3,AND($O$11=1,B27&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D27),D27&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I27">
-        <f>IF(H27=1,NA(),D27)</f>
-        <v/>
-      </c>
-      <c r="J27">
-        <f>IF(AND(ISNUMBER(D27),D27&gt;=$O$4,OR($O$11=0,B27&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K27">
-        <f>B27-$O$14</f>
+        <f>B27-$O$8</f>
         <v/>
       </c>
     </row>
@@ -2194,31 +1935,23 @@
         <v>15.26</v>
       </c>
       <c r="E28">
-        <f>MEDIAN(D8:D48)</f>
+        <f>IFERROR(MEDIAN(D8:D48),D28)</f>
         <v/>
       </c>
       <c r="F28">
-        <f>E8</f>
+        <f>IF(OR(NOT(ISNUMBER(D28)),ABS(D28-E28)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G28">
-        <f>F28-E28</f>
+        <f>IF(F28=1,NA(),D28)</f>
         <v/>
       </c>
       <c r="H28">
-        <f>IF(OR(NOT(ISNUMBER(D28)),ABS(D28-E28)&gt;$O$3,AND($O$11=1,B28&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D28),D28&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I28">
-        <f>IF(H28=1,NA(),D28)</f>
-        <v/>
-      </c>
-      <c r="J28">
-        <f>IF(AND(ISNUMBER(D28),D28&gt;=$O$4,OR($O$11=0,B28&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K28">
-        <f>B28-$O$14</f>
+        <f>B28-$O$8</f>
         <v/>
       </c>
     </row>
@@ -2238,31 +1971,23 @@
         <v>16.45</v>
       </c>
       <c r="E29">
-        <f>MEDIAN(D9:D49)</f>
+        <f>IFERROR(MEDIAN(D9:D49),D29)</f>
         <v/>
       </c>
       <c r="F29">
-        <f>E9</f>
+        <f>IF(OR(NOT(ISNUMBER(D29)),ABS(D29-E29)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G29">
-        <f>F29-E29</f>
+        <f>IF(F29=1,NA(),D29)</f>
         <v/>
       </c>
       <c r="H29">
-        <f>IF(OR(NOT(ISNUMBER(D29)),ABS(D29-E29)&gt;$O$3,AND($O$11=1,B29&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D29),D29&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I29">
-        <f>IF(H29=1,NA(),D29)</f>
-        <v/>
-      </c>
-      <c r="J29">
-        <f>IF(AND(ISNUMBER(D29),D29&gt;=$O$4,OR($O$11=0,B29&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K29">
-        <f>B29-$O$14</f>
+        <f>B29-$O$8</f>
         <v/>
       </c>
     </row>
@@ -2282,31 +2007,23 @@
         <v>19.82</v>
       </c>
       <c r="E30">
-        <f>MEDIAN(D10:D50)</f>
+        <f>IFERROR(MEDIAN(D10:D50),D30)</f>
         <v/>
       </c>
       <c r="F30">
-        <f>E10</f>
+        <f>IF(OR(NOT(ISNUMBER(D30)),ABS(D30-E30)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G30">
-        <f>F30-E30</f>
+        <f>IF(F30=1,NA(),D30)</f>
         <v/>
       </c>
       <c r="H30">
-        <f>IF(OR(NOT(ISNUMBER(D30)),ABS(D30-E30)&gt;$O$3,AND($O$11=1,B30&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D30),D30&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I30">
-        <f>IF(H30=1,NA(),D30)</f>
-        <v/>
-      </c>
-      <c r="J30">
-        <f>IF(AND(ISNUMBER(D30),D30&gt;=$O$4,OR($O$11=0,B30&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K30">
-        <f>B30-$O$14</f>
+        <f>B30-$O$8</f>
         <v/>
       </c>
     </row>
@@ -2326,31 +2043,23 @@
         <v>8.880000000000001</v>
       </c>
       <c r="E31">
-        <f>MEDIAN(D11:D51)</f>
+        <f>IFERROR(MEDIAN(D11:D51),D31)</f>
         <v/>
       </c>
       <c r="F31">
-        <f>E11</f>
+        <f>IF(OR(NOT(ISNUMBER(D31)),ABS(D31-E31)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G31">
-        <f>F31-E31</f>
+        <f>IF(F31=1,NA(),D31)</f>
         <v/>
       </c>
       <c r="H31">
-        <f>IF(OR(NOT(ISNUMBER(D31)),ABS(D31-E31)&gt;$O$3,AND($O$11=1,B31&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D31),D31&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I31">
-        <f>IF(H31=1,NA(),D31)</f>
-        <v/>
-      </c>
-      <c r="J31">
-        <f>IF(AND(ISNUMBER(D31),D31&gt;=$O$4,OR($O$11=0,B31&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K31">
-        <f>B31-$O$14</f>
+        <f>B31-$O$8</f>
         <v/>
       </c>
     </row>
@@ -2370,31 +2079,23 @@
         <v>28.98</v>
       </c>
       <c r="E32">
-        <f>MEDIAN(D12:D52)</f>
+        <f>IFERROR(MEDIAN(D12:D52),D32)</f>
         <v/>
       </c>
       <c r="F32">
-        <f>E12</f>
+        <f>IF(OR(NOT(ISNUMBER(D32)),ABS(D32-E32)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G32">
-        <f>F32-E32</f>
+        <f>IF(F32=1,NA(),D32)</f>
         <v/>
       </c>
       <c r="H32">
-        <f>IF(OR(NOT(ISNUMBER(D32)),ABS(D32-E32)&gt;$O$3,AND($O$11=1,B32&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D32),D32&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I32">
-        <f>IF(H32=1,NA(),D32)</f>
-        <v/>
-      </c>
-      <c r="J32">
-        <f>IF(AND(ISNUMBER(D32),D32&gt;=$O$4,OR($O$11=0,B32&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K32">
-        <f>B32-$O$14</f>
+        <f>B32-$O$8</f>
         <v/>
       </c>
     </row>
@@ -2411,31 +2112,23 @@
         </is>
       </c>
       <c r="E33">
-        <f>MEDIAN(D13:D53)</f>
+        <f>IFERROR(MEDIAN(D13:D53),D33)</f>
         <v/>
       </c>
       <c r="F33">
-        <f>E13</f>
+        <f>IF(OR(NOT(ISNUMBER(D33)),ABS(D33-E33)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G33">
-        <f>F33-E33</f>
+        <f>IF(F33=1,NA(),D33)</f>
         <v/>
       </c>
       <c r="H33">
-        <f>IF(OR(NOT(ISNUMBER(D33)),ABS(D33-E33)&gt;$O$3,AND($O$11=1,B33&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D33),D33&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I33">
-        <f>IF(H33=1,NA(),D33)</f>
-        <v/>
-      </c>
-      <c r="J33">
-        <f>IF(AND(ISNUMBER(D33),D33&gt;=$O$4,OR($O$11=0,B33&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K33">
-        <f>B33-$O$14</f>
+        <f>B33-$O$8</f>
         <v/>
       </c>
     </row>
@@ -2452,31 +2145,23 @@
         </is>
       </c>
       <c r="E34">
-        <f>MEDIAN(D14:D54)</f>
+        <f>IFERROR(MEDIAN(D14:D54),D34)</f>
         <v/>
       </c>
       <c r="F34">
-        <f>E14</f>
+        <f>IF(OR(NOT(ISNUMBER(D34)),ABS(D34-E34)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G34">
-        <f>F34-E34</f>
+        <f>IF(F34=1,NA(),D34)</f>
         <v/>
       </c>
       <c r="H34">
-        <f>IF(OR(NOT(ISNUMBER(D34)),ABS(D34-E34)&gt;$O$3,AND($O$11=1,B34&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D34),D34&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I34">
-        <f>IF(H34=1,NA(),D34)</f>
-        <v/>
-      </c>
-      <c r="J34">
-        <f>IF(AND(ISNUMBER(D34),D34&gt;=$O$4,OR($O$11=0,B34&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K34">
-        <f>B34-$O$14</f>
+        <f>B34-$O$8</f>
         <v/>
       </c>
     </row>
@@ -2496,31 +2181,23 @@
         <v>29.85</v>
       </c>
       <c r="E35">
-        <f>MEDIAN(D15:D55)</f>
+        <f>IFERROR(MEDIAN(D15:D55),D35)</f>
         <v/>
       </c>
       <c r="F35">
-        <f>E15</f>
+        <f>IF(OR(NOT(ISNUMBER(D35)),ABS(D35-E35)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G35">
-        <f>F35-E35</f>
+        <f>IF(F35=1,NA(),D35)</f>
         <v/>
       </c>
       <c r="H35">
-        <f>IF(OR(NOT(ISNUMBER(D35)),ABS(D35-E35)&gt;$O$3,AND($O$11=1,B35&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D35),D35&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I35">
-        <f>IF(H35=1,NA(),D35)</f>
-        <v/>
-      </c>
-      <c r="J35">
-        <f>IF(AND(ISNUMBER(D35),D35&gt;=$O$4,OR($O$11=0,B35&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K35">
-        <f>B35-$O$14</f>
+        <f>B35-$O$8</f>
         <v/>
       </c>
     </row>
@@ -2540,31 +2217,23 @@
         <v>28.88</v>
       </c>
       <c r="E36">
-        <f>MEDIAN(D16:D56)</f>
+        <f>IFERROR(MEDIAN(D16:D56),D36)</f>
         <v/>
       </c>
       <c r="F36">
-        <f>E16</f>
+        <f>IF(OR(NOT(ISNUMBER(D36)),ABS(D36-E36)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G36">
-        <f>F36-E36</f>
+        <f>IF(F36=1,NA(),D36)</f>
         <v/>
       </c>
       <c r="H36">
-        <f>IF(OR(NOT(ISNUMBER(D36)),ABS(D36-E36)&gt;$O$3,AND($O$11=1,B36&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D36),D36&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I36">
-        <f>IF(H36=1,NA(),D36)</f>
-        <v/>
-      </c>
-      <c r="J36">
-        <f>IF(AND(ISNUMBER(D36),D36&gt;=$O$4,OR($O$11=0,B36&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K36">
-        <f>B36-$O$14</f>
+        <f>B36-$O$8</f>
         <v/>
       </c>
     </row>
@@ -2584,31 +2253,23 @@
         <v>28.82</v>
       </c>
       <c r="E37">
-        <f>MEDIAN(D17:D57)</f>
+        <f>IFERROR(MEDIAN(D17:D57),D37)</f>
         <v/>
       </c>
       <c r="F37">
-        <f>E17</f>
+        <f>IF(OR(NOT(ISNUMBER(D37)),ABS(D37-E37)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G37">
-        <f>F37-E37</f>
+        <f>IF(F37=1,NA(),D37)</f>
         <v/>
       </c>
       <c r="H37">
-        <f>IF(OR(NOT(ISNUMBER(D37)),ABS(D37-E37)&gt;$O$3,AND($O$11=1,B37&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D37),D37&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I37">
-        <f>IF(H37=1,NA(),D37)</f>
-        <v/>
-      </c>
-      <c r="J37">
-        <f>IF(AND(ISNUMBER(D37),D37&gt;=$O$4,OR($O$11=0,B37&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K37">
-        <f>B37-$O$14</f>
+        <f>B37-$O$8</f>
         <v/>
       </c>
     </row>
@@ -2625,31 +2286,23 @@
         </is>
       </c>
       <c r="E38">
-        <f>MEDIAN(D18:D58)</f>
+        <f>IFERROR(MEDIAN(D18:D58),D38)</f>
         <v/>
       </c>
       <c r="F38">
-        <f>E18</f>
+        <f>IF(OR(NOT(ISNUMBER(D38)),ABS(D38-E38)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G38">
-        <f>F38-E38</f>
+        <f>IF(F38=1,NA(),D38)</f>
         <v/>
       </c>
       <c r="H38">
-        <f>IF(OR(NOT(ISNUMBER(D38)),ABS(D38-E38)&gt;$O$3,AND($O$11=1,B38&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D38),D38&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I38">
-        <f>IF(H38=1,NA(),D38)</f>
-        <v/>
-      </c>
-      <c r="J38">
-        <f>IF(AND(ISNUMBER(D38),D38&gt;=$O$4,OR($O$11=0,B38&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K38">
-        <f>B38-$O$14</f>
+        <f>B38-$O$8</f>
         <v/>
       </c>
     </row>
@@ -2669,31 +2322,23 @@
         <v>28.26</v>
       </c>
       <c r="E39">
-        <f>MEDIAN(D19:D59)</f>
+        <f>IFERROR(MEDIAN(D19:D59),D39)</f>
         <v/>
       </c>
       <c r="F39">
-        <f>E19</f>
+        <f>IF(OR(NOT(ISNUMBER(D39)),ABS(D39-E39)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G39">
-        <f>F39-E39</f>
+        <f>IF(F39=1,NA(),D39)</f>
         <v/>
       </c>
       <c r="H39">
-        <f>IF(OR(NOT(ISNUMBER(D39)),ABS(D39-E39)&gt;$O$3,AND($O$11=1,B39&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D39),D39&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I39">
-        <f>IF(H39=1,NA(),D39)</f>
-        <v/>
-      </c>
-      <c r="J39">
-        <f>IF(AND(ISNUMBER(D39),D39&gt;=$O$4,OR($O$11=0,B39&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K39">
-        <f>B39-$O$14</f>
+        <f>B39-$O$8</f>
         <v/>
       </c>
     </row>
@@ -2713,31 +2358,23 @@
         <v>28.98</v>
       </c>
       <c r="E40">
-        <f>MEDIAN(D20:D60)</f>
+        <f>IFERROR(MEDIAN(D20:D60),D40)</f>
         <v/>
       </c>
       <c r="F40">
-        <f>E20</f>
+        <f>IF(OR(NOT(ISNUMBER(D40)),ABS(D40-E40)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G40">
-        <f>F40-E40</f>
+        <f>IF(F40=1,NA(),D40)</f>
         <v/>
       </c>
       <c r="H40">
-        <f>IF(OR(NOT(ISNUMBER(D40)),ABS(D40-E40)&gt;$O$3,AND($O$11=1,B40&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D40),D40&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I40">
-        <f>IF(H40=1,NA(),D40)</f>
-        <v/>
-      </c>
-      <c r="J40">
-        <f>IF(AND(ISNUMBER(D40),D40&gt;=$O$4,OR($O$11=0,B40&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K40">
-        <f>B40-$O$14</f>
+        <f>B40-$O$8</f>
         <v/>
       </c>
     </row>
@@ -2757,31 +2394,23 @@
         <v>30.48</v>
       </c>
       <c r="E41">
-        <f>MEDIAN(D21:D61)</f>
+        <f>IFERROR(MEDIAN(D21:D61),D41)</f>
         <v/>
       </c>
       <c r="F41">
-        <f>E21</f>
+        <f>IF(OR(NOT(ISNUMBER(D41)),ABS(D41-E41)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G41">
-        <f>F41-E41</f>
+        <f>IF(F41=1,NA(),D41)</f>
         <v/>
       </c>
       <c r="H41">
-        <f>IF(OR(NOT(ISNUMBER(D41)),ABS(D41-E41)&gt;$O$3,AND($O$11=1,B41&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D41),D41&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I41">
-        <f>IF(H41=1,NA(),D41)</f>
-        <v/>
-      </c>
-      <c r="J41">
-        <f>IF(AND(ISNUMBER(D41),D41&gt;=$O$4,OR($O$11=0,B41&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K41">
-        <f>B41-$O$14</f>
+        <f>B41-$O$8</f>
         <v/>
       </c>
     </row>
@@ -2798,31 +2427,23 @@
         </is>
       </c>
       <c r="E42">
-        <f>MEDIAN(D22:D62)</f>
+        <f>IFERROR(MEDIAN(D22:D62),D42)</f>
         <v/>
       </c>
       <c r="F42">
-        <f>E22</f>
+        <f>IF(OR(NOT(ISNUMBER(D42)),ABS(D42-E42)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G42">
-        <f>F42-E42</f>
+        <f>IF(F42=1,NA(),D42)</f>
         <v/>
       </c>
       <c r="H42">
-        <f>IF(OR(NOT(ISNUMBER(D42)),ABS(D42-E42)&gt;$O$3,AND($O$11=1,B42&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D42),D42&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I42">
-        <f>IF(H42=1,NA(),D42)</f>
-        <v/>
-      </c>
-      <c r="J42">
-        <f>IF(AND(ISNUMBER(D42),D42&gt;=$O$4,OR($O$11=0,B42&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K42">
-        <f>B42-$O$14</f>
+        <f>B42-$O$8</f>
         <v/>
       </c>
     </row>
@@ -2842,31 +2463,23 @@
         <v>32.62</v>
       </c>
       <c r="E43">
-        <f>MEDIAN(D23:D63)</f>
+        <f>IFERROR(MEDIAN(D23:D63),D43)</f>
         <v/>
       </c>
       <c r="F43">
-        <f>E23</f>
+        <f>IF(OR(NOT(ISNUMBER(D43)),ABS(D43-E43)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G43">
-        <f>F43-E43</f>
+        <f>IF(F43=1,NA(),D43)</f>
         <v/>
       </c>
       <c r="H43">
-        <f>IF(OR(NOT(ISNUMBER(D43)),ABS(D43-E43)&gt;$O$3,AND($O$11=1,B43&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D43),D43&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I43">
-        <f>IF(H43=1,NA(),D43)</f>
-        <v/>
-      </c>
-      <c r="J43">
-        <f>IF(AND(ISNUMBER(D43),D43&gt;=$O$4,OR($O$11=0,B43&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K43">
-        <f>B43-$O$14</f>
+        <f>B43-$O$8</f>
         <v/>
       </c>
     </row>
@@ -2886,31 +2499,23 @@
         <v>39.82</v>
       </c>
       <c r="E44">
-        <f>MEDIAN(D24:D64)</f>
+        <f>IFERROR(MEDIAN(D24:D64),D44)</f>
         <v/>
       </c>
       <c r="F44">
-        <f>E24</f>
+        <f>IF(OR(NOT(ISNUMBER(D44)),ABS(D44-E44)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G44">
-        <f>F44-E44</f>
+        <f>IF(F44=1,NA(),D44)</f>
         <v/>
       </c>
       <c r="H44">
-        <f>IF(OR(NOT(ISNUMBER(D44)),ABS(D44-E44)&gt;$O$3,AND($O$11=1,B44&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D44),D44&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I44">
-        <f>IF(H44=1,NA(),D44)</f>
-        <v/>
-      </c>
-      <c r="J44">
-        <f>IF(AND(ISNUMBER(D44),D44&gt;=$O$4,OR($O$11=0,B44&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K44">
-        <f>B44-$O$14</f>
+        <f>B44-$O$8</f>
         <v/>
       </c>
     </row>
@@ -2930,31 +2535,23 @@
         <v>39.72</v>
       </c>
       <c r="E45">
-        <f>MEDIAN(D25:D65)</f>
+        <f>IFERROR(MEDIAN(D25:D65),D45)</f>
         <v/>
       </c>
       <c r="F45">
-        <f>E25</f>
+        <f>IF(OR(NOT(ISNUMBER(D45)),ABS(D45-E45)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G45">
-        <f>F45-E45</f>
+        <f>IF(F45=1,NA(),D45)</f>
         <v/>
       </c>
       <c r="H45">
-        <f>IF(OR(NOT(ISNUMBER(D45)),ABS(D45-E45)&gt;$O$3,AND($O$11=1,B45&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D45),D45&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I45">
-        <f>IF(H45=1,NA(),D45)</f>
-        <v/>
-      </c>
-      <c r="J45">
-        <f>IF(AND(ISNUMBER(D45),D45&gt;=$O$4,OR($O$11=0,B45&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K45">
-        <f>B45-$O$14</f>
+        <f>B45-$O$8</f>
         <v/>
       </c>
     </row>
@@ -2974,31 +2571,23 @@
         <v>36.8</v>
       </c>
       <c r="E46">
-        <f>MEDIAN(D26:D66)</f>
+        <f>IFERROR(MEDIAN(D26:D66),D46)</f>
         <v/>
       </c>
       <c r="F46">
-        <f>E26</f>
+        <f>IF(OR(NOT(ISNUMBER(D46)),ABS(D46-E46)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G46">
-        <f>F46-E46</f>
+        <f>IF(F46=1,NA(),D46)</f>
         <v/>
       </c>
       <c r="H46">
-        <f>IF(OR(NOT(ISNUMBER(D46)),ABS(D46-E46)&gt;$O$3,AND($O$11=1,B46&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D46),D46&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I46">
-        <f>IF(H46=1,NA(),D46)</f>
-        <v/>
-      </c>
-      <c r="J46">
-        <f>IF(AND(ISNUMBER(D46),D46&gt;=$O$4,OR($O$11=0,B46&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K46">
-        <f>B46-$O$14</f>
+        <f>B46-$O$8</f>
         <v/>
       </c>
     </row>
@@ -3018,31 +2607,23 @@
         <v>36.88</v>
       </c>
       <c r="E47">
-        <f>MEDIAN(D27:D67)</f>
+        <f>IFERROR(MEDIAN(D27:D67),D47)</f>
         <v/>
       </c>
       <c r="F47">
-        <f>E27</f>
+        <f>IF(OR(NOT(ISNUMBER(D47)),ABS(D47-E47)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G47">
-        <f>F47-E47</f>
+        <f>IF(F47=1,NA(),D47)</f>
         <v/>
       </c>
       <c r="H47">
-        <f>IF(OR(NOT(ISNUMBER(D47)),ABS(D47-E47)&gt;$O$3,AND($O$11=1,B47&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D47),D47&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I47">
-        <f>IF(H47=1,NA(),D47)</f>
-        <v/>
-      </c>
-      <c r="J47">
-        <f>IF(AND(ISNUMBER(D47),D47&gt;=$O$4,OR($O$11=0,B47&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K47">
-        <f>B47-$O$14</f>
+        <f>B47-$O$8</f>
         <v/>
       </c>
     </row>
@@ -3062,31 +2643,23 @@
         <v>38.82</v>
       </c>
       <c r="E48">
-        <f>MEDIAN(D28:D68)</f>
+        <f>IFERROR(MEDIAN(D28:D68),D48)</f>
         <v/>
       </c>
       <c r="F48">
-        <f>E28</f>
+        <f>IF(OR(NOT(ISNUMBER(D48)),ABS(D48-E48)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G48">
-        <f>F48-E48</f>
+        <f>IF(F48=1,NA(),D48)</f>
         <v/>
       </c>
       <c r="H48">
-        <f>IF(OR(NOT(ISNUMBER(D48)),ABS(D48-E48)&gt;$O$3,AND($O$11=1,B48&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D48),D48&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I48">
-        <f>IF(H48=1,NA(),D48)</f>
-        <v/>
-      </c>
-      <c r="J48">
-        <f>IF(AND(ISNUMBER(D48),D48&gt;=$O$4,OR($O$11=0,B48&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K48">
-        <f>B48-$O$14</f>
+        <f>B48-$O$8</f>
         <v/>
       </c>
     </row>
@@ -3106,31 +2679,23 @@
         <v>38.82</v>
       </c>
       <c r="E49">
-        <f>MEDIAN(D29:D69)</f>
+        <f>IFERROR(MEDIAN(D29:D69),D49)</f>
         <v/>
       </c>
       <c r="F49">
-        <f>E29</f>
+        <f>IF(OR(NOT(ISNUMBER(D49)),ABS(D49-E49)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G49">
-        <f>F49-E49</f>
+        <f>IF(F49=1,NA(),D49)</f>
         <v/>
       </c>
       <c r="H49">
-        <f>IF(OR(NOT(ISNUMBER(D49)),ABS(D49-E49)&gt;$O$3,AND($O$11=1,B49&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D49),D49&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I49">
-        <f>IF(H49=1,NA(),D49)</f>
-        <v/>
-      </c>
-      <c r="J49">
-        <f>IF(AND(ISNUMBER(D49),D49&gt;=$O$4,OR($O$11=0,B49&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K49">
-        <f>B49-$O$14</f>
+        <f>B49-$O$8</f>
         <v/>
       </c>
     </row>
@@ -3150,31 +2715,23 @@
         <v>98.88</v>
       </c>
       <c r="E50">
-        <f>MEDIAN(D30:D70)</f>
+        <f>IFERROR(MEDIAN(D30:D70),D50)</f>
         <v/>
       </c>
       <c r="F50">
-        <f>E30</f>
+        <f>IF(OR(NOT(ISNUMBER(D50)),ABS(D50-E50)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G50">
-        <f>F50-E50</f>
+        <f>IF(F50=1,NA(),D50)</f>
         <v/>
       </c>
       <c r="H50">
-        <f>IF(OR(NOT(ISNUMBER(D50)),ABS(D50-E50)&gt;$O$3,AND($O$11=1,B50&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D50),D50&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I50">
-        <f>IF(H50=1,NA(),D50)</f>
-        <v/>
-      </c>
-      <c r="J50">
-        <f>IF(AND(ISNUMBER(D50),D50&gt;=$O$4,OR($O$11=0,B50&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K50">
-        <f>B50-$O$14</f>
+        <f>B50-$O$8</f>
         <v/>
       </c>
     </row>
@@ -3194,31 +2751,23 @@
         <v>40.88</v>
       </c>
       <c r="E51">
-        <f>MEDIAN(D31:D71)</f>
+        <f>IFERROR(MEDIAN(D31:D71),D51)</f>
         <v/>
       </c>
       <c r="F51">
-        <f>E31</f>
+        <f>IF(OR(NOT(ISNUMBER(D51)),ABS(D51-E51)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G51">
-        <f>F51-E51</f>
+        <f>IF(F51=1,NA(),D51)</f>
         <v/>
       </c>
       <c r="H51">
-        <f>IF(OR(NOT(ISNUMBER(D51)),ABS(D51-E51)&gt;$O$3,AND($O$11=1,B51&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D51),D51&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I51">
-        <f>IF(H51=1,NA(),D51)</f>
-        <v/>
-      </c>
-      <c r="J51">
-        <f>IF(AND(ISNUMBER(D51),D51&gt;=$O$4,OR($O$11=0,B51&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K51">
-        <f>B51-$O$14</f>
+        <f>B51-$O$8</f>
         <v/>
       </c>
     </row>
@@ -3235,31 +2784,23 @@
         </is>
       </c>
       <c r="E52">
-        <f>MEDIAN(D32:D72)</f>
+        <f>IFERROR(MEDIAN(D32:D72),D52)</f>
         <v/>
       </c>
       <c r="F52">
-        <f>E32</f>
+        <f>IF(OR(NOT(ISNUMBER(D52)),ABS(D52-E52)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G52">
-        <f>F52-E52</f>
+        <f>IF(F52=1,NA(),D52)</f>
         <v/>
       </c>
       <c r="H52">
-        <f>IF(OR(NOT(ISNUMBER(D52)),ABS(D52-E52)&gt;$O$3,AND($O$11=1,B52&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D52),D52&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I52">
-        <f>IF(H52=1,NA(),D52)</f>
-        <v/>
-      </c>
-      <c r="J52">
-        <f>IF(AND(ISNUMBER(D52),D52&gt;=$O$4,OR($O$11=0,B52&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K52">
-        <f>B52-$O$14</f>
+        <f>B52-$O$8</f>
         <v/>
       </c>
     </row>
@@ -3276,31 +2817,23 @@
         </is>
       </c>
       <c r="E53">
-        <f>MEDIAN(D33:D73)</f>
+        <f>IFERROR(MEDIAN(D33:D73),D53)</f>
         <v/>
       </c>
       <c r="F53">
-        <f>E33</f>
+        <f>IF(OR(NOT(ISNUMBER(D53)),ABS(D53-E53)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G53">
-        <f>F53-E53</f>
+        <f>IF(F53=1,NA(),D53)</f>
         <v/>
       </c>
       <c r="H53">
-        <f>IF(OR(NOT(ISNUMBER(D53)),ABS(D53-E53)&gt;$O$3,AND($O$11=1,B53&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D53),D53&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I53">
-        <f>IF(H53=1,NA(),D53)</f>
-        <v/>
-      </c>
-      <c r="J53">
-        <f>IF(AND(ISNUMBER(D53),D53&gt;=$O$4,OR($O$11=0,B53&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K53">
-        <f>B53-$O$14</f>
+        <f>B53-$O$8</f>
         <v/>
       </c>
     </row>
@@ -3320,31 +2853,23 @@
         <v>49.69</v>
       </c>
       <c r="E54">
-        <f>MEDIAN(D34:D74)</f>
+        <f>IFERROR(MEDIAN(D34:D74),D54)</f>
         <v/>
       </c>
       <c r="F54">
-        <f>E34</f>
+        <f>IF(OR(NOT(ISNUMBER(D54)),ABS(D54-E54)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G54">
-        <f>F54-E54</f>
+        <f>IF(F54=1,NA(),D54)</f>
         <v/>
       </c>
       <c r="H54">
-        <f>IF(OR(NOT(ISNUMBER(D54)),ABS(D54-E54)&gt;$O$3,AND($O$11=1,B54&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D54),D54&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I54">
-        <f>IF(H54=1,NA(),D54)</f>
-        <v/>
-      </c>
-      <c r="J54">
-        <f>IF(AND(ISNUMBER(D54),D54&gt;=$O$4,OR($O$11=0,B54&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K54">
-        <f>B54-$O$14</f>
+        <f>B54-$O$8</f>
         <v/>
       </c>
     </row>
@@ -3364,31 +2889,23 @@
         <v>44.98</v>
       </c>
       <c r="E55">
-        <f>MEDIAN(D35:D75)</f>
+        <f>IFERROR(MEDIAN(D35:D75),D55)</f>
         <v/>
       </c>
       <c r="F55">
-        <f>E35</f>
+        <f>IF(OR(NOT(ISNUMBER(D55)),ABS(D55-E55)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G55">
-        <f>F55-E55</f>
+        <f>IF(F55=1,NA(),D55)</f>
         <v/>
       </c>
       <c r="H55">
-        <f>IF(OR(NOT(ISNUMBER(D55)),ABS(D55-E55)&gt;$O$3,AND($O$11=1,B55&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D55),D55&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I55">
-        <f>IF(H55=1,NA(),D55)</f>
-        <v/>
-      </c>
-      <c r="J55">
-        <f>IF(AND(ISNUMBER(D55),D55&gt;=$O$4,OR($O$11=0,B55&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K55">
-        <f>B55-$O$14</f>
+        <f>B55-$O$8</f>
         <v/>
       </c>
     </row>
@@ -3408,31 +2925,23 @@
         <v>46.98</v>
       </c>
       <c r="E56">
-        <f>MEDIAN(D36:D76)</f>
+        <f>IFERROR(MEDIAN(D36:D76),D56)</f>
         <v/>
       </c>
       <c r="F56">
-        <f>E36</f>
+        <f>IF(OR(NOT(ISNUMBER(D56)),ABS(D56-E56)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G56">
-        <f>F56-E56</f>
+        <f>IF(F56=1,NA(),D56)</f>
         <v/>
       </c>
       <c r="H56">
-        <f>IF(OR(NOT(ISNUMBER(D56)),ABS(D56-E56)&gt;$O$3,AND($O$11=1,B56&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D56),D56&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I56">
-        <f>IF(H56=1,NA(),D56)</f>
-        <v/>
-      </c>
-      <c r="J56">
-        <f>IF(AND(ISNUMBER(D56),D56&gt;=$O$4,OR($O$11=0,B56&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K56">
-        <f>B56-$O$14</f>
+        <f>B56-$O$8</f>
         <v/>
       </c>
     </row>
@@ -3452,31 +2961,23 @@
         <v>48.28</v>
       </c>
       <c r="E57">
-        <f>MEDIAN(D37:D77)</f>
+        <f>IFERROR(MEDIAN(D37:D77),D57)</f>
         <v/>
       </c>
       <c r="F57">
-        <f>E37</f>
+        <f>IF(OR(NOT(ISNUMBER(D57)),ABS(D57-E57)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G57">
-        <f>F57-E57</f>
+        <f>IF(F57=1,NA(),D57)</f>
         <v/>
       </c>
       <c r="H57">
-        <f>IF(OR(NOT(ISNUMBER(D57)),ABS(D57-E57)&gt;$O$3,AND($O$11=1,B57&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D57),D57&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I57">
-        <f>IF(H57=1,NA(),D57)</f>
-        <v/>
-      </c>
-      <c r="J57">
-        <f>IF(AND(ISNUMBER(D57),D57&gt;=$O$4,OR($O$11=0,B57&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K57">
-        <f>B57-$O$14</f>
+        <f>B57-$O$8</f>
         <v/>
       </c>
     </row>
@@ -3496,31 +2997,23 @@
         <v>48.28</v>
       </c>
       <c r="E58">
-        <f>MEDIAN(D38:D78)</f>
+        <f>IFERROR(MEDIAN(D38:D78),D58)</f>
         <v/>
       </c>
       <c r="F58">
-        <f>E38</f>
+        <f>IF(OR(NOT(ISNUMBER(D58)),ABS(D58-E58)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G58">
-        <f>F58-E58</f>
+        <f>IF(F58=1,NA(),D58)</f>
         <v/>
       </c>
       <c r="H58">
-        <f>IF(OR(NOT(ISNUMBER(D58)),ABS(D58-E58)&gt;$O$3,AND($O$11=1,B58&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D58),D58&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I58">
-        <f>IF(H58=1,NA(),D58)</f>
-        <v/>
-      </c>
-      <c r="J58">
-        <f>IF(AND(ISNUMBER(D58),D58&gt;=$O$4,OR($O$11=0,B58&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K58">
-        <f>B58-$O$14</f>
+        <f>B58-$O$8</f>
         <v/>
       </c>
     </row>
@@ -3540,31 +3033,23 @@
         <v>48.98</v>
       </c>
       <c r="E59">
-        <f>MEDIAN(D39:D79)</f>
+        <f>IFERROR(MEDIAN(D39:D79),D59)</f>
         <v/>
       </c>
       <c r="F59">
-        <f>E39</f>
+        <f>IF(OR(NOT(ISNUMBER(D59)),ABS(D59-E59)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G59">
-        <f>F59-E59</f>
+        <f>IF(F59=1,NA(),D59)</f>
         <v/>
       </c>
       <c r="H59">
-        <f>IF(OR(NOT(ISNUMBER(D59)),ABS(D59-E59)&gt;$O$3,AND($O$11=1,B59&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D59),D59&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I59">
-        <f>IF(H59=1,NA(),D59)</f>
-        <v/>
-      </c>
-      <c r="J59">
-        <f>IF(AND(ISNUMBER(D59),D59&gt;=$O$4,OR($O$11=0,B59&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K59">
-        <f>B59-$O$14</f>
+        <f>B59-$O$8</f>
         <v/>
       </c>
     </row>
@@ -3584,31 +3069,23 @@
         <v>48.88</v>
       </c>
       <c r="E60">
-        <f>MEDIAN(D40:D80)</f>
+        <f>IFERROR(MEDIAN(D40:D80),D60)</f>
         <v/>
       </c>
       <c r="F60">
-        <f>E40</f>
+        <f>IF(OR(NOT(ISNUMBER(D60)),ABS(D60-E60)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G60">
-        <f>F60-E60</f>
+        <f>IF(F60=1,NA(),D60)</f>
         <v/>
       </c>
       <c r="H60">
-        <f>IF(OR(NOT(ISNUMBER(D60)),ABS(D60-E60)&gt;$O$3,AND($O$11=1,B60&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D60),D60&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I60">
-        <f>IF(H60=1,NA(),D60)</f>
-        <v/>
-      </c>
-      <c r="J60">
-        <f>IF(AND(ISNUMBER(D60),D60&gt;=$O$4,OR($O$11=0,B60&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K60">
-        <f>B60-$O$14</f>
+        <f>B60-$O$8</f>
         <v/>
       </c>
     </row>
@@ -3628,31 +3105,23 @@
         <v>98.88</v>
       </c>
       <c r="E61">
-        <f>MEDIAN(D41:D81)</f>
+        <f>IFERROR(MEDIAN(D41:D81),D61)</f>
         <v/>
       </c>
       <c r="F61">
-        <f>E41</f>
+        <f>IF(OR(NOT(ISNUMBER(D61)),ABS(D61-E61)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G61">
-        <f>F61-E61</f>
+        <f>IF(F61=1,NA(),D61)</f>
         <v/>
       </c>
       <c r="H61">
-        <f>IF(OR(NOT(ISNUMBER(D61)),ABS(D61-E61)&gt;$O$3,AND($O$11=1,B61&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D61),D61&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I61">
-        <f>IF(H61=1,NA(),D61)</f>
-        <v/>
-      </c>
-      <c r="J61">
-        <f>IF(AND(ISNUMBER(D61),D61&gt;=$O$4,OR($O$11=0,B61&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K61">
-        <f>B61-$O$14</f>
+        <f>B61-$O$8</f>
         <v/>
       </c>
     </row>
@@ -3672,31 +3141,23 @@
         <v>50.88</v>
       </c>
       <c r="E62">
-        <f>MEDIAN(D42:D82)</f>
+        <f>IFERROR(MEDIAN(D42:D82),D62)</f>
         <v/>
       </c>
       <c r="F62">
-        <f>E42</f>
+        <f>IF(OR(NOT(ISNUMBER(D62)),ABS(D62-E62)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G62">
-        <f>F62-E62</f>
+        <f>IF(F62=1,NA(),D62)</f>
         <v/>
       </c>
       <c r="H62">
-        <f>IF(OR(NOT(ISNUMBER(D62)),ABS(D62-E62)&gt;$O$3,AND($O$11=1,B62&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D62),D62&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I62">
-        <f>IF(H62=1,NA(),D62)</f>
-        <v/>
-      </c>
-      <c r="J62">
-        <f>IF(AND(ISNUMBER(D62),D62&gt;=$O$4,OR($O$11=0,B62&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K62">
-        <f>B62-$O$14</f>
+        <f>B62-$O$8</f>
         <v/>
       </c>
     </row>
@@ -3716,31 +3177,23 @@
         <v>52.88</v>
       </c>
       <c r="E63">
-        <f>MEDIAN(D43:D83)</f>
+        <f>IFERROR(MEDIAN(D43:D83),D63)</f>
         <v/>
       </c>
       <c r="F63">
-        <f>E43</f>
+        <f>IF(OR(NOT(ISNUMBER(D63)),ABS(D63-E63)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G63">
-        <f>F63-E63</f>
+        <f>IF(F63=1,NA(),D63)</f>
         <v/>
       </c>
       <c r="H63">
-        <f>IF(OR(NOT(ISNUMBER(D63)),ABS(D63-E63)&gt;$O$3,AND($O$11=1,B63&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D63),D63&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I63">
-        <f>IF(H63=1,NA(),D63)</f>
-        <v/>
-      </c>
-      <c r="J63">
-        <f>IF(AND(ISNUMBER(D63),D63&gt;=$O$4,OR($O$11=0,B63&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K63">
-        <f>B63-$O$14</f>
+        <f>B63-$O$8</f>
         <v/>
       </c>
     </row>
@@ -3757,31 +3210,23 @@
         </is>
       </c>
       <c r="E64">
-        <f>MEDIAN(D44:D84)</f>
+        <f>IFERROR(MEDIAN(D44:D84),D64)</f>
         <v/>
       </c>
       <c r="F64">
-        <f>E44</f>
+        <f>IF(OR(NOT(ISNUMBER(D64)),ABS(D64-E64)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G64">
-        <f>F64-E64</f>
+        <f>IF(F64=1,NA(),D64)</f>
         <v/>
       </c>
       <c r="H64">
-        <f>IF(OR(NOT(ISNUMBER(D64)),ABS(D64-E64)&gt;$O$3,AND($O$11=1,B64&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D64),D64&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I64">
-        <f>IF(H64=1,NA(),D64)</f>
-        <v/>
-      </c>
-      <c r="J64">
-        <f>IF(AND(ISNUMBER(D64),D64&gt;=$O$4,OR($O$11=0,B64&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K64">
-        <f>B64-$O$14</f>
+        <f>B64-$O$8</f>
         <v/>
       </c>
     </row>
@@ -3801,31 +3246,23 @@
         <v>53.88</v>
       </c>
       <c r="E65">
-        <f>MEDIAN(D45:D85)</f>
+        <f>IFERROR(MEDIAN(D45:D85),D65)</f>
         <v/>
       </c>
       <c r="F65">
-        <f>E45</f>
+        <f>IF(OR(NOT(ISNUMBER(D65)),ABS(D65-E65)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G65">
-        <f>F65-E65</f>
+        <f>IF(F65=1,NA(),D65)</f>
         <v/>
       </c>
       <c r="H65">
-        <f>IF(OR(NOT(ISNUMBER(D65)),ABS(D65-E65)&gt;$O$3,AND($O$11=1,B65&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D65),D65&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I65">
-        <f>IF(H65=1,NA(),D65)</f>
-        <v/>
-      </c>
-      <c r="J65">
-        <f>IF(AND(ISNUMBER(D65),D65&gt;=$O$4,OR($O$11=0,B65&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K65">
-        <f>B65-$O$14</f>
+        <f>B65-$O$8</f>
         <v/>
       </c>
     </row>
@@ -3845,31 +3282,23 @@
         <v>59.88</v>
       </c>
       <c r="E66">
-        <f>MEDIAN(D46:D86)</f>
+        <f>IFERROR(MEDIAN(D46:D86),D66)</f>
         <v/>
       </c>
       <c r="F66">
-        <f>E46</f>
+        <f>IF(OR(NOT(ISNUMBER(D66)),ABS(D66-E66)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G66">
-        <f>F66-E66</f>
+        <f>IF(F66=1,NA(),D66)</f>
         <v/>
       </c>
       <c r="H66">
-        <f>IF(OR(NOT(ISNUMBER(D66)),ABS(D66-E66)&gt;$O$3,AND($O$11=1,B66&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D66),D66&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I66">
-        <f>IF(H66=1,NA(),D66)</f>
-        <v/>
-      </c>
-      <c r="J66">
-        <f>IF(AND(ISNUMBER(D66),D66&gt;=$O$4,OR($O$11=0,B66&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K66">
-        <f>B66-$O$14</f>
+        <f>B66-$O$8</f>
         <v/>
       </c>
     </row>
@@ -3889,31 +3318,23 @@
         <v>55.88</v>
       </c>
       <c r="E67">
-        <f>MEDIAN(D47:D87)</f>
+        <f>IFERROR(MEDIAN(D47:D87),D67)</f>
         <v/>
       </c>
       <c r="F67">
-        <f>E47</f>
+        <f>IF(OR(NOT(ISNUMBER(D67)),ABS(D67-E67)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G67">
-        <f>F67-E67</f>
+        <f>IF(F67=1,NA(),D67)</f>
         <v/>
       </c>
       <c r="H67">
-        <f>IF(OR(NOT(ISNUMBER(D67)),ABS(D67-E67)&gt;$O$3,AND($O$11=1,B67&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D67),D67&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I67">
-        <f>IF(H67=1,NA(),D67)</f>
-        <v/>
-      </c>
-      <c r="J67">
-        <f>IF(AND(ISNUMBER(D67),D67&gt;=$O$4,OR($O$11=0,B67&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K67">
-        <f>B67-$O$14</f>
+        <f>B67-$O$8</f>
         <v/>
       </c>
     </row>
@@ -3933,31 +3354,23 @@
         <v>56.89</v>
       </c>
       <c r="E68">
-        <f>MEDIAN(D48:D88)</f>
+        <f>IFERROR(MEDIAN(D48:D88),D68)</f>
         <v/>
       </c>
       <c r="F68">
-        <f>E48</f>
+        <f>IF(OR(NOT(ISNUMBER(D68)),ABS(D68-E68)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G68">
-        <f>F68-E68</f>
+        <f>IF(F68=1,NA(),D68)</f>
         <v/>
       </c>
       <c r="H68">
-        <f>IF(OR(NOT(ISNUMBER(D68)),ABS(D68-E68)&gt;$O$3,AND($O$11=1,B68&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D68),D68&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I68">
-        <f>IF(H68=1,NA(),D68)</f>
-        <v/>
-      </c>
-      <c r="J68">
-        <f>IF(AND(ISNUMBER(D68),D68&gt;=$O$4,OR($O$11=0,B68&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K68">
-        <f>B68-$O$14</f>
+        <f>B68-$O$8</f>
         <v/>
       </c>
     </row>
@@ -3977,31 +3390,23 @@
         <v>56.89</v>
       </c>
       <c r="E69">
-        <f>MEDIAN(D49:D89)</f>
+        <f>IFERROR(MEDIAN(D49:D89),D69)</f>
         <v/>
       </c>
       <c r="F69">
-        <f>E49</f>
+        <f>IF(OR(NOT(ISNUMBER(D69)),ABS(D69-E69)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G69">
-        <f>F69-E69</f>
+        <f>IF(F69=1,NA(),D69)</f>
         <v/>
       </c>
       <c r="H69">
-        <f>IF(OR(NOT(ISNUMBER(D69)),ABS(D69-E69)&gt;$O$3,AND($O$11=1,B69&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D69),D69&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I69">
-        <f>IF(H69=1,NA(),D69)</f>
-        <v/>
-      </c>
-      <c r="J69">
-        <f>IF(AND(ISNUMBER(D69),D69&gt;=$O$4,OR($O$11=0,B69&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K69">
-        <f>B69-$O$14</f>
+        <f>B69-$O$8</f>
         <v/>
       </c>
     </row>
@@ -4021,31 +3426,23 @@
         <v>58.81</v>
       </c>
       <c r="E70">
-        <f>MEDIAN(D50:D90)</f>
+        <f>IFERROR(MEDIAN(D50:D90),D70)</f>
         <v/>
       </c>
       <c r="F70">
-        <f>E50</f>
+        <f>IF(OR(NOT(ISNUMBER(D70)),ABS(D70-E70)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G70">
-        <f>F70-E70</f>
+        <f>IF(F70=1,NA(),D70)</f>
         <v/>
       </c>
       <c r="H70">
-        <f>IF(OR(NOT(ISNUMBER(D70)),ABS(D70-E70)&gt;$O$3,AND($O$11=1,B70&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D70),D70&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I70">
-        <f>IF(H70=1,NA(),D70)</f>
-        <v/>
-      </c>
-      <c r="J70">
-        <f>IF(AND(ISNUMBER(D70),D70&gt;=$O$4,OR($O$11=0,B70&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K70">
-        <f>B70-$O$14</f>
+        <f>B70-$O$8</f>
         <v/>
       </c>
     </row>
@@ -4065,31 +3462,23 @@
         <v>58.99</v>
       </c>
       <c r="E71">
-        <f>MEDIAN(D51:D91)</f>
+        <f>IFERROR(MEDIAN(D51:D91),D71)</f>
         <v/>
       </c>
       <c r="F71">
-        <f>E51</f>
+        <f>IF(OR(NOT(ISNUMBER(D71)),ABS(D71-E71)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G71">
-        <f>F71-E71</f>
+        <f>IF(F71=1,NA(),D71)</f>
         <v/>
       </c>
       <c r="H71">
-        <f>IF(OR(NOT(ISNUMBER(D71)),ABS(D71-E71)&gt;$O$3,AND($O$11=1,B71&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D71),D71&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I71">
-        <f>IF(H71=1,NA(),D71)</f>
-        <v/>
-      </c>
-      <c r="J71">
-        <f>IF(AND(ISNUMBER(D71),D71&gt;=$O$4,OR($O$11=0,B71&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K71">
-        <f>B71-$O$14</f>
+        <f>B71-$O$8</f>
         <v/>
       </c>
     </row>
@@ -4109,31 +3498,23 @@
         <v>58.89</v>
       </c>
       <c r="E72">
-        <f>MEDIAN(D52:D92)</f>
+        <f>IFERROR(MEDIAN(D52:D92),D72)</f>
         <v/>
       </c>
       <c r="F72">
-        <f>E52</f>
+        <f>IF(OR(NOT(ISNUMBER(D72)),ABS(D72-E72)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G72">
-        <f>F72-E72</f>
+        <f>IF(F72=1,NA(),D72)</f>
         <v/>
       </c>
       <c r="H72">
-        <f>IF(OR(NOT(ISNUMBER(D72)),ABS(D72-E72)&gt;$O$3,AND($O$11=1,B72&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D72),D72&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I72">
-        <f>IF(H72=1,NA(),D72)</f>
-        <v/>
-      </c>
-      <c r="J72">
-        <f>IF(AND(ISNUMBER(D72),D72&gt;=$O$4,OR($O$11=0,B72&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K72">
-        <f>B72-$O$14</f>
+        <f>B72-$O$8</f>
         <v/>
       </c>
     </row>
@@ -4153,31 +3534,23 @@
         <v>58.83</v>
       </c>
       <c r="E73">
-        <f>MEDIAN(D53:D93)</f>
+        <f>IFERROR(MEDIAN(D53:D93),D73)</f>
         <v/>
       </c>
       <c r="F73">
-        <f>E53</f>
+        <f>IF(OR(NOT(ISNUMBER(D73)),ABS(D73-E73)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G73">
-        <f>F73-E73</f>
+        <f>IF(F73=1,NA(),D73)</f>
         <v/>
       </c>
       <c r="H73">
-        <f>IF(OR(NOT(ISNUMBER(D73)),ABS(D73-E73)&gt;$O$3,AND($O$11=1,B73&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D73),D73&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I73">
-        <f>IF(H73=1,NA(),D73)</f>
-        <v/>
-      </c>
-      <c r="J73">
-        <f>IF(AND(ISNUMBER(D73),D73&gt;=$O$4,OR($O$11=0,B73&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K73">
-        <f>B73-$O$14</f>
+        <f>B73-$O$8</f>
         <v/>
       </c>
     </row>
@@ -4197,31 +3570,23 @@
         <v>54.93</v>
       </c>
       <c r="E74">
-        <f>MEDIAN(D54:D94)</f>
+        <f>IFERROR(MEDIAN(D54:D94),D74)</f>
         <v/>
       </c>
       <c r="F74">
-        <f>E54</f>
+        <f>IF(OR(NOT(ISNUMBER(D74)),ABS(D74-E74)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G74">
-        <f>F74-E74</f>
+        <f>IF(F74=1,NA(),D74)</f>
         <v/>
       </c>
       <c r="H74">
-        <f>IF(OR(NOT(ISNUMBER(D74)),ABS(D74-E74)&gt;$O$3,AND($O$11=1,B74&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D74),D74&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I74">
-        <f>IF(H74=1,NA(),D74)</f>
-        <v/>
-      </c>
-      <c r="J74">
-        <f>IF(AND(ISNUMBER(D74),D74&gt;=$O$4,OR($O$11=0,B74&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K74">
-        <f>B74-$O$14</f>
+        <f>B74-$O$8</f>
         <v/>
       </c>
     </row>
@@ -4241,31 +3606,23 @@
         <v>68.43000000000001</v>
       </c>
       <c r="E75">
-        <f>MEDIAN(D55:D95)</f>
+        <f>IFERROR(MEDIAN(D55:D95),D75)</f>
         <v/>
       </c>
       <c r="F75">
-        <f>E55</f>
+        <f>IF(OR(NOT(ISNUMBER(D75)),ABS(D75-E75)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G75">
-        <f>F75-E75</f>
+        <f>IF(F75=1,NA(),D75)</f>
         <v/>
       </c>
       <c r="H75">
-        <f>IF(OR(NOT(ISNUMBER(D75)),ABS(D75-E75)&gt;$O$3,AND($O$11=1,B75&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D75),D75&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I75">
-        <f>IF(H75=1,NA(),D75)</f>
-        <v/>
-      </c>
-      <c r="J75">
-        <f>IF(AND(ISNUMBER(D75),D75&gt;=$O$4,OR($O$11=0,B75&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K75">
-        <f>B75-$O$14</f>
+        <f>B75-$O$8</f>
         <v/>
       </c>
     </row>
@@ -4285,31 +3642,23 @@
         <v>60.83</v>
       </c>
       <c r="E76">
-        <f>MEDIAN(D56:D96)</f>
+        <f>IFERROR(MEDIAN(D56:D96),D76)</f>
         <v/>
       </c>
       <c r="F76">
-        <f>E56</f>
+        <f>IF(OR(NOT(ISNUMBER(D76)),ABS(D76-E76)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G76">
-        <f>F76-E76</f>
+        <f>IF(F76=1,NA(),D76)</f>
         <v/>
       </c>
       <c r="H76">
-        <f>IF(OR(NOT(ISNUMBER(D76)),ABS(D76-E76)&gt;$O$3,AND($O$11=1,B76&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D76),D76&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I76">
-        <f>IF(H76=1,NA(),D76)</f>
-        <v/>
-      </c>
-      <c r="J76">
-        <f>IF(AND(ISNUMBER(D76),D76&gt;=$O$4,OR($O$11=0,B76&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K76">
-        <f>B76-$O$14</f>
+        <f>B76-$O$8</f>
         <v/>
       </c>
     </row>
@@ -4329,31 +3678,23 @@
         <v>60.88</v>
       </c>
       <c r="E77">
-        <f>MEDIAN(D57:D97)</f>
+        <f>IFERROR(MEDIAN(D57:D97),D77)</f>
         <v/>
       </c>
       <c r="F77">
-        <f>E57</f>
+        <f>IF(OR(NOT(ISNUMBER(D77)),ABS(D77-E77)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G77">
-        <f>F77-E77</f>
+        <f>IF(F77=1,NA(),D77)</f>
         <v/>
       </c>
       <c r="H77">
-        <f>IF(OR(NOT(ISNUMBER(D77)),ABS(D77-E77)&gt;$O$3,AND($O$11=1,B77&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D77),D77&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I77">
-        <f>IF(H77=1,NA(),D77)</f>
-        <v/>
-      </c>
-      <c r="J77">
-        <f>IF(AND(ISNUMBER(D77),D77&gt;=$O$4,OR($O$11=0,B77&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K77">
-        <f>B77-$O$14</f>
+        <f>B77-$O$8</f>
         <v/>
       </c>
     </row>
@@ -4373,31 +3714,23 @@
         <v>61.48</v>
       </c>
       <c r="E78">
-        <f>MEDIAN(D58:D98)</f>
+        <f>IFERROR(MEDIAN(D58:D98),D78)</f>
         <v/>
       </c>
       <c r="F78">
-        <f>E58</f>
+        <f>IF(OR(NOT(ISNUMBER(D78)),ABS(D78-E78)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G78">
-        <f>F78-E78</f>
+        <f>IF(F78=1,NA(),D78)</f>
         <v/>
       </c>
       <c r="H78">
-        <f>IF(OR(NOT(ISNUMBER(D78)),ABS(D78-E78)&gt;$O$3,AND($O$11=1,B78&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D78),D78&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I78">
-        <f>IF(H78=1,NA(),D78)</f>
-        <v/>
-      </c>
-      <c r="J78">
-        <f>IF(AND(ISNUMBER(D78),D78&gt;=$O$4,OR($O$11=0,B78&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K78">
-        <f>B78-$O$14</f>
+        <f>B78-$O$8</f>
         <v/>
       </c>
     </row>
@@ -4417,31 +3750,23 @@
         <v>61.88</v>
       </c>
       <c r="E79">
-        <f>MEDIAN(D59:D99)</f>
+        <f>IFERROR(MEDIAN(D59:D99),D79)</f>
         <v/>
       </c>
       <c r="F79">
-        <f>E59</f>
+        <f>IF(OR(NOT(ISNUMBER(D79)),ABS(D79-E79)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G79">
-        <f>F79-E79</f>
+        <f>IF(F79=1,NA(),D79)</f>
         <v/>
       </c>
       <c r="H79">
-        <f>IF(OR(NOT(ISNUMBER(D79)),ABS(D79-E79)&gt;$O$3,AND($O$11=1,B79&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D79),D79&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I79">
-        <f>IF(H79=1,NA(),D79)</f>
-        <v/>
-      </c>
-      <c r="J79">
-        <f>IF(AND(ISNUMBER(D79),D79&gt;=$O$4,OR($O$11=0,B79&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K79">
-        <f>B79-$O$14</f>
+        <f>B79-$O$8</f>
         <v/>
       </c>
     </row>
@@ -4461,31 +3786,23 @@
         <v>61.89</v>
       </c>
       <c r="E80">
-        <f>MEDIAN(D60:D100)</f>
+        <f>IFERROR(MEDIAN(D60:D100),D80)</f>
         <v/>
       </c>
       <c r="F80">
-        <f>E60</f>
+        <f>IF(OR(NOT(ISNUMBER(D80)),ABS(D80-E80)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G80">
-        <f>F80-E80</f>
+        <f>IF(F80=1,NA(),D80)</f>
         <v/>
       </c>
       <c r="H80">
-        <f>IF(OR(NOT(ISNUMBER(D80)),ABS(D80-E80)&gt;$O$3,AND($O$11=1,B80&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D80),D80&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I80">
-        <f>IF(H80=1,NA(),D80)</f>
-        <v/>
-      </c>
-      <c r="J80">
-        <f>IF(AND(ISNUMBER(D80),D80&gt;=$O$4,OR($O$11=0,B80&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K80">
-        <f>B80-$O$14</f>
+        <f>B80-$O$8</f>
         <v/>
       </c>
     </row>
@@ -4505,31 +3822,23 @@
         <v>61.88</v>
       </c>
       <c r="E81">
-        <f>MEDIAN(D61:D101)</f>
+        <f>IFERROR(MEDIAN(D61:D101),D81)</f>
         <v/>
       </c>
       <c r="F81">
-        <f>E61</f>
+        <f>IF(OR(NOT(ISNUMBER(D81)),ABS(D81-E81)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G81">
-        <f>F81-E81</f>
+        <f>IF(F81=1,NA(),D81)</f>
         <v/>
       </c>
       <c r="H81">
-        <f>IF(OR(NOT(ISNUMBER(D81)),ABS(D81-E81)&gt;$O$3,AND($O$11=1,B81&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D81),D81&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I81">
-        <f>IF(H81=1,NA(),D81)</f>
-        <v/>
-      </c>
-      <c r="J81">
-        <f>IF(AND(ISNUMBER(D81),D81&gt;=$O$4,OR($O$11=0,B81&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K81">
-        <f>B81-$O$14</f>
+        <f>B81-$O$8</f>
         <v/>
       </c>
     </row>
@@ -4549,31 +3858,23 @@
         <v>62.88</v>
       </c>
       <c r="E82">
-        <f>MEDIAN(D62:D102)</f>
+        <f>IFERROR(MEDIAN(D62:D102),D82)</f>
         <v/>
       </c>
       <c r="F82">
-        <f>E62</f>
+        <f>IF(OR(NOT(ISNUMBER(D82)),ABS(D82-E82)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G82">
-        <f>F82-E82</f>
+        <f>IF(F82=1,NA(),D82)</f>
         <v/>
       </c>
       <c r="H82">
-        <f>IF(OR(NOT(ISNUMBER(D82)),ABS(D82-E82)&gt;$O$3,AND($O$11=1,B82&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D82),D82&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I82">
-        <f>IF(H82=1,NA(),D82)</f>
-        <v/>
-      </c>
-      <c r="J82">
-        <f>IF(AND(ISNUMBER(D82),D82&gt;=$O$4,OR($O$11=0,B82&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K82">
-        <f>B82-$O$14</f>
+        <f>B82-$O$8</f>
         <v/>
       </c>
     </row>
@@ -4593,31 +3894,23 @@
         <v>62.85</v>
       </c>
       <c r="E83">
-        <f>MEDIAN(D63:D103)</f>
+        <f>IFERROR(MEDIAN(D63:D103),D83)</f>
         <v/>
       </c>
       <c r="F83">
-        <f>E63</f>
+        <f>IF(OR(NOT(ISNUMBER(D83)),ABS(D83-E83)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G83">
-        <f>F83-E83</f>
+        <f>IF(F83=1,NA(),D83)</f>
         <v/>
       </c>
       <c r="H83">
-        <f>IF(OR(NOT(ISNUMBER(D83)),ABS(D83-E83)&gt;$O$3,AND($O$11=1,B83&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D83),D83&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I83">
-        <f>IF(H83=1,NA(),D83)</f>
-        <v/>
-      </c>
-      <c r="J83">
-        <f>IF(AND(ISNUMBER(D83),D83&gt;=$O$4,OR($O$11=0,B83&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K83">
-        <f>B83-$O$14</f>
+        <f>B83-$O$8</f>
         <v/>
       </c>
     </row>
@@ -4637,31 +3930,23 @@
         <v>62.86</v>
       </c>
       <c r="E84">
-        <f>MEDIAN(D64:D104)</f>
+        <f>IFERROR(MEDIAN(D64:D104),D84)</f>
         <v/>
       </c>
       <c r="F84">
-        <f>E64</f>
+        <f>IF(OR(NOT(ISNUMBER(D84)),ABS(D84-E84)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G84">
-        <f>F84-E84</f>
+        <f>IF(F84=1,NA(),D84)</f>
         <v/>
       </c>
       <c r="H84">
-        <f>IF(OR(NOT(ISNUMBER(D84)),ABS(D84-E84)&gt;$O$3,AND($O$11=1,B84&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D84),D84&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I84">
-        <f>IF(H84=1,NA(),D84)</f>
-        <v/>
-      </c>
-      <c r="J84">
-        <f>IF(AND(ISNUMBER(D84),D84&gt;=$O$4,OR($O$11=0,B84&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K84">
-        <f>B84-$O$14</f>
+        <f>B84-$O$8</f>
         <v/>
       </c>
     </row>
@@ -4681,31 +3966,23 @@
         <v>62.88</v>
       </c>
       <c r="E85">
-        <f>MEDIAN(D65:D105)</f>
+        <f>IFERROR(MEDIAN(D65:D105),D85)</f>
         <v/>
       </c>
       <c r="F85">
-        <f>E65</f>
+        <f>IF(OR(NOT(ISNUMBER(D85)),ABS(D85-E85)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G85">
-        <f>F85-E85</f>
+        <f>IF(F85=1,NA(),D85)</f>
         <v/>
       </c>
       <c r="H85">
-        <f>IF(OR(NOT(ISNUMBER(D85)),ABS(D85-E85)&gt;$O$3,AND($O$11=1,B85&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D85),D85&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I85">
-        <f>IF(H85=1,NA(),D85)</f>
-        <v/>
-      </c>
-      <c r="J85">
-        <f>IF(AND(ISNUMBER(D85),D85&gt;=$O$4,OR($O$11=0,B85&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K85">
-        <f>B85-$O$14</f>
+        <f>B85-$O$8</f>
         <v/>
       </c>
     </row>
@@ -4725,31 +4002,23 @@
         <v>62.07</v>
       </c>
       <c r="E86">
-        <f>MEDIAN(D66:D106)</f>
+        <f>IFERROR(MEDIAN(D66:D106),D86)</f>
         <v/>
       </c>
       <c r="F86">
-        <f>E66</f>
+        <f>IF(OR(NOT(ISNUMBER(D86)),ABS(D86-E86)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G86">
-        <f>F86-E86</f>
+        <f>IF(F86=1,NA(),D86)</f>
         <v/>
       </c>
       <c r="H86">
-        <f>IF(OR(NOT(ISNUMBER(D86)),ABS(D86-E86)&gt;$O$3,AND($O$11=1,B86&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D86),D86&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I86">
-        <f>IF(H86=1,NA(),D86)</f>
-        <v/>
-      </c>
-      <c r="J86">
-        <f>IF(AND(ISNUMBER(D86),D86&gt;=$O$4,OR($O$11=0,B86&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K86">
-        <f>B86-$O$14</f>
+        <f>B86-$O$8</f>
         <v/>
       </c>
     </row>
@@ -4769,31 +4038,23 @@
         <v>62.88</v>
       </c>
       <c r="E87">
-        <f>MEDIAN(D67:D107)</f>
+        <f>IFERROR(MEDIAN(D67:D107),D87)</f>
         <v/>
       </c>
       <c r="F87">
-        <f>E67</f>
+        <f>IF(OR(NOT(ISNUMBER(D87)),ABS(D87-E87)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G87">
-        <f>F87-E87</f>
+        <f>IF(F87=1,NA(),D87)</f>
         <v/>
       </c>
       <c r="H87">
-        <f>IF(OR(NOT(ISNUMBER(D87)),ABS(D87-E87)&gt;$O$3,AND($O$11=1,B87&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D87),D87&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I87">
-        <f>IF(H87=1,NA(),D87)</f>
-        <v/>
-      </c>
-      <c r="J87">
-        <f>IF(AND(ISNUMBER(D87),D87&gt;=$O$4,OR($O$11=0,B87&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K87">
-        <f>B87-$O$14</f>
+        <f>B87-$O$8</f>
         <v/>
       </c>
     </row>
@@ -4813,31 +4074,23 @@
         <v>621.1799999999999</v>
       </c>
       <c r="E88">
-        <f>MEDIAN(D68:D108)</f>
+        <f>IFERROR(MEDIAN(D68:D108),D88)</f>
         <v/>
       </c>
       <c r="F88">
-        <f>E68</f>
+        <f>IF(OR(NOT(ISNUMBER(D88)),ABS(D88-E88)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G88">
-        <f>F88-E88</f>
+        <f>IF(F88=1,NA(),D88)</f>
         <v/>
       </c>
       <c r="H88">
-        <f>IF(OR(NOT(ISNUMBER(D88)),ABS(D88-E88)&gt;$O$3,AND($O$11=1,B88&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D88),D88&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I88">
-        <f>IF(H88=1,NA(),D88)</f>
-        <v/>
-      </c>
-      <c r="J88">
-        <f>IF(AND(ISNUMBER(D88),D88&gt;=$O$4,OR($O$11=0,B88&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K88">
-        <f>B88-$O$14</f>
+        <f>B88-$O$8</f>
         <v/>
       </c>
     </row>
@@ -4857,31 +4110,23 @@
         <v>621.11</v>
       </c>
       <c r="E89">
-        <f>MEDIAN(D69:D109)</f>
+        <f>IFERROR(MEDIAN(D69:D109),D89)</f>
         <v/>
       </c>
       <c r="F89">
-        <f>E69</f>
+        <f>IF(OR(NOT(ISNUMBER(D89)),ABS(D89-E89)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G89">
-        <f>F89-E89</f>
+        <f>IF(F89=1,NA(),D89)</f>
         <v/>
       </c>
       <c r="H89">
-        <f>IF(OR(NOT(ISNUMBER(D89)),ABS(D89-E89)&gt;$O$3,AND($O$11=1,B89&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D89),D89&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I89">
-        <f>IF(H89=1,NA(),D89)</f>
-        <v/>
-      </c>
-      <c r="J89">
-        <f>IF(AND(ISNUMBER(D89),D89&gt;=$O$4,OR($O$11=0,B89&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K89">
-        <f>B89-$O$14</f>
+        <f>B89-$O$8</f>
         <v/>
       </c>
     </row>
@@ -4901,31 +4146,23 @@
         <v>62.17</v>
       </c>
       <c r="E90">
-        <f>MEDIAN(D70:D110)</f>
+        <f>IFERROR(MEDIAN(D70:D110),D90)</f>
         <v/>
       </c>
       <c r="F90">
-        <f>E70</f>
+        <f>IF(OR(NOT(ISNUMBER(D90)),ABS(D90-E90)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G90">
-        <f>F90-E90</f>
+        <f>IF(F90=1,NA(),D90)</f>
         <v/>
       </c>
       <c r="H90">
-        <f>IF(OR(NOT(ISNUMBER(D90)),ABS(D90-E90)&gt;$O$3,AND($O$11=1,B90&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D90),D90&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I90">
-        <f>IF(H90=1,NA(),D90)</f>
-        <v/>
-      </c>
-      <c r="J90">
-        <f>IF(AND(ISNUMBER(D90),D90&gt;=$O$4,OR($O$11=0,B90&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K90">
-        <f>B90-$O$14</f>
+        <f>B90-$O$8</f>
         <v/>
       </c>
     </row>
@@ -4945,31 +4182,23 @@
         <v>62.17</v>
       </c>
       <c r="E91">
-        <f>MEDIAN(D71:D111)</f>
+        <f>IFERROR(MEDIAN(D71:D111),D91)</f>
         <v/>
       </c>
       <c r="F91">
-        <f>E71</f>
+        <f>IF(OR(NOT(ISNUMBER(D91)),ABS(D91-E91)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G91">
-        <f>F91-E91</f>
+        <f>IF(F91=1,NA(),D91)</f>
         <v/>
       </c>
       <c r="H91">
-        <f>IF(OR(NOT(ISNUMBER(D91)),ABS(D91-E91)&gt;$O$3,AND($O$11=1,B91&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D91),D91&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I91">
-        <f>IF(H91=1,NA(),D91)</f>
-        <v/>
-      </c>
-      <c r="J91">
-        <f>IF(AND(ISNUMBER(D91),D91&gt;=$O$4,OR($O$11=0,B91&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K91">
-        <f>B91-$O$14</f>
+        <f>B91-$O$8</f>
         <v/>
       </c>
     </row>
@@ -4989,31 +4218,23 @@
         <v>62.17</v>
       </c>
       <c r="E92">
-        <f>MEDIAN(D72:D112)</f>
+        <f>IFERROR(MEDIAN(D72:D112),D92)</f>
         <v/>
       </c>
       <c r="F92">
-        <f>E72</f>
+        <f>IF(OR(NOT(ISNUMBER(D92)),ABS(D92-E92)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G92">
-        <f>F92-E92</f>
+        <f>IF(F92=1,NA(),D92)</f>
         <v/>
       </c>
       <c r="H92">
-        <f>IF(OR(NOT(ISNUMBER(D92)),ABS(D92-E92)&gt;$O$3,AND($O$11=1,B92&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D92),D92&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I92">
-        <f>IF(H92=1,NA(),D92)</f>
-        <v/>
-      </c>
-      <c r="J92">
-        <f>IF(AND(ISNUMBER(D92),D92&gt;=$O$4,OR($O$11=0,B92&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K92">
-        <f>B92-$O$14</f>
+        <f>B92-$O$8</f>
         <v/>
       </c>
     </row>
@@ -5033,31 +4254,23 @@
         <v>62.17</v>
       </c>
       <c r="E93">
-        <f>MEDIAN(D73:D113)</f>
+        <f>IFERROR(MEDIAN(D73:D113),D93)</f>
         <v/>
       </c>
       <c r="F93">
-        <f>E73</f>
+        <f>IF(OR(NOT(ISNUMBER(D93)),ABS(D93-E93)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G93">
-        <f>F93-E93</f>
+        <f>IF(F93=1,NA(),D93)</f>
         <v/>
       </c>
       <c r="H93">
-        <f>IF(OR(NOT(ISNUMBER(D93)),ABS(D93-E93)&gt;$O$3,AND($O$11=1,B93&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D93),D93&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I93">
-        <f>IF(H93=1,NA(),D93)</f>
-        <v/>
-      </c>
-      <c r="J93">
-        <f>IF(AND(ISNUMBER(D93),D93&gt;=$O$4,OR($O$11=0,B93&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K93">
-        <f>B93-$O$14</f>
+        <f>B93-$O$8</f>
         <v/>
       </c>
     </row>
@@ -5077,31 +4290,23 @@
         <v>62.17</v>
       </c>
       <c r="E94">
-        <f>MEDIAN(D74:D114)</f>
+        <f>IFERROR(MEDIAN(D74:D114),D94)</f>
         <v/>
       </c>
       <c r="F94">
-        <f>E74</f>
+        <f>IF(OR(NOT(ISNUMBER(D94)),ABS(D94-E94)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G94">
-        <f>F94-E94</f>
+        <f>IF(F94=1,NA(),D94)</f>
         <v/>
       </c>
       <c r="H94">
-        <f>IF(OR(NOT(ISNUMBER(D94)),ABS(D94-E94)&gt;$O$3,AND($O$11=1,B94&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D94),D94&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I94">
-        <f>IF(H94=1,NA(),D94)</f>
-        <v/>
-      </c>
-      <c r="J94">
-        <f>IF(AND(ISNUMBER(D94),D94&gt;=$O$4,OR($O$11=0,B94&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K94">
-        <f>B94-$O$14</f>
+        <f>B94-$O$8</f>
         <v/>
       </c>
     </row>
@@ -5121,31 +4326,23 @@
         <v>62.17</v>
       </c>
       <c r="E95">
-        <f>MEDIAN(D75:D115)</f>
+        <f>IFERROR(MEDIAN(D75:D115),D95)</f>
         <v/>
       </c>
       <c r="F95">
-        <f>E75</f>
+        <f>IF(OR(NOT(ISNUMBER(D95)),ABS(D95-E95)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G95">
-        <f>F95-E95</f>
+        <f>IF(F95=1,NA(),D95)</f>
         <v/>
       </c>
       <c r="H95">
-        <f>IF(OR(NOT(ISNUMBER(D95)),ABS(D95-E95)&gt;$O$3,AND($O$11=1,B95&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D95),D95&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I95">
-        <f>IF(H95=1,NA(),D95)</f>
-        <v/>
-      </c>
-      <c r="J95">
-        <f>IF(AND(ISNUMBER(D95),D95&gt;=$O$4,OR($O$11=0,B95&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K95">
-        <f>B95-$O$14</f>
+        <f>B95-$O$8</f>
         <v/>
       </c>
     </row>
@@ -5165,31 +4362,23 @@
         <v>62.17</v>
       </c>
       <c r="E96">
-        <f>MEDIAN(D76:D116)</f>
+        <f>IFERROR(MEDIAN(D76:D116),D96)</f>
         <v/>
       </c>
       <c r="F96">
-        <f>E76</f>
+        <f>IF(OR(NOT(ISNUMBER(D96)),ABS(D96-E96)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G96">
-        <f>F96-E96</f>
+        <f>IF(F96=1,NA(),D96)</f>
         <v/>
       </c>
       <c r="H96">
-        <f>IF(OR(NOT(ISNUMBER(D96)),ABS(D96-E96)&gt;$O$3,AND($O$11=1,B96&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D96),D96&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I96">
-        <f>IF(H96=1,NA(),D96)</f>
-        <v/>
-      </c>
-      <c r="J96">
-        <f>IF(AND(ISNUMBER(D96),D96&gt;=$O$4,OR($O$11=0,B96&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K96">
-        <f>B96-$O$14</f>
+        <f>B96-$O$8</f>
         <v/>
       </c>
     </row>
@@ -5209,31 +4398,23 @@
         <v>62.17</v>
       </c>
       <c r="E97">
-        <f>MEDIAN(D77:D116)</f>
+        <f>IFERROR(MEDIAN(D77:D116),D97)</f>
         <v/>
       </c>
       <c r="F97">
-        <f>E77</f>
+        <f>IF(OR(NOT(ISNUMBER(D97)),ABS(D97-E97)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G97">
-        <f>F97-E97</f>
+        <f>IF(F97=1,NA(),D97)</f>
         <v/>
       </c>
       <c r="H97">
-        <f>IF(OR(NOT(ISNUMBER(D97)),ABS(D97-E97)&gt;$O$3,AND($O$11=1,B97&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D97),D97&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I97">
-        <f>IF(H97=1,NA(),D97)</f>
-        <v/>
-      </c>
-      <c r="J97">
-        <f>IF(AND(ISNUMBER(D97),D97&gt;=$O$4,OR($O$11=0,B97&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K97">
-        <f>B97-$O$14</f>
+        <f>B97-$O$8</f>
         <v/>
       </c>
     </row>
@@ -5253,31 +4434,23 @@
         <v>62.17</v>
       </c>
       <c r="E98">
-        <f>MEDIAN(D78:D116)</f>
+        <f>IFERROR(MEDIAN(D78:D116),D98)</f>
         <v/>
       </c>
       <c r="F98">
-        <f>E78</f>
+        <f>IF(OR(NOT(ISNUMBER(D98)),ABS(D98-E98)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G98">
-        <f>F98-E98</f>
+        <f>IF(F98=1,NA(),D98)</f>
         <v/>
       </c>
       <c r="H98">
-        <f>IF(OR(NOT(ISNUMBER(D98)),ABS(D98-E98)&gt;$O$3,AND($O$11=1,B98&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D98),D98&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I98">
-        <f>IF(H98=1,NA(),D98)</f>
-        <v/>
-      </c>
-      <c r="J98">
-        <f>IF(AND(ISNUMBER(D98),D98&gt;=$O$4,OR($O$11=0,B98&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K98">
-        <f>B98-$O$14</f>
+        <f>B98-$O$8</f>
         <v/>
       </c>
     </row>
@@ -5297,31 +4470,23 @@
         <v>62.17</v>
       </c>
       <c r="E99">
-        <f>MEDIAN(D79:D116)</f>
+        <f>IFERROR(MEDIAN(D79:D116),D99)</f>
         <v/>
       </c>
       <c r="F99">
-        <f>E79</f>
+        <f>IF(OR(NOT(ISNUMBER(D99)),ABS(D99-E99)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G99">
-        <f>F99-E99</f>
+        <f>IF(F99=1,NA(),D99)</f>
         <v/>
       </c>
       <c r="H99">
-        <f>IF(OR(NOT(ISNUMBER(D99)),ABS(D99-E99)&gt;$O$3,AND($O$11=1,B99&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D99),D99&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I99">
-        <f>IF(H99=1,NA(),D99)</f>
-        <v/>
-      </c>
-      <c r="J99">
-        <f>IF(AND(ISNUMBER(D99),D99&gt;=$O$4,OR($O$11=0,B99&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K99">
-        <f>B99-$O$14</f>
+        <f>B99-$O$8</f>
         <v/>
       </c>
     </row>
@@ -5341,31 +4506,23 @@
         <v>62.17</v>
       </c>
       <c r="E100">
-        <f>MEDIAN(D80:D116)</f>
+        <f>IFERROR(MEDIAN(D80:D116),D100)</f>
         <v/>
       </c>
       <c r="F100">
-        <f>E80</f>
+        <f>IF(OR(NOT(ISNUMBER(D100)),ABS(D100-E100)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G100">
-        <f>F100-E100</f>
+        <f>IF(F100=1,NA(),D100)</f>
         <v/>
       </c>
       <c r="H100">
-        <f>IF(OR(NOT(ISNUMBER(D100)),ABS(D100-E100)&gt;$O$3,AND($O$11=1,B100&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D100),D100&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I100">
-        <f>IF(H100=1,NA(),D100)</f>
-        <v/>
-      </c>
-      <c r="J100">
-        <f>IF(AND(ISNUMBER(D100),D100&gt;=$O$4,OR($O$11=0,B100&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K100">
-        <f>B100-$O$14</f>
+        <f>B100-$O$8</f>
         <v/>
       </c>
     </row>
@@ -5385,31 +4542,23 @@
         <v>62.17</v>
       </c>
       <c r="E101">
-        <f>MEDIAN(D81:D116)</f>
+        <f>IFERROR(MEDIAN(D81:D116),D101)</f>
         <v/>
       </c>
       <c r="F101">
-        <f>E81</f>
+        <f>IF(OR(NOT(ISNUMBER(D101)),ABS(D101-E101)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G101">
-        <f>F101-E101</f>
+        <f>IF(F101=1,NA(),D101)</f>
         <v/>
       </c>
       <c r="H101">
-        <f>IF(OR(NOT(ISNUMBER(D101)),ABS(D101-E101)&gt;$O$3,AND($O$11=1,B101&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D101),D101&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I101">
-        <f>IF(H101=1,NA(),D101)</f>
-        <v/>
-      </c>
-      <c r="J101">
-        <f>IF(AND(ISNUMBER(D101),D101&gt;=$O$4,OR($O$11=0,B101&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K101">
-        <f>B101-$O$14</f>
+        <f>B101-$O$8</f>
         <v/>
       </c>
     </row>
@@ -5429,31 +4578,23 @@
         <v>62.17</v>
       </c>
       <c r="E102">
-        <f>MEDIAN(D82:D116)</f>
+        <f>IFERROR(MEDIAN(D82:D116),D102)</f>
         <v/>
       </c>
       <c r="F102">
-        <f>E82</f>
+        <f>IF(OR(NOT(ISNUMBER(D102)),ABS(D102-E102)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G102">
-        <f>F102-E102</f>
+        <f>IF(F102=1,NA(),D102)</f>
         <v/>
       </c>
       <c r="H102">
-        <f>IF(OR(NOT(ISNUMBER(D102)),ABS(D102-E102)&gt;$O$3,AND($O$11=1,B102&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D102),D102&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I102">
-        <f>IF(H102=1,NA(),D102)</f>
-        <v/>
-      </c>
-      <c r="J102">
-        <f>IF(AND(ISNUMBER(D102),D102&gt;=$O$4,OR($O$11=0,B102&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K102">
-        <f>B102-$O$14</f>
+        <f>B102-$O$8</f>
         <v/>
       </c>
     </row>
@@ -5473,31 +4614,23 @@
         <v>62.17</v>
       </c>
       <c r="E103">
-        <f>MEDIAN(D83:D116)</f>
+        <f>IFERROR(MEDIAN(D83:D116),D103)</f>
         <v/>
       </c>
       <c r="F103">
-        <f>E83</f>
+        <f>IF(OR(NOT(ISNUMBER(D103)),ABS(D103-E103)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G103">
-        <f>F103-E103</f>
+        <f>IF(F103=1,NA(),D103)</f>
         <v/>
       </c>
       <c r="H103">
-        <f>IF(OR(NOT(ISNUMBER(D103)),ABS(D103-E103)&gt;$O$3,AND($O$11=1,B103&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D103),D103&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I103">
-        <f>IF(H103=1,NA(),D103)</f>
-        <v/>
-      </c>
-      <c r="J103">
-        <f>IF(AND(ISNUMBER(D103),D103&gt;=$O$4,OR($O$11=0,B103&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K103">
-        <f>B103-$O$14</f>
+        <f>B103-$O$8</f>
         <v/>
       </c>
     </row>
@@ -5517,31 +4650,23 @@
         <v>62.18</v>
       </c>
       <c r="E104">
-        <f>MEDIAN(D84:D116)</f>
+        <f>IFERROR(MEDIAN(D84:D116),D104)</f>
         <v/>
       </c>
       <c r="F104">
-        <f>E84</f>
+        <f>IF(OR(NOT(ISNUMBER(D104)),ABS(D104-E104)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G104">
-        <f>F104-E104</f>
+        <f>IF(F104=1,NA(),D104)</f>
         <v/>
       </c>
       <c r="H104">
-        <f>IF(OR(NOT(ISNUMBER(D104)),ABS(D104-E104)&gt;$O$3,AND($O$11=1,B104&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D104),D104&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I104">
-        <f>IF(H104=1,NA(),D104)</f>
-        <v/>
-      </c>
-      <c r="J104">
-        <f>IF(AND(ISNUMBER(D104),D104&gt;=$O$4,OR($O$11=0,B104&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K104">
-        <f>B104-$O$14</f>
+        <f>B104-$O$8</f>
         <v/>
       </c>
     </row>
@@ -5561,31 +4686,23 @@
         <v>62.18</v>
       </c>
       <c r="E105">
-        <f>MEDIAN(D85:D116)</f>
+        <f>IFERROR(MEDIAN(D85:D116),D105)</f>
         <v/>
       </c>
       <c r="F105">
-        <f>E85</f>
+        <f>IF(OR(NOT(ISNUMBER(D105)),ABS(D105-E105)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G105">
-        <f>F105-E105</f>
+        <f>IF(F105=1,NA(),D105)</f>
         <v/>
       </c>
       <c r="H105">
-        <f>IF(OR(NOT(ISNUMBER(D105)),ABS(D105-E105)&gt;$O$3,AND($O$11=1,B105&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D105),D105&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I105">
-        <f>IF(H105=1,NA(),D105)</f>
-        <v/>
-      </c>
-      <c r="J105">
-        <f>IF(AND(ISNUMBER(D105),D105&gt;=$O$4,OR($O$11=0,B105&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K105">
-        <f>B105-$O$14</f>
+        <f>B105-$O$8</f>
         <v/>
       </c>
     </row>
@@ -5605,31 +4722,23 @@
         <v>62.18</v>
       </c>
       <c r="E106">
-        <f>MEDIAN(D86:D116)</f>
+        <f>IFERROR(MEDIAN(D86:D116),D106)</f>
         <v/>
       </c>
       <c r="F106">
-        <f>E86</f>
+        <f>IF(OR(NOT(ISNUMBER(D106)),ABS(D106-E106)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G106">
-        <f>F106-E106</f>
+        <f>IF(F106=1,NA(),D106)</f>
         <v/>
       </c>
       <c r="H106">
-        <f>IF(OR(NOT(ISNUMBER(D106)),ABS(D106-E106)&gt;$O$3,AND($O$11=1,B106&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D106),D106&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I106">
-        <f>IF(H106=1,NA(),D106)</f>
-        <v/>
-      </c>
-      <c r="J106">
-        <f>IF(AND(ISNUMBER(D106),D106&gt;=$O$4,OR($O$11=0,B106&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K106">
-        <f>B106-$O$14</f>
+        <f>B106-$O$8</f>
         <v/>
       </c>
     </row>
@@ -5649,31 +4758,23 @@
         <v>62.18</v>
       </c>
       <c r="E107">
-        <f>MEDIAN(D87:D116)</f>
+        <f>IFERROR(MEDIAN(D87:D116),D107)</f>
         <v/>
       </c>
       <c r="F107">
-        <f>E87</f>
+        <f>IF(OR(NOT(ISNUMBER(D107)),ABS(D107-E107)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G107">
-        <f>F107-E107</f>
+        <f>IF(F107=1,NA(),D107)</f>
         <v/>
       </c>
       <c r="H107">
-        <f>IF(OR(NOT(ISNUMBER(D107)),ABS(D107-E107)&gt;$O$3,AND($O$11=1,B107&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D107),D107&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I107">
-        <f>IF(H107=1,NA(),D107)</f>
-        <v/>
-      </c>
-      <c r="J107">
-        <f>IF(AND(ISNUMBER(D107),D107&gt;=$O$4,OR($O$11=0,B107&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K107">
-        <f>B107-$O$14</f>
+        <f>B107-$O$8</f>
         <v/>
       </c>
     </row>
@@ -5693,31 +4794,23 @@
         <v>62.18</v>
       </c>
       <c r="E108">
-        <f>MEDIAN(D88:D116)</f>
+        <f>IFERROR(MEDIAN(D88:D116),D108)</f>
         <v/>
       </c>
       <c r="F108">
-        <f>E88</f>
+        <f>IF(OR(NOT(ISNUMBER(D108)),ABS(D108-E108)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G108">
-        <f>F108-E108</f>
+        <f>IF(F108=1,NA(),D108)</f>
         <v/>
       </c>
       <c r="H108">
-        <f>IF(OR(NOT(ISNUMBER(D108)),ABS(D108-E108)&gt;$O$3,AND($O$11=1,B108&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D108),D108&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I108">
-        <f>IF(H108=1,NA(),D108)</f>
-        <v/>
-      </c>
-      <c r="J108">
-        <f>IF(AND(ISNUMBER(D108),D108&gt;=$O$4,OR($O$11=0,B108&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K108">
-        <f>B108-$O$14</f>
+        <f>B108-$O$8</f>
         <v/>
       </c>
     </row>
@@ -5737,31 +4830,23 @@
         <v>62.18</v>
       </c>
       <c r="E109">
-        <f>MEDIAN(D89:D116)</f>
+        <f>IFERROR(MEDIAN(D89:D116),D109)</f>
         <v/>
       </c>
       <c r="F109">
-        <f>E89</f>
+        <f>IF(OR(NOT(ISNUMBER(D109)),ABS(D109-E109)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G109">
-        <f>F109-E109</f>
+        <f>IF(F109=1,NA(),D109)</f>
         <v/>
       </c>
       <c r="H109">
-        <f>IF(OR(NOT(ISNUMBER(D109)),ABS(D109-E109)&gt;$O$3,AND($O$11=1,B109&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D109),D109&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I109">
-        <f>IF(H109=1,NA(),D109)</f>
-        <v/>
-      </c>
-      <c r="J109">
-        <f>IF(AND(ISNUMBER(D109),D109&gt;=$O$4,OR($O$11=0,B109&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K109">
-        <f>B109-$O$14</f>
+        <f>B109-$O$8</f>
         <v/>
       </c>
     </row>
@@ -5781,31 +4866,23 @@
         <v>62.18</v>
       </c>
       <c r="E110">
-        <f>MEDIAN(D90:D116)</f>
+        <f>IFERROR(MEDIAN(D90:D116),D110)</f>
         <v/>
       </c>
       <c r="F110">
-        <f>E90</f>
+        <f>IF(OR(NOT(ISNUMBER(D110)),ABS(D110-E110)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G110">
-        <f>F110-E110</f>
+        <f>IF(F110=1,NA(),D110)</f>
         <v/>
       </c>
       <c r="H110">
-        <f>IF(OR(NOT(ISNUMBER(D110)),ABS(D110-E110)&gt;$O$3,AND($O$11=1,B110&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D110),D110&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I110">
-        <f>IF(H110=1,NA(),D110)</f>
-        <v/>
-      </c>
-      <c r="J110">
-        <f>IF(AND(ISNUMBER(D110),D110&gt;=$O$4,OR($O$11=0,B110&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K110">
-        <f>B110-$O$14</f>
+        <f>B110-$O$8</f>
         <v/>
       </c>
     </row>
@@ -5825,31 +4902,23 @@
         <v>62.19</v>
       </c>
       <c r="E111">
-        <f>MEDIAN(D91:D116)</f>
+        <f>IFERROR(MEDIAN(D91:D116),D111)</f>
         <v/>
       </c>
       <c r="F111">
-        <f>E91</f>
+        <f>IF(OR(NOT(ISNUMBER(D111)),ABS(D111-E111)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G111">
-        <f>F111-E111</f>
+        <f>IF(F111=1,NA(),D111)</f>
         <v/>
       </c>
       <c r="H111">
-        <f>IF(OR(NOT(ISNUMBER(D111)),ABS(D111-E111)&gt;$O$3,AND($O$11=1,B111&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D111),D111&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I111">
-        <f>IF(H111=1,NA(),D111)</f>
-        <v/>
-      </c>
-      <c r="J111">
-        <f>IF(AND(ISNUMBER(D111),D111&gt;=$O$4,OR($O$11=0,B111&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K111">
-        <f>B111-$O$14</f>
+        <f>B111-$O$8</f>
         <v/>
       </c>
     </row>
@@ -5869,31 +4938,23 @@
         <v>62.19</v>
       </c>
       <c r="E112">
-        <f>MEDIAN(D92:D116)</f>
+        <f>IFERROR(MEDIAN(D92:D116),D112)</f>
         <v/>
       </c>
       <c r="F112">
-        <f>E92</f>
+        <f>IF(OR(NOT(ISNUMBER(D112)),ABS(D112-E112)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G112">
-        <f>F112-E112</f>
+        <f>IF(F112=1,NA(),D112)</f>
         <v/>
       </c>
       <c r="H112">
-        <f>IF(OR(NOT(ISNUMBER(D112)),ABS(D112-E112)&gt;$O$3,AND($O$11=1,B112&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D112),D112&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I112">
-        <f>IF(H112=1,NA(),D112)</f>
-        <v/>
-      </c>
-      <c r="J112">
-        <f>IF(AND(ISNUMBER(D112),D112&gt;=$O$4,OR($O$11=0,B112&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K112">
-        <f>B112-$O$14</f>
+        <f>B112-$O$8</f>
         <v/>
       </c>
     </row>
@@ -5913,31 +4974,23 @@
         <v>62.19</v>
       </c>
       <c r="E113">
-        <f>MEDIAN(D93:D116)</f>
+        <f>IFERROR(MEDIAN(D93:D116),D113)</f>
         <v/>
       </c>
       <c r="F113">
-        <f>E93</f>
+        <f>IF(OR(NOT(ISNUMBER(D113)),ABS(D113-E113)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G113">
-        <f>F113-E113</f>
+        <f>IF(F113=1,NA(),D113)</f>
         <v/>
       </c>
       <c r="H113">
-        <f>IF(OR(NOT(ISNUMBER(D113)),ABS(D113-E113)&gt;$O$3,AND($O$11=1,B113&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D113),D113&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I113">
-        <f>IF(H113=1,NA(),D113)</f>
-        <v/>
-      </c>
-      <c r="J113">
-        <f>IF(AND(ISNUMBER(D113),D113&gt;=$O$4,OR($O$11=0,B113&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K113">
-        <f>B113-$O$14</f>
+        <f>B113-$O$8</f>
         <v/>
       </c>
     </row>
@@ -5957,31 +5010,23 @@
         <v>62.28</v>
       </c>
       <c r="E114">
-        <f>MEDIAN(D94:D116)</f>
+        <f>IFERROR(MEDIAN(D94:D116),D114)</f>
         <v/>
       </c>
       <c r="F114">
-        <f>E94</f>
+        <f>IF(OR(NOT(ISNUMBER(D114)),ABS(D114-E114)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G114">
-        <f>F114-E114</f>
+        <f>IF(F114=1,NA(),D114)</f>
         <v/>
       </c>
       <c r="H114">
-        <f>IF(OR(NOT(ISNUMBER(D114)),ABS(D114-E114)&gt;$O$3,AND($O$11=1,B114&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D114),D114&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I114">
-        <f>IF(H114=1,NA(),D114)</f>
-        <v/>
-      </c>
-      <c r="J114">
-        <f>IF(AND(ISNUMBER(D114),D114&gt;=$O$4,OR($O$11=0,B114&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K114">
-        <f>B114-$O$14</f>
+        <f>B114-$O$8</f>
         <v/>
       </c>
     </row>
@@ -6001,31 +5046,23 @@
         <v>62.2</v>
       </c>
       <c r="E115">
-        <f>MEDIAN(D95:D116)</f>
+        <f>IFERROR(MEDIAN(D95:D116),D115)</f>
         <v/>
       </c>
       <c r="F115">
-        <f>E95</f>
+        <f>IF(OR(NOT(ISNUMBER(D115)),ABS(D115-E115)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G115">
-        <f>F115-E115</f>
+        <f>IF(F115=1,NA(),D115)</f>
         <v/>
       </c>
       <c r="H115">
-        <f>IF(OR(NOT(ISNUMBER(D115)),ABS(D115-E115)&gt;$O$3,AND($O$11=1,B115&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D115),D115&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I115">
-        <f>IF(H115=1,NA(),D115)</f>
-        <v/>
-      </c>
-      <c r="J115">
-        <f>IF(AND(ISNUMBER(D115),D115&gt;=$O$4,OR($O$11=0,B115&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K115">
-        <f>B115-$O$14</f>
+        <f>B115-$O$8</f>
         <v/>
       </c>
     </row>
@@ -6045,31 +5082,23 @@
         <v>62.2</v>
       </c>
       <c r="E116">
-        <f>MEDIAN(D96:D116)</f>
+        <f>IFERROR(MEDIAN(D96:D116),D116)</f>
         <v/>
       </c>
       <c r="F116">
-        <f>E96</f>
+        <f>IF(OR(NOT(ISNUMBER(D116)),ABS(D116-E116)&gt;$O$3),1,0)</f>
         <v/>
       </c>
       <c r="G116">
-        <f>F116-E116</f>
+        <f>IF(F116=1,NA(),D116)</f>
         <v/>
       </c>
       <c r="H116">
-        <f>IF(OR(NOT(ISNUMBER(D116)),ABS(D116-E116)&gt;$O$3,AND($O$11=1,B116&lt;$O$12)),1,0)</f>
+        <f>IF(AND(ISNUMBER(D116),D116&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="I116">
-        <f>IF(H116=1,NA(),D116)</f>
-        <v/>
-      </c>
-      <c r="J116">
-        <f>IF(AND(ISNUMBER(D116),D116&gt;=$O$4,OR($O$11=0,B116&gt;=$O$12)),1,0)</f>
-        <v/>
-      </c>
-      <c r="K116">
-        <f>B116-$O$14</f>
+        <f>B116-$O$8</f>
         <v/>
       </c>
     </row>
@@ -6102,1151 +5131,1151 @@
     </row>
     <row r="2">
       <c r="A2">
-        <f>Sheet1!K2</f>
+        <f>Sheet1!I2</f>
         <v/>
       </c>
       <c r="B2">
-        <f>IF(ISNA(Sheet1!I2),NA(),Sheet1!$O$5-(Sheet1!I2/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G2),NA(),Sheet1!$O$5-(Sheet1!G2/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <f>Sheet1!K3</f>
+        <f>Sheet1!I3</f>
         <v/>
       </c>
       <c r="B3">
-        <f>IF(ISNA(Sheet1!I3),NA(),Sheet1!$O$5-(Sheet1!I3/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G3),NA(),Sheet1!$O$5-(Sheet1!G3/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <f>Sheet1!K4</f>
+        <f>Sheet1!I4</f>
         <v/>
       </c>
       <c r="B4">
-        <f>IF(ISNA(Sheet1!I4),NA(),Sheet1!$O$5-(Sheet1!I4/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G4),NA(),Sheet1!$O$5-(Sheet1!G4/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <f>Sheet1!K5</f>
+        <f>Sheet1!I5</f>
         <v/>
       </c>
       <c r="B5">
-        <f>IF(ISNA(Sheet1!I5),NA(),Sheet1!$O$5-(Sheet1!I5/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G5),NA(),Sheet1!$O$5-(Sheet1!G5/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <f>Sheet1!K6</f>
+        <f>Sheet1!I6</f>
         <v/>
       </c>
       <c r="B6">
-        <f>IF(ISNA(Sheet1!I6),NA(),Sheet1!$O$5-(Sheet1!I6/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G6),NA(),Sheet1!$O$5-(Sheet1!G6/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <f>Sheet1!K7</f>
+        <f>Sheet1!I7</f>
         <v/>
       </c>
       <c r="B7">
-        <f>IF(ISNA(Sheet1!I7),NA(),Sheet1!$O$5-(Sheet1!I7/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G7),NA(),Sheet1!$O$5-(Sheet1!G7/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <f>Sheet1!K8</f>
+        <f>Sheet1!I8</f>
         <v/>
       </c>
       <c r="B8">
-        <f>IF(ISNA(Sheet1!I8),NA(),Sheet1!$O$5-(Sheet1!I8/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G8),NA(),Sheet1!$O$5-(Sheet1!G8/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <f>Sheet1!K9</f>
+        <f>Sheet1!I9</f>
         <v/>
       </c>
       <c r="B9">
-        <f>IF(ISNA(Sheet1!I9),NA(),Sheet1!$O$5-(Sheet1!I9/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G9),NA(),Sheet1!$O$5-(Sheet1!G9/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <f>Sheet1!K10</f>
+        <f>Sheet1!I10</f>
         <v/>
       </c>
       <c r="B10">
-        <f>IF(ISNA(Sheet1!I10),NA(),Sheet1!$O$5-(Sheet1!I10/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G10),NA(),Sheet1!$O$5-(Sheet1!G10/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <f>Sheet1!K11</f>
+        <f>Sheet1!I11</f>
         <v/>
       </c>
       <c r="B11">
-        <f>IF(ISNA(Sheet1!I11),NA(),Sheet1!$O$5-(Sheet1!I11/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G11),NA(),Sheet1!$O$5-(Sheet1!G11/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <f>Sheet1!K12</f>
+        <f>Sheet1!I12</f>
         <v/>
       </c>
       <c r="B12">
-        <f>IF(ISNA(Sheet1!I12),NA(),Sheet1!$O$5-(Sheet1!I12/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G12),NA(),Sheet1!$O$5-(Sheet1!G12/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <f>Sheet1!K13</f>
+        <f>Sheet1!I13</f>
         <v/>
       </c>
       <c r="B13">
-        <f>IF(ISNA(Sheet1!I13),NA(),Sheet1!$O$5-(Sheet1!I13/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G13),NA(),Sheet1!$O$5-(Sheet1!G13/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <f>Sheet1!K14</f>
+        <f>Sheet1!I14</f>
         <v/>
       </c>
       <c r="B14">
-        <f>IF(ISNA(Sheet1!I14),NA(),Sheet1!$O$5-(Sheet1!I14/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G14),NA(),Sheet1!$O$5-(Sheet1!G14/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <f>Sheet1!K15</f>
+        <f>Sheet1!I15</f>
         <v/>
       </c>
       <c r="B15">
-        <f>IF(ISNA(Sheet1!I15),NA(),Sheet1!$O$5-(Sheet1!I15/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G15),NA(),Sheet1!$O$5-(Sheet1!G15/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <f>Sheet1!K16</f>
+        <f>Sheet1!I16</f>
         <v/>
       </c>
       <c r="B16">
-        <f>IF(ISNA(Sheet1!I16),NA(),Sheet1!$O$5-(Sheet1!I16/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G16),NA(),Sheet1!$O$5-(Sheet1!G16/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <f>Sheet1!K17</f>
+        <f>Sheet1!I17</f>
         <v/>
       </c>
       <c r="B17">
-        <f>IF(ISNA(Sheet1!I17),NA(),Sheet1!$O$5-(Sheet1!I17/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G17),NA(),Sheet1!$O$5-(Sheet1!G17/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <f>Sheet1!K18</f>
+        <f>Sheet1!I18</f>
         <v/>
       </c>
       <c r="B18">
-        <f>IF(ISNA(Sheet1!I18),NA(),Sheet1!$O$5-(Sheet1!I18/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G18),NA(),Sheet1!$O$5-(Sheet1!G18/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <f>Sheet1!K19</f>
+        <f>Sheet1!I19</f>
         <v/>
       </c>
       <c r="B19">
-        <f>IF(ISNA(Sheet1!I19),NA(),Sheet1!$O$5-(Sheet1!I19/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G19),NA(),Sheet1!$O$5-(Sheet1!G19/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <f>Sheet1!K20</f>
+        <f>Sheet1!I20</f>
         <v/>
       </c>
       <c r="B20">
-        <f>IF(ISNA(Sheet1!I20),NA(),Sheet1!$O$5-(Sheet1!I20/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G20),NA(),Sheet1!$O$5-(Sheet1!G20/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <f>Sheet1!K21</f>
+        <f>Sheet1!I21</f>
         <v/>
       </c>
       <c r="B21">
-        <f>IF(ISNA(Sheet1!I21),NA(),Sheet1!$O$5-(Sheet1!I21/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G21),NA(),Sheet1!$O$5-(Sheet1!G21/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <f>Sheet1!K22</f>
+        <f>Sheet1!I22</f>
         <v/>
       </c>
       <c r="B22">
-        <f>IF(ISNA(Sheet1!I22),NA(),Sheet1!$O$5-(Sheet1!I22/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G22),NA(),Sheet1!$O$5-(Sheet1!G22/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <f>Sheet1!K23</f>
+        <f>Sheet1!I23</f>
         <v/>
       </c>
       <c r="B23">
-        <f>IF(ISNA(Sheet1!I23),NA(),Sheet1!$O$5-(Sheet1!I23/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G23),NA(),Sheet1!$O$5-(Sheet1!G23/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <f>Sheet1!K24</f>
+        <f>Sheet1!I24</f>
         <v/>
       </c>
       <c r="B24">
-        <f>IF(ISNA(Sheet1!I24),NA(),Sheet1!$O$5-(Sheet1!I24/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G24),NA(),Sheet1!$O$5-(Sheet1!G24/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <f>Sheet1!K25</f>
+        <f>Sheet1!I25</f>
         <v/>
       </c>
       <c r="B25">
-        <f>IF(ISNA(Sheet1!I25),NA(),Sheet1!$O$5-(Sheet1!I25/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G25),NA(),Sheet1!$O$5-(Sheet1!G25/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <f>Sheet1!K26</f>
+        <f>Sheet1!I26</f>
         <v/>
       </c>
       <c r="B26">
-        <f>IF(ISNA(Sheet1!I26),NA(),Sheet1!$O$5-(Sheet1!I26/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G26),NA(),Sheet1!$O$5-(Sheet1!G26/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <f>Sheet1!K27</f>
+        <f>Sheet1!I27</f>
         <v/>
       </c>
       <c r="B27">
-        <f>IF(ISNA(Sheet1!I27),NA(),Sheet1!$O$5-(Sheet1!I27/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G27),NA(),Sheet1!$O$5-(Sheet1!G27/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <f>Sheet1!K28</f>
+        <f>Sheet1!I28</f>
         <v/>
       </c>
       <c r="B28">
-        <f>IF(ISNA(Sheet1!I28),NA(),Sheet1!$O$5-(Sheet1!I28/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G28),NA(),Sheet1!$O$5-(Sheet1!G28/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <f>Sheet1!K29</f>
+        <f>Sheet1!I29</f>
         <v/>
       </c>
       <c r="B29">
-        <f>IF(ISNA(Sheet1!I29),NA(),Sheet1!$O$5-(Sheet1!I29/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G29),NA(),Sheet1!$O$5-(Sheet1!G29/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <f>Sheet1!K30</f>
+        <f>Sheet1!I30</f>
         <v/>
       </c>
       <c r="B30">
-        <f>IF(ISNA(Sheet1!I30),NA(),Sheet1!$O$5-(Sheet1!I30/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G30),NA(),Sheet1!$O$5-(Sheet1!G30/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <f>Sheet1!K31</f>
+        <f>Sheet1!I31</f>
         <v/>
       </c>
       <c r="B31">
-        <f>IF(ISNA(Sheet1!I31),NA(),Sheet1!$O$5-(Sheet1!I31/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G31),NA(),Sheet1!$O$5-(Sheet1!G31/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <f>Sheet1!K32</f>
+        <f>Sheet1!I32</f>
         <v/>
       </c>
       <c r="B32">
-        <f>IF(ISNA(Sheet1!I32),NA(),Sheet1!$O$5-(Sheet1!I32/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G32),NA(),Sheet1!$O$5-(Sheet1!G32/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <f>Sheet1!K33</f>
+        <f>Sheet1!I33</f>
         <v/>
       </c>
       <c r="B33">
-        <f>IF(ISNA(Sheet1!I33),NA(),Sheet1!$O$5-(Sheet1!I33/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G33),NA(),Sheet1!$O$5-(Sheet1!G33/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <f>Sheet1!K34</f>
+        <f>Sheet1!I34</f>
         <v/>
       </c>
       <c r="B34">
-        <f>IF(ISNA(Sheet1!I34),NA(),Sheet1!$O$5-(Sheet1!I34/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G34),NA(),Sheet1!$O$5-(Sheet1!G34/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <f>Sheet1!K35</f>
+        <f>Sheet1!I35</f>
         <v/>
       </c>
       <c r="B35">
-        <f>IF(ISNA(Sheet1!I35),NA(),Sheet1!$O$5-(Sheet1!I35/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G35),NA(),Sheet1!$O$5-(Sheet1!G35/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <f>Sheet1!K36</f>
+        <f>Sheet1!I36</f>
         <v/>
       </c>
       <c r="B36">
-        <f>IF(ISNA(Sheet1!I36),NA(),Sheet1!$O$5-(Sheet1!I36/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G36),NA(),Sheet1!$O$5-(Sheet1!G36/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <f>Sheet1!K37</f>
+        <f>Sheet1!I37</f>
         <v/>
       </c>
       <c r="B37">
-        <f>IF(ISNA(Sheet1!I37),NA(),Sheet1!$O$5-(Sheet1!I37/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G37),NA(),Sheet1!$O$5-(Sheet1!G37/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <f>Sheet1!K38</f>
+        <f>Sheet1!I38</f>
         <v/>
       </c>
       <c r="B38">
-        <f>IF(ISNA(Sheet1!I38),NA(),Sheet1!$O$5-(Sheet1!I38/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G38),NA(),Sheet1!$O$5-(Sheet1!G38/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <f>Sheet1!K39</f>
+        <f>Sheet1!I39</f>
         <v/>
       </c>
       <c r="B39">
-        <f>IF(ISNA(Sheet1!I39),NA(),Sheet1!$O$5-(Sheet1!I39/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G39),NA(),Sheet1!$O$5-(Sheet1!G39/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <f>Sheet1!K40</f>
+        <f>Sheet1!I40</f>
         <v/>
       </c>
       <c r="B40">
-        <f>IF(ISNA(Sheet1!I40),NA(),Sheet1!$O$5-(Sheet1!I40/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G40),NA(),Sheet1!$O$5-(Sheet1!G40/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <f>Sheet1!K41</f>
+        <f>Sheet1!I41</f>
         <v/>
       </c>
       <c r="B41">
-        <f>IF(ISNA(Sheet1!I41),NA(),Sheet1!$O$5-(Sheet1!I41/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G41),NA(),Sheet1!$O$5-(Sheet1!G41/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <f>Sheet1!K42</f>
+        <f>Sheet1!I42</f>
         <v/>
       </c>
       <c r="B42">
-        <f>IF(ISNA(Sheet1!I42),NA(),Sheet1!$O$5-(Sheet1!I42/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G42),NA(),Sheet1!$O$5-(Sheet1!G42/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <f>Sheet1!K43</f>
+        <f>Sheet1!I43</f>
         <v/>
       </c>
       <c r="B43">
-        <f>IF(ISNA(Sheet1!I43),NA(),Sheet1!$O$5-(Sheet1!I43/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G43),NA(),Sheet1!$O$5-(Sheet1!G43/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <f>Sheet1!K44</f>
+        <f>Sheet1!I44</f>
         <v/>
       </c>
       <c r="B44">
-        <f>IF(ISNA(Sheet1!I44),NA(),Sheet1!$O$5-(Sheet1!I44/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G44),NA(),Sheet1!$O$5-(Sheet1!G44/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <f>Sheet1!K45</f>
+        <f>Sheet1!I45</f>
         <v/>
       </c>
       <c r="B45">
-        <f>IF(ISNA(Sheet1!I45),NA(),Sheet1!$O$5-(Sheet1!I45/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G45),NA(),Sheet1!$O$5-(Sheet1!G45/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <f>Sheet1!K46</f>
+        <f>Sheet1!I46</f>
         <v/>
       </c>
       <c r="B46">
-        <f>IF(ISNA(Sheet1!I46),NA(),Sheet1!$O$5-(Sheet1!I46/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G46),NA(),Sheet1!$O$5-(Sheet1!G46/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <f>Sheet1!K47</f>
+        <f>Sheet1!I47</f>
         <v/>
       </c>
       <c r="B47">
-        <f>IF(ISNA(Sheet1!I47),NA(),Sheet1!$O$5-(Sheet1!I47/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G47),NA(),Sheet1!$O$5-(Sheet1!G47/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <f>Sheet1!K48</f>
+        <f>Sheet1!I48</f>
         <v/>
       </c>
       <c r="B48">
-        <f>IF(ISNA(Sheet1!I48),NA(),Sheet1!$O$5-(Sheet1!I48/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G48),NA(),Sheet1!$O$5-(Sheet1!G48/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <f>Sheet1!K49</f>
+        <f>Sheet1!I49</f>
         <v/>
       </c>
       <c r="B49">
-        <f>IF(ISNA(Sheet1!I49),NA(),Sheet1!$O$5-(Sheet1!I49/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G49),NA(),Sheet1!$O$5-(Sheet1!G49/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <f>Sheet1!K50</f>
+        <f>Sheet1!I50</f>
         <v/>
       </c>
       <c r="B50">
-        <f>IF(ISNA(Sheet1!I50),NA(),Sheet1!$O$5-(Sheet1!I50/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G50),NA(),Sheet1!$O$5-(Sheet1!G50/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <f>Sheet1!K51</f>
+        <f>Sheet1!I51</f>
         <v/>
       </c>
       <c r="B51">
-        <f>IF(ISNA(Sheet1!I51),NA(),Sheet1!$O$5-(Sheet1!I51/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G51),NA(),Sheet1!$O$5-(Sheet1!G51/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52">
-        <f>Sheet1!K52</f>
+        <f>Sheet1!I52</f>
         <v/>
       </c>
       <c r="B52">
-        <f>IF(ISNA(Sheet1!I52),NA(),Sheet1!$O$5-(Sheet1!I52/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G52),NA(),Sheet1!$O$5-(Sheet1!G52/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53">
-        <f>Sheet1!K53</f>
+        <f>Sheet1!I53</f>
         <v/>
       </c>
       <c r="B53">
-        <f>IF(ISNA(Sheet1!I53),NA(),Sheet1!$O$5-(Sheet1!I53/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G53),NA(),Sheet1!$O$5-(Sheet1!G53/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54">
-        <f>Sheet1!K54</f>
+        <f>Sheet1!I54</f>
         <v/>
       </c>
       <c r="B54">
-        <f>IF(ISNA(Sheet1!I54),NA(),Sheet1!$O$5-(Sheet1!I54/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G54),NA(),Sheet1!$O$5-(Sheet1!G54/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <f>Sheet1!K55</f>
+        <f>Sheet1!I55</f>
         <v/>
       </c>
       <c r="B55">
-        <f>IF(ISNA(Sheet1!I55),NA(),Sheet1!$O$5-(Sheet1!I55/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G55),NA(),Sheet1!$O$5-(Sheet1!G55/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <f>Sheet1!K56</f>
+        <f>Sheet1!I56</f>
         <v/>
       </c>
       <c r="B56">
-        <f>IF(ISNA(Sheet1!I56),NA(),Sheet1!$O$5-(Sheet1!I56/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G56),NA(),Sheet1!$O$5-(Sheet1!G56/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57">
-        <f>Sheet1!K57</f>
+        <f>Sheet1!I57</f>
         <v/>
       </c>
       <c r="B57">
-        <f>IF(ISNA(Sheet1!I57),NA(),Sheet1!$O$5-(Sheet1!I57/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G57),NA(),Sheet1!$O$5-(Sheet1!G57/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <f>Sheet1!K58</f>
+        <f>Sheet1!I58</f>
         <v/>
       </c>
       <c r="B58">
-        <f>IF(ISNA(Sheet1!I58),NA(),Sheet1!$O$5-(Sheet1!I58/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G58),NA(),Sheet1!$O$5-(Sheet1!G58/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59">
-        <f>Sheet1!K59</f>
+        <f>Sheet1!I59</f>
         <v/>
       </c>
       <c r="B59">
-        <f>IF(ISNA(Sheet1!I59),NA(),Sheet1!$O$5-(Sheet1!I59/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G59),NA(),Sheet1!$O$5-(Sheet1!G59/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60">
-        <f>Sheet1!K60</f>
+        <f>Sheet1!I60</f>
         <v/>
       </c>
       <c r="B60">
-        <f>IF(ISNA(Sheet1!I60),NA(),Sheet1!$O$5-(Sheet1!I60/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G60),NA(),Sheet1!$O$5-(Sheet1!G60/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61">
-        <f>Sheet1!K61</f>
+        <f>Sheet1!I61</f>
         <v/>
       </c>
       <c r="B61">
-        <f>IF(ISNA(Sheet1!I61),NA(),Sheet1!$O$5-(Sheet1!I61/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G61),NA(),Sheet1!$O$5-(Sheet1!G61/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62">
-        <f>Sheet1!K62</f>
+        <f>Sheet1!I62</f>
         <v/>
       </c>
       <c r="B62">
-        <f>IF(ISNA(Sheet1!I62),NA(),Sheet1!$O$5-(Sheet1!I62/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G62),NA(),Sheet1!$O$5-(Sheet1!G62/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <f>Sheet1!K63</f>
+        <f>Sheet1!I63</f>
         <v/>
       </c>
       <c r="B63">
-        <f>IF(ISNA(Sheet1!I63),NA(),Sheet1!$O$5-(Sheet1!I63/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G63),NA(),Sheet1!$O$5-(Sheet1!G63/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <f>Sheet1!K64</f>
+        <f>Sheet1!I64</f>
         <v/>
       </c>
       <c r="B64">
-        <f>IF(ISNA(Sheet1!I64),NA(),Sheet1!$O$5-(Sheet1!I64/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G64),NA(),Sheet1!$O$5-(Sheet1!G64/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65">
-        <f>Sheet1!K65</f>
+        <f>Sheet1!I65</f>
         <v/>
       </c>
       <c r="B65">
-        <f>IF(ISNA(Sheet1!I65),NA(),Sheet1!$O$5-(Sheet1!I65/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G65),NA(),Sheet1!$O$5-(Sheet1!G65/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66">
-        <f>Sheet1!K66</f>
+        <f>Sheet1!I66</f>
         <v/>
       </c>
       <c r="B66">
-        <f>IF(ISNA(Sheet1!I66),NA(),Sheet1!$O$5-(Sheet1!I66/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G66),NA(),Sheet1!$O$5-(Sheet1!G66/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67">
-        <f>Sheet1!K67</f>
+        <f>Sheet1!I67</f>
         <v/>
       </c>
       <c r="B67">
-        <f>IF(ISNA(Sheet1!I67),NA(),Sheet1!$O$5-(Sheet1!I67/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G67),NA(),Sheet1!$O$5-(Sheet1!G67/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68">
-        <f>Sheet1!K68</f>
+        <f>Sheet1!I68</f>
         <v/>
       </c>
       <c r="B68">
-        <f>IF(ISNA(Sheet1!I68),NA(),Sheet1!$O$5-(Sheet1!I68/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G68),NA(),Sheet1!$O$5-(Sheet1!G68/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69">
-        <f>Sheet1!K69</f>
+        <f>Sheet1!I69</f>
         <v/>
       </c>
       <c r="B69">
-        <f>IF(ISNA(Sheet1!I69),NA(),Sheet1!$O$5-(Sheet1!I69/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G69),NA(),Sheet1!$O$5-(Sheet1!G69/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70">
-        <f>Sheet1!K70</f>
+        <f>Sheet1!I70</f>
         <v/>
       </c>
       <c r="B70">
-        <f>IF(ISNA(Sheet1!I70),NA(),Sheet1!$O$5-(Sheet1!I70/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G70),NA(),Sheet1!$O$5-(Sheet1!G70/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71">
-        <f>Sheet1!K71</f>
+        <f>Sheet1!I71</f>
         <v/>
       </c>
       <c r="B71">
-        <f>IF(ISNA(Sheet1!I71),NA(),Sheet1!$O$5-(Sheet1!I71/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G71),NA(),Sheet1!$O$5-(Sheet1!G71/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72">
-        <f>Sheet1!K72</f>
+        <f>Sheet1!I72</f>
         <v/>
       </c>
       <c r="B72">
-        <f>IF(ISNA(Sheet1!I72),NA(),Sheet1!$O$5-(Sheet1!I72/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G72),NA(),Sheet1!$O$5-(Sheet1!G72/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73">
-        <f>Sheet1!K73</f>
+        <f>Sheet1!I73</f>
         <v/>
       </c>
       <c r="B73">
-        <f>IF(ISNA(Sheet1!I73),NA(),Sheet1!$O$5-(Sheet1!I73/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G73),NA(),Sheet1!$O$5-(Sheet1!G73/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74">
-        <f>Sheet1!K74</f>
+        <f>Sheet1!I74</f>
         <v/>
       </c>
       <c r="B74">
-        <f>IF(ISNA(Sheet1!I74),NA(),Sheet1!$O$5-(Sheet1!I74/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G74),NA(),Sheet1!$O$5-(Sheet1!G74/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75">
-        <f>Sheet1!K75</f>
+        <f>Sheet1!I75</f>
         <v/>
       </c>
       <c r="B75">
-        <f>IF(ISNA(Sheet1!I75),NA(),Sheet1!$O$5-(Sheet1!I75/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G75),NA(),Sheet1!$O$5-(Sheet1!G75/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76">
-        <f>Sheet1!K76</f>
+        <f>Sheet1!I76</f>
         <v/>
       </c>
       <c r="B76">
-        <f>IF(ISNA(Sheet1!I76),NA(),Sheet1!$O$5-(Sheet1!I76/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G76),NA(),Sheet1!$O$5-(Sheet1!G76/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77">
-        <f>Sheet1!K77</f>
+        <f>Sheet1!I77</f>
         <v/>
       </c>
       <c r="B77">
-        <f>IF(ISNA(Sheet1!I77),NA(),Sheet1!$O$5-(Sheet1!I77/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G77),NA(),Sheet1!$O$5-(Sheet1!G77/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78">
-        <f>Sheet1!K78</f>
+        <f>Sheet1!I78</f>
         <v/>
       </c>
       <c r="B78">
-        <f>IF(ISNA(Sheet1!I78),NA(),Sheet1!$O$5-(Sheet1!I78/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G78),NA(),Sheet1!$O$5-(Sheet1!G78/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79">
-        <f>Sheet1!K79</f>
+        <f>Sheet1!I79</f>
         <v/>
       </c>
       <c r="B79">
-        <f>IF(ISNA(Sheet1!I79),NA(),Sheet1!$O$5-(Sheet1!I79/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G79),NA(),Sheet1!$O$5-(Sheet1!G79/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80">
-        <f>Sheet1!K80</f>
+        <f>Sheet1!I80</f>
         <v/>
       </c>
       <c r="B80">
-        <f>IF(ISNA(Sheet1!I80),NA(),Sheet1!$O$5-(Sheet1!I80/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G80),NA(),Sheet1!$O$5-(Sheet1!G80/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81">
-        <f>Sheet1!K81</f>
+        <f>Sheet1!I81</f>
         <v/>
       </c>
       <c r="B81">
-        <f>IF(ISNA(Sheet1!I81),NA(),Sheet1!$O$5-(Sheet1!I81/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G81),NA(),Sheet1!$O$5-(Sheet1!G81/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82">
-        <f>Sheet1!K82</f>
+        <f>Sheet1!I82</f>
         <v/>
       </c>
       <c r="B82">
-        <f>IF(ISNA(Sheet1!I82),NA(),Sheet1!$O$5-(Sheet1!I82/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G82),NA(),Sheet1!$O$5-(Sheet1!G82/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83">
-        <f>Sheet1!K83</f>
+        <f>Sheet1!I83</f>
         <v/>
       </c>
       <c r="B83">
-        <f>IF(ISNA(Sheet1!I83),NA(),Sheet1!$O$5-(Sheet1!I83/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G83),NA(),Sheet1!$O$5-(Sheet1!G83/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84">
-        <f>Sheet1!K84</f>
+        <f>Sheet1!I84</f>
         <v/>
       </c>
       <c r="B84">
-        <f>IF(ISNA(Sheet1!I84),NA(),Sheet1!$O$5-(Sheet1!I84/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G84),NA(),Sheet1!$O$5-(Sheet1!G84/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85">
-        <f>Sheet1!K85</f>
+        <f>Sheet1!I85</f>
         <v/>
       </c>
       <c r="B85">
-        <f>IF(ISNA(Sheet1!I85),NA(),Sheet1!$O$5-(Sheet1!I85/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G85),NA(),Sheet1!$O$5-(Sheet1!G85/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86">
-        <f>Sheet1!K86</f>
+        <f>Sheet1!I86</f>
         <v/>
       </c>
       <c r="B86">
-        <f>IF(ISNA(Sheet1!I86),NA(),Sheet1!$O$5-(Sheet1!I86/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G86),NA(),Sheet1!$O$5-(Sheet1!G86/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87">
-        <f>Sheet1!K87</f>
+        <f>Sheet1!I87</f>
         <v/>
       </c>
       <c r="B87">
-        <f>IF(ISNA(Sheet1!I87),NA(),Sheet1!$O$5-(Sheet1!I87/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G87),NA(),Sheet1!$O$5-(Sheet1!G87/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88">
-        <f>Sheet1!K88</f>
+        <f>Sheet1!I88</f>
         <v/>
       </c>
       <c r="B88">
-        <f>IF(ISNA(Sheet1!I88),NA(),Sheet1!$O$5-(Sheet1!I88/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G88),NA(),Sheet1!$O$5-(Sheet1!G88/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89">
-        <f>Sheet1!K89</f>
+        <f>Sheet1!I89</f>
         <v/>
       </c>
       <c r="B89">
-        <f>IF(ISNA(Sheet1!I89),NA(),Sheet1!$O$5-(Sheet1!I89/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G89),NA(),Sheet1!$O$5-(Sheet1!G89/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="90">
       <c r="A90">
-        <f>Sheet1!K90</f>
+        <f>Sheet1!I90</f>
         <v/>
       </c>
       <c r="B90">
-        <f>IF(ISNA(Sheet1!I90),NA(),Sheet1!$O$5-(Sheet1!I90/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G90),NA(),Sheet1!$O$5-(Sheet1!G90/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="91">
       <c r="A91">
-        <f>Sheet1!K91</f>
+        <f>Sheet1!I91</f>
         <v/>
       </c>
       <c r="B91">
-        <f>IF(ISNA(Sheet1!I91),NA(),Sheet1!$O$5-(Sheet1!I91/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G91),NA(),Sheet1!$O$5-(Sheet1!G91/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92">
-        <f>Sheet1!K92</f>
+        <f>Sheet1!I92</f>
         <v/>
       </c>
       <c r="B92">
-        <f>IF(ISNA(Sheet1!I92),NA(),Sheet1!$O$5-(Sheet1!I92/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G92),NA(),Sheet1!$O$5-(Sheet1!G92/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93">
-        <f>Sheet1!K93</f>
+        <f>Sheet1!I93</f>
         <v/>
       </c>
       <c r="B93">
-        <f>IF(ISNA(Sheet1!I93),NA(),Sheet1!$O$5-(Sheet1!I93/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G93),NA(),Sheet1!$O$5-(Sheet1!G93/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94">
-        <f>Sheet1!K94</f>
+        <f>Sheet1!I94</f>
         <v/>
       </c>
       <c r="B94">
-        <f>IF(ISNA(Sheet1!I94),NA(),Sheet1!$O$5-(Sheet1!I94/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G94),NA(),Sheet1!$O$5-(Sheet1!G94/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95">
-        <f>Sheet1!K95</f>
+        <f>Sheet1!I95</f>
         <v/>
       </c>
       <c r="B95">
-        <f>IF(ISNA(Sheet1!I95),NA(),Sheet1!$O$5-(Sheet1!I95/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G95),NA(),Sheet1!$O$5-(Sheet1!G95/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="96">
       <c r="A96">
-        <f>Sheet1!K96</f>
+        <f>Sheet1!I96</f>
         <v/>
       </c>
       <c r="B96">
-        <f>IF(ISNA(Sheet1!I96),NA(),Sheet1!$O$5-(Sheet1!I96/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G96),NA(),Sheet1!$O$5-(Sheet1!G96/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97">
-        <f>Sheet1!K97</f>
+        <f>Sheet1!I97</f>
         <v/>
       </c>
       <c r="B97">
-        <f>IF(ISNA(Sheet1!I97),NA(),Sheet1!$O$5-(Sheet1!I97/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G97),NA(),Sheet1!$O$5-(Sheet1!G97/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98">
-        <f>Sheet1!K98</f>
+        <f>Sheet1!I98</f>
         <v/>
       </c>
       <c r="B98">
-        <f>IF(ISNA(Sheet1!I98),NA(),Sheet1!$O$5-(Sheet1!I98/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G98),NA(),Sheet1!$O$5-(Sheet1!G98/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="99">
       <c r="A99">
-        <f>Sheet1!K99</f>
+        <f>Sheet1!I99</f>
         <v/>
       </c>
       <c r="B99">
-        <f>IF(ISNA(Sheet1!I99),NA(),Sheet1!$O$5-(Sheet1!I99/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G99),NA(),Sheet1!$O$5-(Sheet1!G99/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100">
-        <f>Sheet1!K100</f>
+        <f>Sheet1!I100</f>
         <v/>
       </c>
       <c r="B100">
-        <f>IF(ISNA(Sheet1!I100),NA(),Sheet1!$O$5-(Sheet1!I100/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G100),NA(),Sheet1!$O$5-(Sheet1!G100/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101">
-        <f>Sheet1!K101</f>
+        <f>Sheet1!I101</f>
         <v/>
       </c>
       <c r="B101">
-        <f>IF(ISNA(Sheet1!I101),NA(),Sheet1!$O$5-(Sheet1!I101/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G101),NA(),Sheet1!$O$5-(Sheet1!G101/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102">
-        <f>Sheet1!K102</f>
+        <f>Sheet1!I102</f>
         <v/>
       </c>
       <c r="B102">
-        <f>IF(ISNA(Sheet1!I102),NA(),Sheet1!$O$5-(Sheet1!I102/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G102),NA(),Sheet1!$O$5-(Sheet1!G102/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="103">
       <c r="A103">
-        <f>Sheet1!K103</f>
+        <f>Sheet1!I103</f>
         <v/>
       </c>
       <c r="B103">
-        <f>IF(ISNA(Sheet1!I103),NA(),Sheet1!$O$5-(Sheet1!I103/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G103),NA(),Sheet1!$O$5-(Sheet1!G103/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="104">
       <c r="A104">
-        <f>Sheet1!K104</f>
+        <f>Sheet1!I104</f>
         <v/>
       </c>
       <c r="B104">
-        <f>IF(ISNA(Sheet1!I104),NA(),Sheet1!$O$5-(Sheet1!I104/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G104),NA(),Sheet1!$O$5-(Sheet1!G104/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105">
-        <f>Sheet1!K105</f>
+        <f>Sheet1!I105</f>
         <v/>
       </c>
       <c r="B105">
-        <f>IF(ISNA(Sheet1!I105),NA(),Sheet1!$O$5-(Sheet1!I105/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G105),NA(),Sheet1!$O$5-(Sheet1!G105/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106">
-        <f>Sheet1!K106</f>
+        <f>Sheet1!I106</f>
         <v/>
       </c>
       <c r="B106">
-        <f>IF(ISNA(Sheet1!I106),NA(),Sheet1!$O$5-(Sheet1!I106/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G106),NA(),Sheet1!$O$5-(Sheet1!G106/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107">
-        <f>Sheet1!K107</f>
+        <f>Sheet1!I107</f>
         <v/>
       </c>
       <c r="B107">
-        <f>IF(ISNA(Sheet1!I107),NA(),Sheet1!$O$5-(Sheet1!I107/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G107),NA(),Sheet1!$O$5-(Sheet1!G107/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="108">
       <c r="A108">
-        <f>Sheet1!K108</f>
+        <f>Sheet1!I108</f>
         <v/>
       </c>
       <c r="B108">
-        <f>IF(ISNA(Sheet1!I108),NA(),Sheet1!$O$5-(Sheet1!I108/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G108),NA(),Sheet1!$O$5-(Sheet1!G108/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="109">
       <c r="A109">
-        <f>Sheet1!K109</f>
+        <f>Sheet1!I109</f>
         <v/>
       </c>
       <c r="B109">
-        <f>IF(ISNA(Sheet1!I109),NA(),Sheet1!$O$5-(Sheet1!I109/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G109),NA(),Sheet1!$O$5-(Sheet1!G109/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110">
-        <f>Sheet1!K110</f>
+        <f>Sheet1!I110</f>
         <v/>
       </c>
       <c r="B110">
-        <f>IF(ISNA(Sheet1!I110),NA(),Sheet1!$O$5-(Sheet1!I110/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G110),NA(),Sheet1!$O$5-(Sheet1!G110/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="111">
       <c r="A111">
-        <f>Sheet1!K111</f>
+        <f>Sheet1!I111</f>
         <v/>
       </c>
       <c r="B111">
-        <f>IF(ISNA(Sheet1!I111),NA(),Sheet1!$O$5-(Sheet1!I111/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G111),NA(),Sheet1!$O$5-(Sheet1!G111/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="112">
       <c r="A112">
-        <f>Sheet1!K112</f>
+        <f>Sheet1!I112</f>
         <v/>
       </c>
       <c r="B112">
-        <f>IF(ISNA(Sheet1!I112),NA(),Sheet1!$O$5-(Sheet1!I112/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G112),NA(),Sheet1!$O$5-(Sheet1!G112/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="113">
       <c r="A113">
-        <f>Sheet1!K113</f>
+        <f>Sheet1!I113</f>
         <v/>
       </c>
       <c r="B113">
-        <f>IF(ISNA(Sheet1!I113),NA(),Sheet1!$O$5-(Sheet1!I113/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G113),NA(),Sheet1!$O$5-(Sheet1!G113/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="114">
       <c r="A114">
-        <f>Sheet1!K114</f>
+        <f>Sheet1!I114</f>
         <v/>
       </c>
       <c r="B114">
-        <f>IF(ISNA(Sheet1!I114),NA(),Sheet1!$O$5-(Sheet1!I114/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G114),NA(),Sheet1!$O$5-(Sheet1!G114/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="115">
       <c r="A115">
-        <f>Sheet1!K115</f>
+        <f>Sheet1!I115</f>
         <v/>
       </c>
       <c r="B115">
-        <f>IF(ISNA(Sheet1!I115),NA(),Sheet1!$O$5-(Sheet1!I115/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G115),NA(),Sheet1!$O$5-(Sheet1!G115/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="116">
       <c r="A116">
-        <f>Sheet1!K116</f>
+        <f>Sheet1!I116</f>
         <v/>
       </c>
       <c r="B116">
-        <f>IF(ISNA(Sheet1!I116),NA(),Sheet1!$O$5-(Sheet1!I116/Sheet1!$O$6))</f>
+        <f>IF(ISNA(Sheet1!G116),NA(),Sheet1!$O$5-(Sheet1!G116/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>

--- a/kivampro_iddsi/iddsi1/iddsi1_iddsi1-60ml-2/iddsi1_iddsi1-60ml-2_weights.xlsx
+++ b/kivampro_iddsi/iddsi1/iddsi1_iddsi1-60ml-2/iddsi1_iddsi1-60ml-2_weights.xlsx
@@ -269,7 +269,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>iddsi1_iddsi1-60ml-2_weights - kept weight vs corrected time</a:t>
+              <a:t>iddsi1_iddsi1-60ml-2_weights - weight vs corrected time</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -282,7 +282,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Sheet1'!G1</f>
+              <f>'Sheet1'!D1</f>
             </strRef>
           </tx>
           <spPr>
@@ -308,12 +308,12 @@
           </marker>
           <xVal>
             <numRef>
-              <f>'Sheet1'!$I$2:$I$116</f>
+              <f>'Sheet1'!$F$2:$F$116</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'Sheet1'!$G$2:$G$116</f>
+              <f>'Sheet1'!$D$2:$D$116</f>
             </numRef>
           </yVal>
         </ser>
@@ -903,29 +903,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>local_median_g</t>
+          <t>is_started</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>excluded</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>weight_kept_g</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>is_started</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
           <t>time_corrected_s</t>
         </is>
       </c>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
       <c r="J1" s="1" t="n"/>
       <c r="K1" s="1" t="n"/>
       <c r="N1" s="1" t="inlineStr">
@@ -950,22 +938,10 @@
         <v>8.880000000000001</v>
       </c>
       <c r="E2">
-        <f>IFERROR(MEDIAN(D2:D22),D2)</f>
+        <f>IF(AND(ISNUMBER(D2),D2&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F2">
-        <f>IF(OR(NOT(ISNUMBER(D2)),ABS(D2-E2)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G2">
-        <f>IF(F2=1,NA(),D2)</f>
-        <v/>
-      </c>
-      <c r="H2">
-        <f>IF(AND(ISNUMBER(D2),D2&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I2">
         <f>B2-$O$8</f>
         <v/>
       </c>
@@ -994,22 +970,10 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <f>IFERROR(MEDIAN(D2:D23),D3)</f>
+        <f>IF(AND(ISNUMBER(D3),D3&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F3">
-        <f>IF(OR(NOT(ISNUMBER(D3)),ABS(D3-E3)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G3">
-        <f>IF(F3=1,NA(),D3)</f>
-        <v/>
-      </c>
-      <c r="H3">
-        <f>IF(AND(ISNUMBER(D3),D3&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I3">
         <f>B3-$O$8</f>
         <v/>
       </c>
@@ -1038,22 +1002,10 @@
         <v>8.880000000000001</v>
       </c>
       <c r="E4">
-        <f>IFERROR(MEDIAN(D2:D24),D4)</f>
+        <f>IF(AND(ISNUMBER(D4),D4&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F4">
-        <f>IF(OR(NOT(ISNUMBER(D4)),ABS(D4-E4)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G4">
-        <f>IF(F4=1,NA(),D4)</f>
-        <v/>
-      </c>
-      <c r="H4">
-        <f>IF(AND(ISNUMBER(D4),D4&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I4">
         <f>B4-$O$8</f>
         <v/>
       </c>
@@ -1082,22 +1034,10 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <f>IFERROR(MEDIAN(D2:D25),D5)</f>
+        <f>IF(AND(ISNUMBER(D5),D5&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F5">
-        <f>IF(OR(NOT(ISNUMBER(D5)),ABS(D5-E5)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G5">
-        <f>IF(F5=1,NA(),D5)</f>
-        <v/>
-      </c>
-      <c r="H5">
-        <f>IF(AND(ISNUMBER(D5),D5&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I5">
         <f>B5-$O$8</f>
         <v/>
       </c>
@@ -1126,22 +1066,10 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <f>IFERROR(MEDIAN(D2:D26),D6)</f>
+        <f>IF(AND(ISNUMBER(D6),D6&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F6">
-        <f>IF(OR(NOT(ISNUMBER(D6)),ABS(D6-E6)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G6">
-        <f>IF(F6=1,NA(),D6)</f>
-        <v/>
-      </c>
-      <c r="H6">
-        <f>IF(AND(ISNUMBER(D6),D6&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I6">
         <f>B6-$O$8</f>
         <v/>
       </c>
@@ -1170,22 +1098,10 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <f>IFERROR(MEDIAN(D2:D27),D7)</f>
+        <f>IF(AND(ISNUMBER(D7),D7&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F7">
-        <f>IF(OR(NOT(ISNUMBER(D7)),ABS(D7-E7)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G7">
-        <f>IF(F7=1,NA(),D7)</f>
-        <v/>
-      </c>
-      <c r="H7">
-        <f>IF(AND(ISNUMBER(D7),D7&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I7">
         <f>B7-$O$8</f>
         <v/>
       </c>
@@ -1206,22 +1122,10 @@
         <v>8.880000000000001</v>
       </c>
       <c r="E8">
-        <f>IFERROR(MEDIAN(D2:D28),D8)</f>
+        <f>IF(AND(ISNUMBER(D8),D8&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F8">
-        <f>IF(OR(NOT(ISNUMBER(D8)),ABS(D8-E8)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G8">
-        <f>IF(F8=1,NA(),D8)</f>
-        <v/>
-      </c>
-      <c r="H8">
-        <f>IF(AND(ISNUMBER(D8),D8&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I8">
         <f>B8-$O$8</f>
         <v/>
       </c>
@@ -1231,7 +1135,7 @@
         </is>
       </c>
       <c r="O8">
-        <f>IFERROR(INDEX(B2:B116,MATCH(1,H2:H116,0)),0)</f>
+        <f>IFERROR(INDEX(B2:B116,MATCH(1,E2:E116,0)),0)</f>
         <v/>
       </c>
     </row>
@@ -1251,22 +1155,10 @@
         <v>8.880000000000001</v>
       </c>
       <c r="E9">
-        <f>IFERROR(MEDIAN(D2:D29),D9)</f>
+        <f>IF(AND(ISNUMBER(D9),D9&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F9">
-        <f>IF(OR(NOT(ISNUMBER(D9)),ABS(D9-E9)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G9">
-        <f>IF(F9=1,NA(),D9)</f>
-        <v/>
-      </c>
-      <c r="H9">
-        <f>IF(AND(ISNUMBER(D9),D9&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I9">
         <f>B9-$O$8</f>
         <v/>
       </c>
@@ -1287,22 +1179,10 @@
         <v>8.08</v>
       </c>
       <c r="E10">
-        <f>IFERROR(MEDIAN(D2:D30),D10)</f>
+        <f>IF(AND(ISNUMBER(D10),D10&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F10">
-        <f>IF(OR(NOT(ISNUMBER(D10)),ABS(D10-E10)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G10">
-        <f>IF(F10=1,NA(),D10)</f>
-        <v/>
-      </c>
-      <c r="H10">
-        <f>IF(AND(ISNUMBER(D10),D10&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I10">
         <f>B10-$O$8</f>
         <v/>
       </c>
@@ -1323,22 +1203,10 @@
         <v>8.08</v>
       </c>
       <c r="E11">
-        <f>IFERROR(MEDIAN(D2:D31),D11)</f>
+        <f>IF(AND(ISNUMBER(D11),D11&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F11">
-        <f>IF(OR(NOT(ISNUMBER(D11)),ABS(D11-E11)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G11">
-        <f>IF(F11=1,NA(),D11)</f>
-        <v/>
-      </c>
-      <c r="H11">
-        <f>IF(AND(ISNUMBER(D11),D11&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I11">
         <f>B11-$O$8</f>
         <v/>
       </c>
@@ -1359,22 +1227,10 @@
         <v>8.880000000000001</v>
       </c>
       <c r="E12">
-        <f>IFERROR(MEDIAN(D2:D32),D12)</f>
+        <f>IF(AND(ISNUMBER(D12),D12&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F12">
-        <f>IF(OR(NOT(ISNUMBER(D12)),ABS(D12-E12)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G12">
-        <f>IF(F12=1,NA(),D12)</f>
-        <v/>
-      </c>
-      <c r="H12">
-        <f>IF(AND(ISNUMBER(D12),D12&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I12">
         <f>B12-$O$8</f>
         <v/>
       </c>
@@ -1395,22 +1251,10 @@
         <v>8.880000000000001</v>
       </c>
       <c r="E13">
-        <f>IFERROR(MEDIAN(D2:D33),D13)</f>
+        <f>IF(AND(ISNUMBER(D13),D13&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F13">
-        <f>IF(OR(NOT(ISNUMBER(D13)),ABS(D13-E13)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G13">
-        <f>IF(F13=1,NA(),D13)</f>
-        <v/>
-      </c>
-      <c r="H13">
-        <f>IF(AND(ISNUMBER(D13),D13&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I13">
         <f>B13-$O$8</f>
         <v/>
       </c>
@@ -1431,22 +1275,10 @@
         <v>8.16</v>
       </c>
       <c r="E14">
-        <f>IFERROR(MEDIAN(D2:D34),D14)</f>
+        <f>IF(AND(ISNUMBER(D14),D14&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F14">
-        <f>IF(OR(NOT(ISNUMBER(D14)),ABS(D14-E14)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G14">
-        <f>IF(F14=1,NA(),D14)</f>
-        <v/>
-      </c>
-      <c r="H14">
-        <f>IF(AND(ISNUMBER(D14),D14&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I14">
         <f>B14-$O$8</f>
         <v/>
       </c>
@@ -1467,22 +1299,10 @@
         <v>8.56</v>
       </c>
       <c r="E15">
-        <f>IFERROR(MEDIAN(D2:D35),D15)</f>
+        <f>IF(AND(ISNUMBER(D15),D15&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F15">
-        <f>IF(OR(NOT(ISNUMBER(D15)),ABS(D15-E15)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G15">
-        <f>IF(F15=1,NA(),D15)</f>
-        <v/>
-      </c>
-      <c r="H15">
-        <f>IF(AND(ISNUMBER(D15),D15&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I15">
         <f>B15-$O$8</f>
         <v/>
       </c>
@@ -1503,22 +1323,10 @@
         <v>11.18</v>
       </c>
       <c r="E16">
-        <f>IFERROR(MEDIAN(D2:D36),D16)</f>
+        <f>IF(AND(ISNUMBER(D16),D16&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F16">
-        <f>IF(OR(NOT(ISNUMBER(D16)),ABS(D16-E16)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G16">
-        <f>IF(F16=1,NA(),D16)</f>
-        <v/>
-      </c>
-      <c r="H16">
-        <f>IF(AND(ISNUMBER(D16),D16&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I16">
         <f>B16-$O$8</f>
         <v/>
       </c>
@@ -1539,22 +1347,10 @@
         <v>1.11</v>
       </c>
       <c r="E17">
-        <f>IFERROR(MEDIAN(D2:D37),D17)</f>
+        <f>IF(AND(ISNUMBER(D17),D17&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F17">
-        <f>IF(OR(NOT(ISNUMBER(D17)),ABS(D17-E17)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G17">
-        <f>IF(F17=1,NA(),D17)</f>
-        <v/>
-      </c>
-      <c r="H17">
-        <f>IF(AND(ISNUMBER(D17),D17&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I17">
         <f>B17-$O$8</f>
         <v/>
       </c>
@@ -1575,22 +1371,10 @@
         <v>2.56</v>
       </c>
       <c r="E18">
-        <f>IFERROR(MEDIAN(D2:D38),D18)</f>
+        <f>IF(AND(ISNUMBER(D18),D18&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F18">
-        <f>IF(OR(NOT(ISNUMBER(D18)),ABS(D18-E18)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G18">
-        <f>IF(F18=1,NA(),D18)</f>
-        <v/>
-      </c>
-      <c r="H18">
-        <f>IF(AND(ISNUMBER(D18),D18&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I18">
         <f>B18-$O$8</f>
         <v/>
       </c>
@@ -1611,22 +1395,10 @@
         <v>3.48</v>
       </c>
       <c r="E19">
-        <f>IFERROR(MEDIAN(D2:D39),D19)</f>
+        <f>IF(AND(ISNUMBER(D19),D19&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F19">
-        <f>IF(OR(NOT(ISNUMBER(D19)),ABS(D19-E19)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G19">
-        <f>IF(F19=1,NA(),D19)</f>
-        <v/>
-      </c>
-      <c r="H19">
-        <f>IF(AND(ISNUMBER(D19),D19&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I19">
         <f>B19-$O$8</f>
         <v/>
       </c>
@@ -1647,22 +1419,10 @@
         <v>4.51</v>
       </c>
       <c r="E20">
-        <f>IFERROR(MEDIAN(D2:D40),D20)</f>
+        <f>IF(AND(ISNUMBER(D20),D20&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F20">
-        <f>IF(OR(NOT(ISNUMBER(D20)),ABS(D20-E20)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G20">
-        <f>IF(F20=1,NA(),D20)</f>
-        <v/>
-      </c>
-      <c r="H20">
-        <f>IF(AND(ISNUMBER(D20),D20&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I20">
         <f>B20-$O$8</f>
         <v/>
       </c>
@@ -1683,22 +1443,10 @@
         <v>6.87</v>
       </c>
       <c r="E21">
-        <f>IFERROR(MEDIAN(D2:D41),D21)</f>
+        <f>IF(AND(ISNUMBER(D21),D21&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F21">
-        <f>IF(OR(NOT(ISNUMBER(D21)),ABS(D21-E21)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G21">
-        <f>IF(F21=1,NA(),D21)</f>
-        <v/>
-      </c>
-      <c r="H21">
-        <f>IF(AND(ISNUMBER(D21),D21&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I21">
         <f>B21-$O$8</f>
         <v/>
       </c>
@@ -1719,22 +1467,10 @@
         <v>6.99</v>
       </c>
       <c r="E22">
-        <f>IFERROR(MEDIAN(D2:D42),D22)</f>
+        <f>IF(AND(ISNUMBER(D22),D22&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F22">
-        <f>IF(OR(NOT(ISNUMBER(D22)),ABS(D22-E22)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G22">
-        <f>IF(F22=1,NA(),D22)</f>
-        <v/>
-      </c>
-      <c r="H22">
-        <f>IF(AND(ISNUMBER(D22),D22&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I22">
         <f>B22-$O$8</f>
         <v/>
       </c>
@@ -1755,22 +1491,10 @@
         <v>8.34</v>
       </c>
       <c r="E23">
-        <f>IFERROR(MEDIAN(D3:D43),D23)</f>
+        <f>IF(AND(ISNUMBER(D23),D23&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F23">
-        <f>IF(OR(NOT(ISNUMBER(D23)),ABS(D23-E23)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G23">
-        <f>IF(F23=1,NA(),D23)</f>
-        <v/>
-      </c>
-      <c r="H23">
-        <f>IF(AND(ISNUMBER(D23),D23&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I23">
         <f>B23-$O$8</f>
         <v/>
       </c>
@@ -1791,22 +1515,10 @@
         <v>9.890000000000001</v>
       </c>
       <c r="E24">
-        <f>IFERROR(MEDIAN(D4:D44),D24)</f>
+        <f>IF(AND(ISNUMBER(D24),D24&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F24">
-        <f>IF(OR(NOT(ISNUMBER(D24)),ABS(D24-E24)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G24">
-        <f>IF(F24=1,NA(),D24)</f>
-        <v/>
-      </c>
-      <c r="H24">
-        <f>IF(AND(ISNUMBER(D24),D24&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I24">
         <f>B24-$O$8</f>
         <v/>
       </c>
@@ -1827,22 +1539,10 @@
         <v>14.32</v>
       </c>
       <c r="E25">
-        <f>IFERROR(MEDIAN(D5:D45),D25)</f>
+        <f>IF(AND(ISNUMBER(D25),D25&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F25">
-        <f>IF(OR(NOT(ISNUMBER(D25)),ABS(D25-E25)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G25">
-        <f>IF(F25=1,NA(),D25)</f>
-        <v/>
-      </c>
-      <c r="H25">
-        <f>IF(AND(ISNUMBER(D25),D25&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I25">
         <f>B25-$O$8</f>
         <v/>
       </c>
@@ -1863,22 +1563,10 @@
         <v>12.87</v>
       </c>
       <c r="E26">
-        <f>IFERROR(MEDIAN(D6:D46),D26)</f>
+        <f>IF(AND(ISNUMBER(D26),D26&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F26">
-        <f>IF(OR(NOT(ISNUMBER(D26)),ABS(D26-E26)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G26">
-        <f>IF(F26=1,NA(),D26)</f>
-        <v/>
-      </c>
-      <c r="H26">
-        <f>IF(AND(ISNUMBER(D26),D26&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I26">
         <f>B26-$O$8</f>
         <v/>
       </c>
@@ -1899,22 +1587,10 @@
         <v>19.97</v>
       </c>
       <c r="E27">
-        <f>IFERROR(MEDIAN(D7:D47),D27)</f>
+        <f>IF(AND(ISNUMBER(D27),D27&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F27">
-        <f>IF(OR(NOT(ISNUMBER(D27)),ABS(D27-E27)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G27">
-        <f>IF(F27=1,NA(),D27)</f>
-        <v/>
-      </c>
-      <c r="H27">
-        <f>IF(AND(ISNUMBER(D27),D27&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I27">
         <f>B27-$O$8</f>
         <v/>
       </c>
@@ -1935,22 +1611,10 @@
         <v>15.26</v>
       </c>
       <c r="E28">
-        <f>IFERROR(MEDIAN(D8:D48),D28)</f>
+        <f>IF(AND(ISNUMBER(D28),D28&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F28">
-        <f>IF(OR(NOT(ISNUMBER(D28)),ABS(D28-E28)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G28">
-        <f>IF(F28=1,NA(),D28)</f>
-        <v/>
-      </c>
-      <c r="H28">
-        <f>IF(AND(ISNUMBER(D28),D28&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I28">
         <f>B28-$O$8</f>
         <v/>
       </c>
@@ -1971,22 +1635,10 @@
         <v>16.45</v>
       </c>
       <c r="E29">
-        <f>IFERROR(MEDIAN(D9:D49),D29)</f>
+        <f>IF(AND(ISNUMBER(D29),D29&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F29">
-        <f>IF(OR(NOT(ISNUMBER(D29)),ABS(D29-E29)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G29">
-        <f>IF(F29=1,NA(),D29)</f>
-        <v/>
-      </c>
-      <c r="H29">
-        <f>IF(AND(ISNUMBER(D29),D29&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I29">
         <f>B29-$O$8</f>
         <v/>
       </c>
@@ -2007,22 +1659,10 @@
         <v>19.82</v>
       </c>
       <c r="E30">
-        <f>IFERROR(MEDIAN(D10:D50),D30)</f>
+        <f>IF(AND(ISNUMBER(D30),D30&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F30">
-        <f>IF(OR(NOT(ISNUMBER(D30)),ABS(D30-E30)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G30">
-        <f>IF(F30=1,NA(),D30)</f>
-        <v/>
-      </c>
-      <c r="H30">
-        <f>IF(AND(ISNUMBER(D30),D30&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I30">
         <f>B30-$O$8</f>
         <v/>
       </c>
@@ -2043,22 +1683,10 @@
         <v>8.880000000000001</v>
       </c>
       <c r="E31">
-        <f>IFERROR(MEDIAN(D11:D51),D31)</f>
+        <f>IF(AND(ISNUMBER(D31),D31&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F31">
-        <f>IF(OR(NOT(ISNUMBER(D31)),ABS(D31-E31)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G31">
-        <f>IF(F31=1,NA(),D31)</f>
-        <v/>
-      </c>
-      <c r="H31">
-        <f>IF(AND(ISNUMBER(D31),D31&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I31">
         <f>B31-$O$8</f>
         <v/>
       </c>
@@ -2079,22 +1707,10 @@
         <v>28.98</v>
       </c>
       <c r="E32">
-        <f>IFERROR(MEDIAN(D12:D52),D32)</f>
+        <f>IF(AND(ISNUMBER(D32),D32&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F32">
-        <f>IF(OR(NOT(ISNUMBER(D32)),ABS(D32-E32)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G32">
-        <f>IF(F32=1,NA(),D32)</f>
-        <v/>
-      </c>
-      <c r="H32">
-        <f>IF(AND(ISNUMBER(D32),D32&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I32">
         <f>B32-$O$8</f>
         <v/>
       </c>
@@ -2112,22 +1728,10 @@
         </is>
       </c>
       <c r="E33">
-        <f>IFERROR(MEDIAN(D13:D53),D33)</f>
+        <f>IF(AND(ISNUMBER(D33),D33&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F33">
-        <f>IF(OR(NOT(ISNUMBER(D33)),ABS(D33-E33)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G33">
-        <f>IF(F33=1,NA(),D33)</f>
-        <v/>
-      </c>
-      <c r="H33">
-        <f>IF(AND(ISNUMBER(D33),D33&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I33">
         <f>B33-$O$8</f>
         <v/>
       </c>
@@ -2145,22 +1749,10 @@
         </is>
       </c>
       <c r="E34">
-        <f>IFERROR(MEDIAN(D14:D54),D34)</f>
+        <f>IF(AND(ISNUMBER(D34),D34&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F34">
-        <f>IF(OR(NOT(ISNUMBER(D34)),ABS(D34-E34)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G34">
-        <f>IF(F34=1,NA(),D34)</f>
-        <v/>
-      </c>
-      <c r="H34">
-        <f>IF(AND(ISNUMBER(D34),D34&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I34">
         <f>B34-$O$8</f>
         <v/>
       </c>
@@ -2181,22 +1773,10 @@
         <v>29.85</v>
       </c>
       <c r="E35">
-        <f>IFERROR(MEDIAN(D15:D55),D35)</f>
+        <f>IF(AND(ISNUMBER(D35),D35&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F35">
-        <f>IF(OR(NOT(ISNUMBER(D35)),ABS(D35-E35)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G35">
-        <f>IF(F35=1,NA(),D35)</f>
-        <v/>
-      </c>
-      <c r="H35">
-        <f>IF(AND(ISNUMBER(D35),D35&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I35">
         <f>B35-$O$8</f>
         <v/>
       </c>
@@ -2217,22 +1797,10 @@
         <v>28.88</v>
       </c>
       <c r="E36">
-        <f>IFERROR(MEDIAN(D16:D56),D36)</f>
+        <f>IF(AND(ISNUMBER(D36),D36&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F36">
-        <f>IF(OR(NOT(ISNUMBER(D36)),ABS(D36-E36)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G36">
-        <f>IF(F36=1,NA(),D36)</f>
-        <v/>
-      </c>
-      <c r="H36">
-        <f>IF(AND(ISNUMBER(D36),D36&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I36">
         <f>B36-$O$8</f>
         <v/>
       </c>
@@ -2253,22 +1821,10 @@
         <v>28.82</v>
       </c>
       <c r="E37">
-        <f>IFERROR(MEDIAN(D17:D57),D37)</f>
+        <f>IF(AND(ISNUMBER(D37),D37&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F37">
-        <f>IF(OR(NOT(ISNUMBER(D37)),ABS(D37-E37)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G37">
-        <f>IF(F37=1,NA(),D37)</f>
-        <v/>
-      </c>
-      <c r="H37">
-        <f>IF(AND(ISNUMBER(D37),D37&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I37">
         <f>B37-$O$8</f>
         <v/>
       </c>
@@ -2286,22 +1842,10 @@
         </is>
       </c>
       <c r="E38">
-        <f>IFERROR(MEDIAN(D18:D58),D38)</f>
+        <f>IF(AND(ISNUMBER(D38),D38&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F38">
-        <f>IF(OR(NOT(ISNUMBER(D38)),ABS(D38-E38)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G38">
-        <f>IF(F38=1,NA(),D38)</f>
-        <v/>
-      </c>
-      <c r="H38">
-        <f>IF(AND(ISNUMBER(D38),D38&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I38">
         <f>B38-$O$8</f>
         <v/>
       </c>
@@ -2322,22 +1866,10 @@
         <v>28.26</v>
       </c>
       <c r="E39">
-        <f>IFERROR(MEDIAN(D19:D59),D39)</f>
+        <f>IF(AND(ISNUMBER(D39),D39&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F39">
-        <f>IF(OR(NOT(ISNUMBER(D39)),ABS(D39-E39)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G39">
-        <f>IF(F39=1,NA(),D39)</f>
-        <v/>
-      </c>
-      <c r="H39">
-        <f>IF(AND(ISNUMBER(D39),D39&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I39">
         <f>B39-$O$8</f>
         <v/>
       </c>
@@ -2358,22 +1890,10 @@
         <v>28.98</v>
       </c>
       <c r="E40">
-        <f>IFERROR(MEDIAN(D20:D60),D40)</f>
+        <f>IF(AND(ISNUMBER(D40),D40&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F40">
-        <f>IF(OR(NOT(ISNUMBER(D40)),ABS(D40-E40)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G40">
-        <f>IF(F40=1,NA(),D40)</f>
-        <v/>
-      </c>
-      <c r="H40">
-        <f>IF(AND(ISNUMBER(D40),D40&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I40">
         <f>B40-$O$8</f>
         <v/>
       </c>
@@ -2394,22 +1914,10 @@
         <v>30.48</v>
       </c>
       <c r="E41">
-        <f>IFERROR(MEDIAN(D21:D61),D41)</f>
+        <f>IF(AND(ISNUMBER(D41),D41&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F41">
-        <f>IF(OR(NOT(ISNUMBER(D41)),ABS(D41-E41)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G41">
-        <f>IF(F41=1,NA(),D41)</f>
-        <v/>
-      </c>
-      <c r="H41">
-        <f>IF(AND(ISNUMBER(D41),D41&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I41">
         <f>B41-$O$8</f>
         <v/>
       </c>
@@ -2427,22 +1935,10 @@
         </is>
       </c>
       <c r="E42">
-        <f>IFERROR(MEDIAN(D22:D62),D42)</f>
+        <f>IF(AND(ISNUMBER(D42),D42&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F42">
-        <f>IF(OR(NOT(ISNUMBER(D42)),ABS(D42-E42)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G42">
-        <f>IF(F42=1,NA(),D42)</f>
-        <v/>
-      </c>
-      <c r="H42">
-        <f>IF(AND(ISNUMBER(D42),D42&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I42">
         <f>B42-$O$8</f>
         <v/>
       </c>
@@ -2463,22 +1959,10 @@
         <v>32.62</v>
       </c>
       <c r="E43">
-        <f>IFERROR(MEDIAN(D23:D63),D43)</f>
+        <f>IF(AND(ISNUMBER(D43),D43&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F43">
-        <f>IF(OR(NOT(ISNUMBER(D43)),ABS(D43-E43)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G43">
-        <f>IF(F43=1,NA(),D43)</f>
-        <v/>
-      </c>
-      <c r="H43">
-        <f>IF(AND(ISNUMBER(D43),D43&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I43">
         <f>B43-$O$8</f>
         <v/>
       </c>
@@ -2499,22 +1983,10 @@
         <v>39.82</v>
       </c>
       <c r="E44">
-        <f>IFERROR(MEDIAN(D24:D64),D44)</f>
+        <f>IF(AND(ISNUMBER(D44),D44&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F44">
-        <f>IF(OR(NOT(ISNUMBER(D44)),ABS(D44-E44)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G44">
-        <f>IF(F44=1,NA(),D44)</f>
-        <v/>
-      </c>
-      <c r="H44">
-        <f>IF(AND(ISNUMBER(D44),D44&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I44">
         <f>B44-$O$8</f>
         <v/>
       </c>
@@ -2535,22 +2007,10 @@
         <v>39.72</v>
       </c>
       <c r="E45">
-        <f>IFERROR(MEDIAN(D25:D65),D45)</f>
+        <f>IF(AND(ISNUMBER(D45),D45&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F45">
-        <f>IF(OR(NOT(ISNUMBER(D45)),ABS(D45-E45)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G45">
-        <f>IF(F45=1,NA(),D45)</f>
-        <v/>
-      </c>
-      <c r="H45">
-        <f>IF(AND(ISNUMBER(D45),D45&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I45">
         <f>B45-$O$8</f>
         <v/>
       </c>
@@ -2571,22 +2031,10 @@
         <v>36.8</v>
       </c>
       <c r="E46">
-        <f>IFERROR(MEDIAN(D26:D66),D46)</f>
+        <f>IF(AND(ISNUMBER(D46),D46&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F46">
-        <f>IF(OR(NOT(ISNUMBER(D46)),ABS(D46-E46)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G46">
-        <f>IF(F46=1,NA(),D46)</f>
-        <v/>
-      </c>
-      <c r="H46">
-        <f>IF(AND(ISNUMBER(D46),D46&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I46">
         <f>B46-$O$8</f>
         <v/>
       </c>
@@ -2607,22 +2055,10 @@
         <v>36.88</v>
       </c>
       <c r="E47">
-        <f>IFERROR(MEDIAN(D27:D67),D47)</f>
+        <f>IF(AND(ISNUMBER(D47),D47&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F47">
-        <f>IF(OR(NOT(ISNUMBER(D47)),ABS(D47-E47)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G47">
-        <f>IF(F47=1,NA(),D47)</f>
-        <v/>
-      </c>
-      <c r="H47">
-        <f>IF(AND(ISNUMBER(D47),D47&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I47">
         <f>B47-$O$8</f>
         <v/>
       </c>
@@ -2643,22 +2079,10 @@
         <v>38.82</v>
       </c>
       <c r="E48">
-        <f>IFERROR(MEDIAN(D28:D68),D48)</f>
+        <f>IF(AND(ISNUMBER(D48),D48&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F48">
-        <f>IF(OR(NOT(ISNUMBER(D48)),ABS(D48-E48)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G48">
-        <f>IF(F48=1,NA(),D48)</f>
-        <v/>
-      </c>
-      <c r="H48">
-        <f>IF(AND(ISNUMBER(D48),D48&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I48">
         <f>B48-$O$8</f>
         <v/>
       </c>
@@ -2679,22 +2103,10 @@
         <v>38.82</v>
       </c>
       <c r="E49">
-        <f>IFERROR(MEDIAN(D29:D69),D49)</f>
+        <f>IF(AND(ISNUMBER(D49),D49&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F49">
-        <f>IF(OR(NOT(ISNUMBER(D49)),ABS(D49-E49)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G49">
-        <f>IF(F49=1,NA(),D49)</f>
-        <v/>
-      </c>
-      <c r="H49">
-        <f>IF(AND(ISNUMBER(D49),D49&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I49">
         <f>B49-$O$8</f>
         <v/>
       </c>
@@ -2715,22 +2127,10 @@
         <v>98.88</v>
       </c>
       <c r="E50">
-        <f>IFERROR(MEDIAN(D30:D70),D50)</f>
+        <f>IF(AND(ISNUMBER(D50),D50&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F50">
-        <f>IF(OR(NOT(ISNUMBER(D50)),ABS(D50-E50)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G50">
-        <f>IF(F50=1,NA(),D50)</f>
-        <v/>
-      </c>
-      <c r="H50">
-        <f>IF(AND(ISNUMBER(D50),D50&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I50">
         <f>B50-$O$8</f>
         <v/>
       </c>
@@ -2751,22 +2151,10 @@
         <v>40.88</v>
       </c>
       <c r="E51">
-        <f>IFERROR(MEDIAN(D31:D71),D51)</f>
+        <f>IF(AND(ISNUMBER(D51),D51&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F51">
-        <f>IF(OR(NOT(ISNUMBER(D51)),ABS(D51-E51)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G51">
-        <f>IF(F51=1,NA(),D51)</f>
-        <v/>
-      </c>
-      <c r="H51">
-        <f>IF(AND(ISNUMBER(D51),D51&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I51">
         <f>B51-$O$8</f>
         <v/>
       </c>
@@ -2784,22 +2172,10 @@
         </is>
       </c>
       <c r="E52">
-        <f>IFERROR(MEDIAN(D32:D72),D52)</f>
+        <f>IF(AND(ISNUMBER(D52),D52&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F52">
-        <f>IF(OR(NOT(ISNUMBER(D52)),ABS(D52-E52)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G52">
-        <f>IF(F52=1,NA(),D52)</f>
-        <v/>
-      </c>
-      <c r="H52">
-        <f>IF(AND(ISNUMBER(D52),D52&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I52">
         <f>B52-$O$8</f>
         <v/>
       </c>
@@ -2817,22 +2193,10 @@
         </is>
       </c>
       <c r="E53">
-        <f>IFERROR(MEDIAN(D33:D73),D53)</f>
+        <f>IF(AND(ISNUMBER(D53),D53&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F53">
-        <f>IF(OR(NOT(ISNUMBER(D53)),ABS(D53-E53)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G53">
-        <f>IF(F53=1,NA(),D53)</f>
-        <v/>
-      </c>
-      <c r="H53">
-        <f>IF(AND(ISNUMBER(D53),D53&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I53">
         <f>B53-$O$8</f>
         <v/>
       </c>
@@ -2853,22 +2217,10 @@
         <v>49.69</v>
       </c>
       <c r="E54">
-        <f>IFERROR(MEDIAN(D34:D74),D54)</f>
+        <f>IF(AND(ISNUMBER(D54),D54&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F54">
-        <f>IF(OR(NOT(ISNUMBER(D54)),ABS(D54-E54)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G54">
-        <f>IF(F54=1,NA(),D54)</f>
-        <v/>
-      </c>
-      <c r="H54">
-        <f>IF(AND(ISNUMBER(D54),D54&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I54">
         <f>B54-$O$8</f>
         <v/>
       </c>
@@ -2889,22 +2241,10 @@
         <v>44.98</v>
       </c>
       <c r="E55">
-        <f>IFERROR(MEDIAN(D35:D75),D55)</f>
+        <f>IF(AND(ISNUMBER(D55),D55&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F55">
-        <f>IF(OR(NOT(ISNUMBER(D55)),ABS(D55-E55)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G55">
-        <f>IF(F55=1,NA(),D55)</f>
-        <v/>
-      </c>
-      <c r="H55">
-        <f>IF(AND(ISNUMBER(D55),D55&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I55">
         <f>B55-$O$8</f>
         <v/>
       </c>
@@ -2925,22 +2265,10 @@
         <v>46.98</v>
       </c>
       <c r="E56">
-        <f>IFERROR(MEDIAN(D36:D76),D56)</f>
+        <f>IF(AND(ISNUMBER(D56),D56&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F56">
-        <f>IF(OR(NOT(ISNUMBER(D56)),ABS(D56-E56)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G56">
-        <f>IF(F56=1,NA(),D56)</f>
-        <v/>
-      </c>
-      <c r="H56">
-        <f>IF(AND(ISNUMBER(D56),D56&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I56">
         <f>B56-$O$8</f>
         <v/>
       </c>
@@ -2961,22 +2289,10 @@
         <v>48.28</v>
       </c>
       <c r="E57">
-        <f>IFERROR(MEDIAN(D37:D77),D57)</f>
+        <f>IF(AND(ISNUMBER(D57),D57&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F57">
-        <f>IF(OR(NOT(ISNUMBER(D57)),ABS(D57-E57)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G57">
-        <f>IF(F57=1,NA(),D57)</f>
-        <v/>
-      </c>
-      <c r="H57">
-        <f>IF(AND(ISNUMBER(D57),D57&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I57">
         <f>B57-$O$8</f>
         <v/>
       </c>
@@ -2997,22 +2313,10 @@
         <v>48.28</v>
       </c>
       <c r="E58">
-        <f>IFERROR(MEDIAN(D38:D78),D58)</f>
+        <f>IF(AND(ISNUMBER(D58),D58&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F58">
-        <f>IF(OR(NOT(ISNUMBER(D58)),ABS(D58-E58)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G58">
-        <f>IF(F58=1,NA(),D58)</f>
-        <v/>
-      </c>
-      <c r="H58">
-        <f>IF(AND(ISNUMBER(D58),D58&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I58">
         <f>B58-$O$8</f>
         <v/>
       </c>
@@ -3033,22 +2337,10 @@
         <v>48.98</v>
       </c>
       <c r="E59">
-        <f>IFERROR(MEDIAN(D39:D79),D59)</f>
+        <f>IF(AND(ISNUMBER(D59),D59&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F59">
-        <f>IF(OR(NOT(ISNUMBER(D59)),ABS(D59-E59)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G59">
-        <f>IF(F59=1,NA(),D59)</f>
-        <v/>
-      </c>
-      <c r="H59">
-        <f>IF(AND(ISNUMBER(D59),D59&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I59">
         <f>B59-$O$8</f>
         <v/>
       </c>
@@ -3069,22 +2361,10 @@
         <v>48.88</v>
       </c>
       <c r="E60">
-        <f>IFERROR(MEDIAN(D40:D80),D60)</f>
+        <f>IF(AND(ISNUMBER(D60),D60&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F60">
-        <f>IF(OR(NOT(ISNUMBER(D60)),ABS(D60-E60)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G60">
-        <f>IF(F60=1,NA(),D60)</f>
-        <v/>
-      </c>
-      <c r="H60">
-        <f>IF(AND(ISNUMBER(D60),D60&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I60">
         <f>B60-$O$8</f>
         <v/>
       </c>
@@ -3105,22 +2385,10 @@
         <v>98.88</v>
       </c>
       <c r="E61">
-        <f>IFERROR(MEDIAN(D41:D81),D61)</f>
+        <f>IF(AND(ISNUMBER(D61),D61&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F61">
-        <f>IF(OR(NOT(ISNUMBER(D61)),ABS(D61-E61)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G61">
-        <f>IF(F61=1,NA(),D61)</f>
-        <v/>
-      </c>
-      <c r="H61">
-        <f>IF(AND(ISNUMBER(D61),D61&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I61">
         <f>B61-$O$8</f>
         <v/>
       </c>
@@ -3141,22 +2409,10 @@
         <v>50.88</v>
       </c>
       <c r="E62">
-        <f>IFERROR(MEDIAN(D42:D82),D62)</f>
+        <f>IF(AND(ISNUMBER(D62),D62&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F62">
-        <f>IF(OR(NOT(ISNUMBER(D62)),ABS(D62-E62)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G62">
-        <f>IF(F62=1,NA(),D62)</f>
-        <v/>
-      </c>
-      <c r="H62">
-        <f>IF(AND(ISNUMBER(D62),D62&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I62">
         <f>B62-$O$8</f>
         <v/>
       </c>
@@ -3177,22 +2433,10 @@
         <v>52.88</v>
       </c>
       <c r="E63">
-        <f>IFERROR(MEDIAN(D43:D83),D63)</f>
+        <f>IF(AND(ISNUMBER(D63),D63&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F63">
-        <f>IF(OR(NOT(ISNUMBER(D63)),ABS(D63-E63)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G63">
-        <f>IF(F63=1,NA(),D63)</f>
-        <v/>
-      </c>
-      <c r="H63">
-        <f>IF(AND(ISNUMBER(D63),D63&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I63">
         <f>B63-$O$8</f>
         <v/>
       </c>
@@ -3210,22 +2454,10 @@
         </is>
       </c>
       <c r="E64">
-        <f>IFERROR(MEDIAN(D44:D84),D64)</f>
+        <f>IF(AND(ISNUMBER(D64),D64&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F64">
-        <f>IF(OR(NOT(ISNUMBER(D64)),ABS(D64-E64)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G64">
-        <f>IF(F64=1,NA(),D64)</f>
-        <v/>
-      </c>
-      <c r="H64">
-        <f>IF(AND(ISNUMBER(D64),D64&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I64">
         <f>B64-$O$8</f>
         <v/>
       </c>
@@ -3246,22 +2478,10 @@
         <v>53.88</v>
       </c>
       <c r="E65">
-        <f>IFERROR(MEDIAN(D45:D85),D65)</f>
+        <f>IF(AND(ISNUMBER(D65),D65&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F65">
-        <f>IF(OR(NOT(ISNUMBER(D65)),ABS(D65-E65)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G65">
-        <f>IF(F65=1,NA(),D65)</f>
-        <v/>
-      </c>
-      <c r="H65">
-        <f>IF(AND(ISNUMBER(D65),D65&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I65">
         <f>B65-$O$8</f>
         <v/>
       </c>
@@ -3282,22 +2502,10 @@
         <v>59.88</v>
       </c>
       <c r="E66">
-        <f>IFERROR(MEDIAN(D46:D86),D66)</f>
+        <f>IF(AND(ISNUMBER(D66),D66&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F66">
-        <f>IF(OR(NOT(ISNUMBER(D66)),ABS(D66-E66)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G66">
-        <f>IF(F66=1,NA(),D66)</f>
-        <v/>
-      </c>
-      <c r="H66">
-        <f>IF(AND(ISNUMBER(D66),D66&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I66">
         <f>B66-$O$8</f>
         <v/>
       </c>
@@ -3318,22 +2526,10 @@
         <v>55.88</v>
       </c>
       <c r="E67">
-        <f>IFERROR(MEDIAN(D47:D87),D67)</f>
+        <f>IF(AND(ISNUMBER(D67),D67&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F67">
-        <f>IF(OR(NOT(ISNUMBER(D67)),ABS(D67-E67)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G67">
-        <f>IF(F67=1,NA(),D67)</f>
-        <v/>
-      </c>
-      <c r="H67">
-        <f>IF(AND(ISNUMBER(D67),D67&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I67">
         <f>B67-$O$8</f>
         <v/>
       </c>
@@ -3354,22 +2550,10 @@
         <v>56.89</v>
       </c>
       <c r="E68">
-        <f>IFERROR(MEDIAN(D48:D88),D68)</f>
+        <f>IF(AND(ISNUMBER(D68),D68&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F68">
-        <f>IF(OR(NOT(ISNUMBER(D68)),ABS(D68-E68)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G68">
-        <f>IF(F68=1,NA(),D68)</f>
-        <v/>
-      </c>
-      <c r="H68">
-        <f>IF(AND(ISNUMBER(D68),D68&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I68">
         <f>B68-$O$8</f>
         <v/>
       </c>
@@ -3390,22 +2574,10 @@
         <v>56.89</v>
       </c>
       <c r="E69">
-        <f>IFERROR(MEDIAN(D49:D89),D69)</f>
+        <f>IF(AND(ISNUMBER(D69),D69&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F69">
-        <f>IF(OR(NOT(ISNUMBER(D69)),ABS(D69-E69)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G69">
-        <f>IF(F69=1,NA(),D69)</f>
-        <v/>
-      </c>
-      <c r="H69">
-        <f>IF(AND(ISNUMBER(D69),D69&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I69">
         <f>B69-$O$8</f>
         <v/>
       </c>
@@ -3426,22 +2598,10 @@
         <v>58.81</v>
       </c>
       <c r="E70">
-        <f>IFERROR(MEDIAN(D50:D90),D70)</f>
+        <f>IF(AND(ISNUMBER(D70),D70&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F70">
-        <f>IF(OR(NOT(ISNUMBER(D70)),ABS(D70-E70)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G70">
-        <f>IF(F70=1,NA(),D70)</f>
-        <v/>
-      </c>
-      <c r="H70">
-        <f>IF(AND(ISNUMBER(D70),D70&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I70">
         <f>B70-$O$8</f>
         <v/>
       </c>
@@ -3462,22 +2622,10 @@
         <v>58.99</v>
       </c>
       <c r="E71">
-        <f>IFERROR(MEDIAN(D51:D91),D71)</f>
+        <f>IF(AND(ISNUMBER(D71),D71&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F71">
-        <f>IF(OR(NOT(ISNUMBER(D71)),ABS(D71-E71)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G71">
-        <f>IF(F71=1,NA(),D71)</f>
-        <v/>
-      </c>
-      <c r="H71">
-        <f>IF(AND(ISNUMBER(D71),D71&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I71">
         <f>B71-$O$8</f>
         <v/>
       </c>
@@ -3498,22 +2646,10 @@
         <v>58.89</v>
       </c>
       <c r="E72">
-        <f>IFERROR(MEDIAN(D52:D92),D72)</f>
+        <f>IF(AND(ISNUMBER(D72),D72&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F72">
-        <f>IF(OR(NOT(ISNUMBER(D72)),ABS(D72-E72)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G72">
-        <f>IF(F72=1,NA(),D72)</f>
-        <v/>
-      </c>
-      <c r="H72">
-        <f>IF(AND(ISNUMBER(D72),D72&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I72">
         <f>B72-$O$8</f>
         <v/>
       </c>
@@ -3534,22 +2670,10 @@
         <v>58.83</v>
       </c>
       <c r="E73">
-        <f>IFERROR(MEDIAN(D53:D93),D73)</f>
+        <f>IF(AND(ISNUMBER(D73),D73&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F73">
-        <f>IF(OR(NOT(ISNUMBER(D73)),ABS(D73-E73)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G73">
-        <f>IF(F73=1,NA(),D73)</f>
-        <v/>
-      </c>
-      <c r="H73">
-        <f>IF(AND(ISNUMBER(D73),D73&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I73">
         <f>B73-$O$8</f>
         <v/>
       </c>
@@ -3570,22 +2694,10 @@
         <v>54.93</v>
       </c>
       <c r="E74">
-        <f>IFERROR(MEDIAN(D54:D94),D74)</f>
+        <f>IF(AND(ISNUMBER(D74),D74&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F74">
-        <f>IF(OR(NOT(ISNUMBER(D74)),ABS(D74-E74)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G74">
-        <f>IF(F74=1,NA(),D74)</f>
-        <v/>
-      </c>
-      <c r="H74">
-        <f>IF(AND(ISNUMBER(D74),D74&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I74">
         <f>B74-$O$8</f>
         <v/>
       </c>
@@ -3606,22 +2718,10 @@
         <v>68.43000000000001</v>
       </c>
       <c r="E75">
-        <f>IFERROR(MEDIAN(D55:D95),D75)</f>
+        <f>IF(AND(ISNUMBER(D75),D75&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F75">
-        <f>IF(OR(NOT(ISNUMBER(D75)),ABS(D75-E75)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G75">
-        <f>IF(F75=1,NA(),D75)</f>
-        <v/>
-      </c>
-      <c r="H75">
-        <f>IF(AND(ISNUMBER(D75),D75&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I75">
         <f>B75-$O$8</f>
         <v/>
       </c>
@@ -3642,22 +2742,10 @@
         <v>60.83</v>
       </c>
       <c r="E76">
-        <f>IFERROR(MEDIAN(D56:D96),D76)</f>
+        <f>IF(AND(ISNUMBER(D76),D76&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F76">
-        <f>IF(OR(NOT(ISNUMBER(D76)),ABS(D76-E76)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G76">
-        <f>IF(F76=1,NA(),D76)</f>
-        <v/>
-      </c>
-      <c r="H76">
-        <f>IF(AND(ISNUMBER(D76),D76&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I76">
         <f>B76-$O$8</f>
         <v/>
       </c>
@@ -3678,22 +2766,10 @@
         <v>60.88</v>
       </c>
       <c r="E77">
-        <f>IFERROR(MEDIAN(D57:D97),D77)</f>
+        <f>IF(AND(ISNUMBER(D77),D77&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F77">
-        <f>IF(OR(NOT(ISNUMBER(D77)),ABS(D77-E77)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G77">
-        <f>IF(F77=1,NA(),D77)</f>
-        <v/>
-      </c>
-      <c r="H77">
-        <f>IF(AND(ISNUMBER(D77),D77&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I77">
         <f>B77-$O$8</f>
         <v/>
       </c>
@@ -3714,22 +2790,10 @@
         <v>61.48</v>
       </c>
       <c r="E78">
-        <f>IFERROR(MEDIAN(D58:D98),D78)</f>
+        <f>IF(AND(ISNUMBER(D78),D78&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F78">
-        <f>IF(OR(NOT(ISNUMBER(D78)),ABS(D78-E78)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G78">
-        <f>IF(F78=1,NA(),D78)</f>
-        <v/>
-      </c>
-      <c r="H78">
-        <f>IF(AND(ISNUMBER(D78),D78&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I78">
         <f>B78-$O$8</f>
         <v/>
       </c>
@@ -3750,22 +2814,10 @@
         <v>61.88</v>
       </c>
       <c r="E79">
-        <f>IFERROR(MEDIAN(D59:D99),D79)</f>
+        <f>IF(AND(ISNUMBER(D79),D79&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F79">
-        <f>IF(OR(NOT(ISNUMBER(D79)),ABS(D79-E79)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G79">
-        <f>IF(F79=1,NA(),D79)</f>
-        <v/>
-      </c>
-      <c r="H79">
-        <f>IF(AND(ISNUMBER(D79),D79&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I79">
         <f>B79-$O$8</f>
         <v/>
       </c>
@@ -3786,22 +2838,10 @@
         <v>61.89</v>
       </c>
       <c r="E80">
-        <f>IFERROR(MEDIAN(D60:D100),D80)</f>
+        <f>IF(AND(ISNUMBER(D80),D80&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F80">
-        <f>IF(OR(NOT(ISNUMBER(D80)),ABS(D80-E80)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G80">
-        <f>IF(F80=1,NA(),D80)</f>
-        <v/>
-      </c>
-      <c r="H80">
-        <f>IF(AND(ISNUMBER(D80),D80&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I80">
         <f>B80-$O$8</f>
         <v/>
       </c>
@@ -3822,22 +2862,10 @@
         <v>61.88</v>
       </c>
       <c r="E81">
-        <f>IFERROR(MEDIAN(D61:D101),D81)</f>
+        <f>IF(AND(ISNUMBER(D81),D81&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F81">
-        <f>IF(OR(NOT(ISNUMBER(D81)),ABS(D81-E81)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G81">
-        <f>IF(F81=1,NA(),D81)</f>
-        <v/>
-      </c>
-      <c r="H81">
-        <f>IF(AND(ISNUMBER(D81),D81&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I81">
         <f>B81-$O$8</f>
         <v/>
       </c>
@@ -3858,22 +2886,10 @@
         <v>62.88</v>
       </c>
       <c r="E82">
-        <f>IFERROR(MEDIAN(D62:D102),D82)</f>
+        <f>IF(AND(ISNUMBER(D82),D82&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F82">
-        <f>IF(OR(NOT(ISNUMBER(D82)),ABS(D82-E82)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G82">
-        <f>IF(F82=1,NA(),D82)</f>
-        <v/>
-      </c>
-      <c r="H82">
-        <f>IF(AND(ISNUMBER(D82),D82&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I82">
         <f>B82-$O$8</f>
         <v/>
       </c>
@@ -3894,22 +2910,10 @@
         <v>62.85</v>
       </c>
       <c r="E83">
-        <f>IFERROR(MEDIAN(D63:D103),D83)</f>
+        <f>IF(AND(ISNUMBER(D83),D83&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F83">
-        <f>IF(OR(NOT(ISNUMBER(D83)),ABS(D83-E83)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G83">
-        <f>IF(F83=1,NA(),D83)</f>
-        <v/>
-      </c>
-      <c r="H83">
-        <f>IF(AND(ISNUMBER(D83),D83&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I83">
         <f>B83-$O$8</f>
         <v/>
       </c>
@@ -3930,22 +2934,10 @@
         <v>62.86</v>
       </c>
       <c r="E84">
-        <f>IFERROR(MEDIAN(D64:D104),D84)</f>
+        <f>IF(AND(ISNUMBER(D84),D84&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F84">
-        <f>IF(OR(NOT(ISNUMBER(D84)),ABS(D84-E84)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G84">
-        <f>IF(F84=1,NA(),D84)</f>
-        <v/>
-      </c>
-      <c r="H84">
-        <f>IF(AND(ISNUMBER(D84),D84&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I84">
         <f>B84-$O$8</f>
         <v/>
       </c>
@@ -3966,22 +2958,10 @@
         <v>62.88</v>
       </c>
       <c r="E85">
-        <f>IFERROR(MEDIAN(D65:D105),D85)</f>
+        <f>IF(AND(ISNUMBER(D85),D85&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F85">
-        <f>IF(OR(NOT(ISNUMBER(D85)),ABS(D85-E85)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G85">
-        <f>IF(F85=1,NA(),D85)</f>
-        <v/>
-      </c>
-      <c r="H85">
-        <f>IF(AND(ISNUMBER(D85),D85&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I85">
         <f>B85-$O$8</f>
         <v/>
       </c>
@@ -4002,22 +2982,10 @@
         <v>62.07</v>
       </c>
       <c r="E86">
-        <f>IFERROR(MEDIAN(D66:D106),D86)</f>
+        <f>IF(AND(ISNUMBER(D86),D86&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F86">
-        <f>IF(OR(NOT(ISNUMBER(D86)),ABS(D86-E86)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G86">
-        <f>IF(F86=1,NA(),D86)</f>
-        <v/>
-      </c>
-      <c r="H86">
-        <f>IF(AND(ISNUMBER(D86),D86&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I86">
         <f>B86-$O$8</f>
         <v/>
       </c>
@@ -4038,22 +3006,10 @@
         <v>62.88</v>
       </c>
       <c r="E87">
-        <f>IFERROR(MEDIAN(D67:D107),D87)</f>
+        <f>IF(AND(ISNUMBER(D87),D87&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F87">
-        <f>IF(OR(NOT(ISNUMBER(D87)),ABS(D87-E87)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G87">
-        <f>IF(F87=1,NA(),D87)</f>
-        <v/>
-      </c>
-      <c r="H87">
-        <f>IF(AND(ISNUMBER(D87),D87&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I87">
         <f>B87-$O$8</f>
         <v/>
       </c>
@@ -4074,22 +3030,10 @@
         <v>621.1799999999999</v>
       </c>
       <c r="E88">
-        <f>IFERROR(MEDIAN(D68:D108),D88)</f>
+        <f>IF(AND(ISNUMBER(D88),D88&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F88">
-        <f>IF(OR(NOT(ISNUMBER(D88)),ABS(D88-E88)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G88">
-        <f>IF(F88=1,NA(),D88)</f>
-        <v/>
-      </c>
-      <c r="H88">
-        <f>IF(AND(ISNUMBER(D88),D88&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I88">
         <f>B88-$O$8</f>
         <v/>
       </c>
@@ -4110,22 +3054,10 @@
         <v>621.11</v>
       </c>
       <c r="E89">
-        <f>IFERROR(MEDIAN(D69:D109),D89)</f>
+        <f>IF(AND(ISNUMBER(D89),D89&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F89">
-        <f>IF(OR(NOT(ISNUMBER(D89)),ABS(D89-E89)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G89">
-        <f>IF(F89=1,NA(),D89)</f>
-        <v/>
-      </c>
-      <c r="H89">
-        <f>IF(AND(ISNUMBER(D89),D89&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I89">
         <f>B89-$O$8</f>
         <v/>
       </c>
@@ -4146,22 +3078,10 @@
         <v>62.17</v>
       </c>
       <c r="E90">
-        <f>IFERROR(MEDIAN(D70:D110),D90)</f>
+        <f>IF(AND(ISNUMBER(D90),D90&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F90">
-        <f>IF(OR(NOT(ISNUMBER(D90)),ABS(D90-E90)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G90">
-        <f>IF(F90=1,NA(),D90)</f>
-        <v/>
-      </c>
-      <c r="H90">
-        <f>IF(AND(ISNUMBER(D90),D90&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I90">
         <f>B90-$O$8</f>
         <v/>
       </c>
@@ -4182,22 +3102,10 @@
         <v>62.17</v>
       </c>
       <c r="E91">
-        <f>IFERROR(MEDIAN(D71:D111),D91)</f>
+        <f>IF(AND(ISNUMBER(D91),D91&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F91">
-        <f>IF(OR(NOT(ISNUMBER(D91)),ABS(D91-E91)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G91">
-        <f>IF(F91=1,NA(),D91)</f>
-        <v/>
-      </c>
-      <c r="H91">
-        <f>IF(AND(ISNUMBER(D91),D91&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I91">
         <f>B91-$O$8</f>
         <v/>
       </c>
@@ -4218,22 +3126,10 @@
         <v>62.17</v>
       </c>
       <c r="E92">
-        <f>IFERROR(MEDIAN(D72:D112),D92)</f>
+        <f>IF(AND(ISNUMBER(D92),D92&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F92">
-        <f>IF(OR(NOT(ISNUMBER(D92)),ABS(D92-E92)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G92">
-        <f>IF(F92=1,NA(),D92)</f>
-        <v/>
-      </c>
-      <c r="H92">
-        <f>IF(AND(ISNUMBER(D92),D92&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I92">
         <f>B92-$O$8</f>
         <v/>
       </c>
@@ -4254,22 +3150,10 @@
         <v>62.17</v>
       </c>
       <c r="E93">
-        <f>IFERROR(MEDIAN(D73:D113),D93)</f>
+        <f>IF(AND(ISNUMBER(D93),D93&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F93">
-        <f>IF(OR(NOT(ISNUMBER(D93)),ABS(D93-E93)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G93">
-        <f>IF(F93=1,NA(),D93)</f>
-        <v/>
-      </c>
-      <c r="H93">
-        <f>IF(AND(ISNUMBER(D93),D93&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I93">
         <f>B93-$O$8</f>
         <v/>
       </c>
@@ -4290,22 +3174,10 @@
         <v>62.17</v>
       </c>
       <c r="E94">
-        <f>IFERROR(MEDIAN(D74:D114),D94)</f>
+        <f>IF(AND(ISNUMBER(D94),D94&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F94">
-        <f>IF(OR(NOT(ISNUMBER(D94)),ABS(D94-E94)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G94">
-        <f>IF(F94=1,NA(),D94)</f>
-        <v/>
-      </c>
-      <c r="H94">
-        <f>IF(AND(ISNUMBER(D94),D94&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I94">
         <f>B94-$O$8</f>
         <v/>
       </c>
@@ -4326,22 +3198,10 @@
         <v>62.17</v>
       </c>
       <c r="E95">
-        <f>IFERROR(MEDIAN(D75:D115),D95)</f>
+        <f>IF(AND(ISNUMBER(D95),D95&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F95">
-        <f>IF(OR(NOT(ISNUMBER(D95)),ABS(D95-E95)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G95">
-        <f>IF(F95=1,NA(),D95)</f>
-        <v/>
-      </c>
-      <c r="H95">
-        <f>IF(AND(ISNUMBER(D95),D95&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I95">
         <f>B95-$O$8</f>
         <v/>
       </c>
@@ -4362,22 +3222,10 @@
         <v>62.17</v>
       </c>
       <c r="E96">
-        <f>IFERROR(MEDIAN(D76:D116),D96)</f>
+        <f>IF(AND(ISNUMBER(D96),D96&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F96">
-        <f>IF(OR(NOT(ISNUMBER(D96)),ABS(D96-E96)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G96">
-        <f>IF(F96=1,NA(),D96)</f>
-        <v/>
-      </c>
-      <c r="H96">
-        <f>IF(AND(ISNUMBER(D96),D96&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I96">
         <f>B96-$O$8</f>
         <v/>
       </c>
@@ -4398,22 +3246,10 @@
         <v>62.17</v>
       </c>
       <c r="E97">
-        <f>IFERROR(MEDIAN(D77:D116),D97)</f>
+        <f>IF(AND(ISNUMBER(D97),D97&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F97">
-        <f>IF(OR(NOT(ISNUMBER(D97)),ABS(D97-E97)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G97">
-        <f>IF(F97=1,NA(),D97)</f>
-        <v/>
-      </c>
-      <c r="H97">
-        <f>IF(AND(ISNUMBER(D97),D97&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I97">
         <f>B97-$O$8</f>
         <v/>
       </c>
@@ -4434,22 +3270,10 @@
         <v>62.17</v>
       </c>
       <c r="E98">
-        <f>IFERROR(MEDIAN(D78:D116),D98)</f>
+        <f>IF(AND(ISNUMBER(D98),D98&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F98">
-        <f>IF(OR(NOT(ISNUMBER(D98)),ABS(D98-E98)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G98">
-        <f>IF(F98=1,NA(),D98)</f>
-        <v/>
-      </c>
-      <c r="H98">
-        <f>IF(AND(ISNUMBER(D98),D98&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I98">
         <f>B98-$O$8</f>
         <v/>
       </c>
@@ -4470,22 +3294,10 @@
         <v>62.17</v>
       </c>
       <c r="E99">
-        <f>IFERROR(MEDIAN(D79:D116),D99)</f>
+        <f>IF(AND(ISNUMBER(D99),D99&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F99">
-        <f>IF(OR(NOT(ISNUMBER(D99)),ABS(D99-E99)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G99">
-        <f>IF(F99=1,NA(),D99)</f>
-        <v/>
-      </c>
-      <c r="H99">
-        <f>IF(AND(ISNUMBER(D99),D99&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I99">
         <f>B99-$O$8</f>
         <v/>
       </c>
@@ -4506,22 +3318,10 @@
         <v>62.17</v>
       </c>
       <c r="E100">
-        <f>IFERROR(MEDIAN(D80:D116),D100)</f>
+        <f>IF(AND(ISNUMBER(D100),D100&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F100">
-        <f>IF(OR(NOT(ISNUMBER(D100)),ABS(D100-E100)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G100">
-        <f>IF(F100=1,NA(),D100)</f>
-        <v/>
-      </c>
-      <c r="H100">
-        <f>IF(AND(ISNUMBER(D100),D100&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I100">
         <f>B100-$O$8</f>
         <v/>
       </c>
@@ -4542,22 +3342,10 @@
         <v>62.17</v>
       </c>
       <c r="E101">
-        <f>IFERROR(MEDIAN(D81:D116),D101)</f>
+        <f>IF(AND(ISNUMBER(D101),D101&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F101">
-        <f>IF(OR(NOT(ISNUMBER(D101)),ABS(D101-E101)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G101">
-        <f>IF(F101=1,NA(),D101)</f>
-        <v/>
-      </c>
-      <c r="H101">
-        <f>IF(AND(ISNUMBER(D101),D101&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I101">
         <f>B101-$O$8</f>
         <v/>
       </c>
@@ -4578,22 +3366,10 @@
         <v>62.17</v>
       </c>
       <c r="E102">
-        <f>IFERROR(MEDIAN(D82:D116),D102)</f>
+        <f>IF(AND(ISNUMBER(D102),D102&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F102">
-        <f>IF(OR(NOT(ISNUMBER(D102)),ABS(D102-E102)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G102">
-        <f>IF(F102=1,NA(),D102)</f>
-        <v/>
-      </c>
-      <c r="H102">
-        <f>IF(AND(ISNUMBER(D102),D102&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I102">
         <f>B102-$O$8</f>
         <v/>
       </c>
@@ -4614,22 +3390,10 @@
         <v>62.17</v>
       </c>
       <c r="E103">
-        <f>IFERROR(MEDIAN(D83:D116),D103)</f>
+        <f>IF(AND(ISNUMBER(D103),D103&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F103">
-        <f>IF(OR(NOT(ISNUMBER(D103)),ABS(D103-E103)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G103">
-        <f>IF(F103=1,NA(),D103)</f>
-        <v/>
-      </c>
-      <c r="H103">
-        <f>IF(AND(ISNUMBER(D103),D103&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I103">
         <f>B103-$O$8</f>
         <v/>
       </c>
@@ -4650,22 +3414,10 @@
         <v>62.18</v>
       </c>
       <c r="E104">
-        <f>IFERROR(MEDIAN(D84:D116),D104)</f>
+        <f>IF(AND(ISNUMBER(D104),D104&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F104">
-        <f>IF(OR(NOT(ISNUMBER(D104)),ABS(D104-E104)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G104">
-        <f>IF(F104=1,NA(),D104)</f>
-        <v/>
-      </c>
-      <c r="H104">
-        <f>IF(AND(ISNUMBER(D104),D104&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I104">
         <f>B104-$O$8</f>
         <v/>
       </c>
@@ -4686,22 +3438,10 @@
         <v>62.18</v>
       </c>
       <c r="E105">
-        <f>IFERROR(MEDIAN(D85:D116),D105)</f>
+        <f>IF(AND(ISNUMBER(D105),D105&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F105">
-        <f>IF(OR(NOT(ISNUMBER(D105)),ABS(D105-E105)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G105">
-        <f>IF(F105=1,NA(),D105)</f>
-        <v/>
-      </c>
-      <c r="H105">
-        <f>IF(AND(ISNUMBER(D105),D105&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I105">
         <f>B105-$O$8</f>
         <v/>
       </c>
@@ -4722,22 +3462,10 @@
         <v>62.18</v>
       </c>
       <c r="E106">
-        <f>IFERROR(MEDIAN(D86:D116),D106)</f>
+        <f>IF(AND(ISNUMBER(D106),D106&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F106">
-        <f>IF(OR(NOT(ISNUMBER(D106)),ABS(D106-E106)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G106">
-        <f>IF(F106=1,NA(),D106)</f>
-        <v/>
-      </c>
-      <c r="H106">
-        <f>IF(AND(ISNUMBER(D106),D106&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I106">
         <f>B106-$O$8</f>
         <v/>
       </c>
@@ -4758,22 +3486,10 @@
         <v>62.18</v>
       </c>
       <c r="E107">
-        <f>IFERROR(MEDIAN(D87:D116),D107)</f>
+        <f>IF(AND(ISNUMBER(D107),D107&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F107">
-        <f>IF(OR(NOT(ISNUMBER(D107)),ABS(D107-E107)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G107">
-        <f>IF(F107=1,NA(),D107)</f>
-        <v/>
-      </c>
-      <c r="H107">
-        <f>IF(AND(ISNUMBER(D107),D107&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I107">
         <f>B107-$O$8</f>
         <v/>
       </c>
@@ -4794,22 +3510,10 @@
         <v>62.18</v>
       </c>
       <c r="E108">
-        <f>IFERROR(MEDIAN(D88:D116),D108)</f>
+        <f>IF(AND(ISNUMBER(D108),D108&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F108">
-        <f>IF(OR(NOT(ISNUMBER(D108)),ABS(D108-E108)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G108">
-        <f>IF(F108=1,NA(),D108)</f>
-        <v/>
-      </c>
-      <c r="H108">
-        <f>IF(AND(ISNUMBER(D108),D108&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I108">
         <f>B108-$O$8</f>
         <v/>
       </c>
@@ -4830,22 +3534,10 @@
         <v>62.18</v>
       </c>
       <c r="E109">
-        <f>IFERROR(MEDIAN(D89:D116),D109)</f>
+        <f>IF(AND(ISNUMBER(D109),D109&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F109">
-        <f>IF(OR(NOT(ISNUMBER(D109)),ABS(D109-E109)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G109">
-        <f>IF(F109=1,NA(),D109)</f>
-        <v/>
-      </c>
-      <c r="H109">
-        <f>IF(AND(ISNUMBER(D109),D109&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I109">
         <f>B109-$O$8</f>
         <v/>
       </c>
@@ -4866,22 +3558,10 @@
         <v>62.18</v>
       </c>
       <c r="E110">
-        <f>IFERROR(MEDIAN(D90:D116),D110)</f>
+        <f>IF(AND(ISNUMBER(D110),D110&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F110">
-        <f>IF(OR(NOT(ISNUMBER(D110)),ABS(D110-E110)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G110">
-        <f>IF(F110=1,NA(),D110)</f>
-        <v/>
-      </c>
-      <c r="H110">
-        <f>IF(AND(ISNUMBER(D110),D110&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I110">
         <f>B110-$O$8</f>
         <v/>
       </c>
@@ -4902,22 +3582,10 @@
         <v>62.19</v>
       </c>
       <c r="E111">
-        <f>IFERROR(MEDIAN(D91:D116),D111)</f>
+        <f>IF(AND(ISNUMBER(D111),D111&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F111">
-        <f>IF(OR(NOT(ISNUMBER(D111)),ABS(D111-E111)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G111">
-        <f>IF(F111=1,NA(),D111)</f>
-        <v/>
-      </c>
-      <c r="H111">
-        <f>IF(AND(ISNUMBER(D111),D111&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I111">
         <f>B111-$O$8</f>
         <v/>
       </c>
@@ -4938,22 +3606,10 @@
         <v>62.19</v>
       </c>
       <c r="E112">
-        <f>IFERROR(MEDIAN(D92:D116),D112)</f>
+        <f>IF(AND(ISNUMBER(D112),D112&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F112">
-        <f>IF(OR(NOT(ISNUMBER(D112)),ABS(D112-E112)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G112">
-        <f>IF(F112=1,NA(),D112)</f>
-        <v/>
-      </c>
-      <c r="H112">
-        <f>IF(AND(ISNUMBER(D112),D112&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I112">
         <f>B112-$O$8</f>
         <v/>
       </c>
@@ -4974,22 +3630,10 @@
         <v>62.19</v>
       </c>
       <c r="E113">
-        <f>IFERROR(MEDIAN(D93:D116),D113)</f>
+        <f>IF(AND(ISNUMBER(D113),D113&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F113">
-        <f>IF(OR(NOT(ISNUMBER(D113)),ABS(D113-E113)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G113">
-        <f>IF(F113=1,NA(),D113)</f>
-        <v/>
-      </c>
-      <c r="H113">
-        <f>IF(AND(ISNUMBER(D113),D113&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I113">
         <f>B113-$O$8</f>
         <v/>
       </c>
@@ -5010,22 +3654,10 @@
         <v>62.28</v>
       </c>
       <c r="E114">
-        <f>IFERROR(MEDIAN(D94:D116),D114)</f>
+        <f>IF(AND(ISNUMBER(D114),D114&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F114">
-        <f>IF(OR(NOT(ISNUMBER(D114)),ABS(D114-E114)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G114">
-        <f>IF(F114=1,NA(),D114)</f>
-        <v/>
-      </c>
-      <c r="H114">
-        <f>IF(AND(ISNUMBER(D114),D114&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I114">
         <f>B114-$O$8</f>
         <v/>
       </c>
@@ -5046,22 +3678,10 @@
         <v>62.2</v>
       </c>
       <c r="E115">
-        <f>IFERROR(MEDIAN(D95:D116),D115)</f>
+        <f>IF(AND(ISNUMBER(D115),D115&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F115">
-        <f>IF(OR(NOT(ISNUMBER(D115)),ABS(D115-E115)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G115">
-        <f>IF(F115=1,NA(),D115)</f>
-        <v/>
-      </c>
-      <c r="H115">
-        <f>IF(AND(ISNUMBER(D115),D115&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I115">
         <f>B115-$O$8</f>
         <v/>
       </c>
@@ -5082,22 +3702,10 @@
         <v>62.2</v>
       </c>
       <c r="E116">
-        <f>IFERROR(MEDIAN(D96:D116),D116)</f>
+        <f>IF(AND(ISNUMBER(D116),D116&gt;=$O$4),1,0)</f>
         <v/>
       </c>
       <c r="F116">
-        <f>IF(OR(NOT(ISNUMBER(D116)),ABS(D116-E116)&gt;$O$3),1,0)</f>
-        <v/>
-      </c>
-      <c r="G116">
-        <f>IF(F116=1,NA(),D116)</f>
-        <v/>
-      </c>
-      <c r="H116">
-        <f>IF(AND(ISNUMBER(D116),D116&gt;=$O$4),1,0)</f>
-        <v/>
-      </c>
-      <c r="I116">
         <f>B116-$O$8</f>
         <v/>
       </c>
@@ -5131,1151 +3739,1151 @@
     </row>
     <row r="2">
       <c r="A2">
-        <f>Sheet1!I2</f>
+        <f>Sheet1!F2</f>
         <v/>
       </c>
       <c r="B2">
-        <f>IF(ISNA(Sheet1!G2),NA(),Sheet1!$O$5-(Sheet1!G2/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D2)),NA(),Sheet1!$O$5-(Sheet1!D2/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <f>Sheet1!I3</f>
+        <f>Sheet1!F3</f>
         <v/>
       </c>
       <c r="B3">
-        <f>IF(ISNA(Sheet1!G3),NA(),Sheet1!$O$5-(Sheet1!G3/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D3)),NA(),Sheet1!$O$5-(Sheet1!D3/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <f>Sheet1!I4</f>
+        <f>Sheet1!F4</f>
         <v/>
       </c>
       <c r="B4">
-        <f>IF(ISNA(Sheet1!G4),NA(),Sheet1!$O$5-(Sheet1!G4/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D4)),NA(),Sheet1!$O$5-(Sheet1!D4/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <f>Sheet1!I5</f>
+        <f>Sheet1!F5</f>
         <v/>
       </c>
       <c r="B5">
-        <f>IF(ISNA(Sheet1!G5),NA(),Sheet1!$O$5-(Sheet1!G5/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D5)),NA(),Sheet1!$O$5-(Sheet1!D5/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <f>Sheet1!I6</f>
+        <f>Sheet1!F6</f>
         <v/>
       </c>
       <c r="B6">
-        <f>IF(ISNA(Sheet1!G6),NA(),Sheet1!$O$5-(Sheet1!G6/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D6)),NA(),Sheet1!$O$5-(Sheet1!D6/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <f>Sheet1!I7</f>
+        <f>Sheet1!F7</f>
         <v/>
       </c>
       <c r="B7">
-        <f>IF(ISNA(Sheet1!G7),NA(),Sheet1!$O$5-(Sheet1!G7/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D7)),NA(),Sheet1!$O$5-(Sheet1!D7/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <f>Sheet1!I8</f>
+        <f>Sheet1!F8</f>
         <v/>
       </c>
       <c r="B8">
-        <f>IF(ISNA(Sheet1!G8),NA(),Sheet1!$O$5-(Sheet1!G8/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D8)),NA(),Sheet1!$O$5-(Sheet1!D8/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <f>Sheet1!I9</f>
+        <f>Sheet1!F9</f>
         <v/>
       </c>
       <c r="B9">
-        <f>IF(ISNA(Sheet1!G9),NA(),Sheet1!$O$5-(Sheet1!G9/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D9)),NA(),Sheet1!$O$5-(Sheet1!D9/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <f>Sheet1!I10</f>
+        <f>Sheet1!F10</f>
         <v/>
       </c>
       <c r="B10">
-        <f>IF(ISNA(Sheet1!G10),NA(),Sheet1!$O$5-(Sheet1!G10/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D10)),NA(),Sheet1!$O$5-(Sheet1!D10/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <f>Sheet1!I11</f>
+        <f>Sheet1!F11</f>
         <v/>
       </c>
       <c r="B11">
-        <f>IF(ISNA(Sheet1!G11),NA(),Sheet1!$O$5-(Sheet1!G11/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D11)),NA(),Sheet1!$O$5-(Sheet1!D11/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <f>Sheet1!I12</f>
+        <f>Sheet1!F12</f>
         <v/>
       </c>
       <c r="B12">
-        <f>IF(ISNA(Sheet1!G12),NA(),Sheet1!$O$5-(Sheet1!G12/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D12)),NA(),Sheet1!$O$5-(Sheet1!D12/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <f>Sheet1!I13</f>
+        <f>Sheet1!F13</f>
         <v/>
       </c>
       <c r="B13">
-        <f>IF(ISNA(Sheet1!G13),NA(),Sheet1!$O$5-(Sheet1!G13/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D13)),NA(),Sheet1!$O$5-(Sheet1!D13/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <f>Sheet1!I14</f>
+        <f>Sheet1!F14</f>
         <v/>
       </c>
       <c r="B14">
-        <f>IF(ISNA(Sheet1!G14),NA(),Sheet1!$O$5-(Sheet1!G14/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D14)),NA(),Sheet1!$O$5-(Sheet1!D14/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <f>Sheet1!I15</f>
+        <f>Sheet1!F15</f>
         <v/>
       </c>
       <c r="B15">
-        <f>IF(ISNA(Sheet1!G15),NA(),Sheet1!$O$5-(Sheet1!G15/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D15)),NA(),Sheet1!$O$5-(Sheet1!D15/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <f>Sheet1!I16</f>
+        <f>Sheet1!F16</f>
         <v/>
       </c>
       <c r="B16">
-        <f>IF(ISNA(Sheet1!G16),NA(),Sheet1!$O$5-(Sheet1!G16/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D16)),NA(),Sheet1!$O$5-(Sheet1!D16/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <f>Sheet1!I17</f>
+        <f>Sheet1!F17</f>
         <v/>
       </c>
       <c r="B17">
-        <f>IF(ISNA(Sheet1!G17),NA(),Sheet1!$O$5-(Sheet1!G17/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D17)),NA(),Sheet1!$O$5-(Sheet1!D17/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <f>Sheet1!I18</f>
+        <f>Sheet1!F18</f>
         <v/>
       </c>
       <c r="B18">
-        <f>IF(ISNA(Sheet1!G18),NA(),Sheet1!$O$5-(Sheet1!G18/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D18)),NA(),Sheet1!$O$5-(Sheet1!D18/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <f>Sheet1!I19</f>
+        <f>Sheet1!F19</f>
         <v/>
       </c>
       <c r="B19">
-        <f>IF(ISNA(Sheet1!G19),NA(),Sheet1!$O$5-(Sheet1!G19/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D19)),NA(),Sheet1!$O$5-(Sheet1!D19/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <f>Sheet1!I20</f>
+        <f>Sheet1!F20</f>
         <v/>
       </c>
       <c r="B20">
-        <f>IF(ISNA(Sheet1!G20),NA(),Sheet1!$O$5-(Sheet1!G20/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D20)),NA(),Sheet1!$O$5-(Sheet1!D20/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <f>Sheet1!I21</f>
+        <f>Sheet1!F21</f>
         <v/>
       </c>
       <c r="B21">
-        <f>IF(ISNA(Sheet1!G21),NA(),Sheet1!$O$5-(Sheet1!G21/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D21)),NA(),Sheet1!$O$5-(Sheet1!D21/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <f>Sheet1!I22</f>
+        <f>Sheet1!F22</f>
         <v/>
       </c>
       <c r="B22">
-        <f>IF(ISNA(Sheet1!G22),NA(),Sheet1!$O$5-(Sheet1!G22/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D22)),NA(),Sheet1!$O$5-(Sheet1!D22/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <f>Sheet1!I23</f>
+        <f>Sheet1!F23</f>
         <v/>
       </c>
       <c r="B23">
-        <f>IF(ISNA(Sheet1!G23),NA(),Sheet1!$O$5-(Sheet1!G23/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D23)),NA(),Sheet1!$O$5-(Sheet1!D23/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <f>Sheet1!I24</f>
+        <f>Sheet1!F24</f>
         <v/>
       </c>
       <c r="B24">
-        <f>IF(ISNA(Sheet1!G24),NA(),Sheet1!$O$5-(Sheet1!G24/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D24)),NA(),Sheet1!$O$5-(Sheet1!D24/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <f>Sheet1!I25</f>
+        <f>Sheet1!F25</f>
         <v/>
       </c>
       <c r="B25">
-        <f>IF(ISNA(Sheet1!G25),NA(),Sheet1!$O$5-(Sheet1!G25/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D25)),NA(),Sheet1!$O$5-(Sheet1!D25/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <f>Sheet1!I26</f>
+        <f>Sheet1!F26</f>
         <v/>
       </c>
       <c r="B26">
-        <f>IF(ISNA(Sheet1!G26),NA(),Sheet1!$O$5-(Sheet1!G26/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D26)),NA(),Sheet1!$O$5-(Sheet1!D26/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <f>Sheet1!I27</f>
+        <f>Sheet1!F27</f>
         <v/>
       </c>
       <c r="B27">
-        <f>IF(ISNA(Sheet1!G27),NA(),Sheet1!$O$5-(Sheet1!G27/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D27)),NA(),Sheet1!$O$5-(Sheet1!D27/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <f>Sheet1!I28</f>
+        <f>Sheet1!F28</f>
         <v/>
       </c>
       <c r="B28">
-        <f>IF(ISNA(Sheet1!G28),NA(),Sheet1!$O$5-(Sheet1!G28/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D28)),NA(),Sheet1!$O$5-(Sheet1!D28/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <f>Sheet1!I29</f>
+        <f>Sheet1!F29</f>
         <v/>
       </c>
       <c r="B29">
-        <f>IF(ISNA(Sheet1!G29),NA(),Sheet1!$O$5-(Sheet1!G29/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D29)),NA(),Sheet1!$O$5-(Sheet1!D29/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <f>Sheet1!I30</f>
+        <f>Sheet1!F30</f>
         <v/>
       </c>
       <c r="B30">
-        <f>IF(ISNA(Sheet1!G30),NA(),Sheet1!$O$5-(Sheet1!G30/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D30)),NA(),Sheet1!$O$5-(Sheet1!D30/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <f>Sheet1!I31</f>
+        <f>Sheet1!F31</f>
         <v/>
       </c>
       <c r="B31">
-        <f>IF(ISNA(Sheet1!G31),NA(),Sheet1!$O$5-(Sheet1!G31/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D31)),NA(),Sheet1!$O$5-(Sheet1!D31/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <f>Sheet1!I32</f>
+        <f>Sheet1!F32</f>
         <v/>
       </c>
       <c r="B32">
-        <f>IF(ISNA(Sheet1!G32),NA(),Sheet1!$O$5-(Sheet1!G32/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D32)),NA(),Sheet1!$O$5-(Sheet1!D32/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <f>Sheet1!I33</f>
+        <f>Sheet1!F33</f>
         <v/>
       </c>
       <c r="B33">
-        <f>IF(ISNA(Sheet1!G33),NA(),Sheet1!$O$5-(Sheet1!G33/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D33)),NA(),Sheet1!$O$5-(Sheet1!D33/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <f>Sheet1!I34</f>
+        <f>Sheet1!F34</f>
         <v/>
       </c>
       <c r="B34">
-        <f>IF(ISNA(Sheet1!G34),NA(),Sheet1!$O$5-(Sheet1!G34/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D34)),NA(),Sheet1!$O$5-(Sheet1!D34/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <f>Sheet1!I35</f>
+        <f>Sheet1!F35</f>
         <v/>
       </c>
       <c r="B35">
-        <f>IF(ISNA(Sheet1!G35),NA(),Sheet1!$O$5-(Sheet1!G35/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D35)),NA(),Sheet1!$O$5-(Sheet1!D35/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <f>Sheet1!I36</f>
+        <f>Sheet1!F36</f>
         <v/>
       </c>
       <c r="B36">
-        <f>IF(ISNA(Sheet1!G36),NA(),Sheet1!$O$5-(Sheet1!G36/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D36)),NA(),Sheet1!$O$5-(Sheet1!D36/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <f>Sheet1!I37</f>
+        <f>Sheet1!F37</f>
         <v/>
       </c>
       <c r="B37">
-        <f>IF(ISNA(Sheet1!G37),NA(),Sheet1!$O$5-(Sheet1!G37/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D37)),NA(),Sheet1!$O$5-(Sheet1!D37/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <f>Sheet1!I38</f>
+        <f>Sheet1!F38</f>
         <v/>
       </c>
       <c r="B38">
-        <f>IF(ISNA(Sheet1!G38),NA(),Sheet1!$O$5-(Sheet1!G38/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D38)),NA(),Sheet1!$O$5-(Sheet1!D38/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <f>Sheet1!I39</f>
+        <f>Sheet1!F39</f>
         <v/>
       </c>
       <c r="B39">
-        <f>IF(ISNA(Sheet1!G39),NA(),Sheet1!$O$5-(Sheet1!G39/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D39)),NA(),Sheet1!$O$5-(Sheet1!D39/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <f>Sheet1!I40</f>
+        <f>Sheet1!F40</f>
         <v/>
       </c>
       <c r="B40">
-        <f>IF(ISNA(Sheet1!G40),NA(),Sheet1!$O$5-(Sheet1!G40/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D40)),NA(),Sheet1!$O$5-(Sheet1!D40/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <f>Sheet1!I41</f>
+        <f>Sheet1!F41</f>
         <v/>
       </c>
       <c r="B41">
-        <f>IF(ISNA(Sheet1!G41),NA(),Sheet1!$O$5-(Sheet1!G41/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D41)),NA(),Sheet1!$O$5-(Sheet1!D41/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <f>Sheet1!I42</f>
+        <f>Sheet1!F42</f>
         <v/>
       </c>
       <c r="B42">
-        <f>IF(ISNA(Sheet1!G42),NA(),Sheet1!$O$5-(Sheet1!G42/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D42)),NA(),Sheet1!$O$5-(Sheet1!D42/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <f>Sheet1!I43</f>
+        <f>Sheet1!F43</f>
         <v/>
       </c>
       <c r="B43">
-        <f>IF(ISNA(Sheet1!G43),NA(),Sheet1!$O$5-(Sheet1!G43/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D43)),NA(),Sheet1!$O$5-(Sheet1!D43/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <f>Sheet1!I44</f>
+        <f>Sheet1!F44</f>
         <v/>
       </c>
       <c r="B44">
-        <f>IF(ISNA(Sheet1!G44),NA(),Sheet1!$O$5-(Sheet1!G44/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D44)),NA(),Sheet1!$O$5-(Sheet1!D44/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <f>Sheet1!I45</f>
+        <f>Sheet1!F45</f>
         <v/>
       </c>
       <c r="B45">
-        <f>IF(ISNA(Sheet1!G45),NA(),Sheet1!$O$5-(Sheet1!G45/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D45)),NA(),Sheet1!$O$5-(Sheet1!D45/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <f>Sheet1!I46</f>
+        <f>Sheet1!F46</f>
         <v/>
       </c>
       <c r="B46">
-        <f>IF(ISNA(Sheet1!G46),NA(),Sheet1!$O$5-(Sheet1!G46/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D46)),NA(),Sheet1!$O$5-(Sheet1!D46/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <f>Sheet1!I47</f>
+        <f>Sheet1!F47</f>
         <v/>
       </c>
       <c r="B47">
-        <f>IF(ISNA(Sheet1!G47),NA(),Sheet1!$O$5-(Sheet1!G47/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D47)),NA(),Sheet1!$O$5-(Sheet1!D47/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <f>Sheet1!I48</f>
+        <f>Sheet1!F48</f>
         <v/>
       </c>
       <c r="B48">
-        <f>IF(ISNA(Sheet1!G48),NA(),Sheet1!$O$5-(Sheet1!G48/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D48)),NA(),Sheet1!$O$5-(Sheet1!D48/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <f>Sheet1!I49</f>
+        <f>Sheet1!F49</f>
         <v/>
       </c>
       <c r="B49">
-        <f>IF(ISNA(Sheet1!G49),NA(),Sheet1!$O$5-(Sheet1!G49/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D49)),NA(),Sheet1!$O$5-(Sheet1!D49/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <f>Sheet1!I50</f>
+        <f>Sheet1!F50</f>
         <v/>
       </c>
       <c r="B50">
-        <f>IF(ISNA(Sheet1!G50),NA(),Sheet1!$O$5-(Sheet1!G50/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D50)),NA(),Sheet1!$O$5-(Sheet1!D50/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <f>Sheet1!I51</f>
+        <f>Sheet1!F51</f>
         <v/>
       </c>
       <c r="B51">
-        <f>IF(ISNA(Sheet1!G51),NA(),Sheet1!$O$5-(Sheet1!G51/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D51)),NA(),Sheet1!$O$5-(Sheet1!D51/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52">
-        <f>Sheet1!I52</f>
+        <f>Sheet1!F52</f>
         <v/>
       </c>
       <c r="B52">
-        <f>IF(ISNA(Sheet1!G52),NA(),Sheet1!$O$5-(Sheet1!G52/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D52)),NA(),Sheet1!$O$5-(Sheet1!D52/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53">
-        <f>Sheet1!I53</f>
+        <f>Sheet1!F53</f>
         <v/>
       </c>
       <c r="B53">
-        <f>IF(ISNA(Sheet1!G53),NA(),Sheet1!$O$5-(Sheet1!G53/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D53)),NA(),Sheet1!$O$5-(Sheet1!D53/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54">
-        <f>Sheet1!I54</f>
+        <f>Sheet1!F54</f>
         <v/>
       </c>
       <c r="B54">
-        <f>IF(ISNA(Sheet1!G54),NA(),Sheet1!$O$5-(Sheet1!G54/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D54)),NA(),Sheet1!$O$5-(Sheet1!D54/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <f>Sheet1!I55</f>
+        <f>Sheet1!F55</f>
         <v/>
       </c>
       <c r="B55">
-        <f>IF(ISNA(Sheet1!G55),NA(),Sheet1!$O$5-(Sheet1!G55/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D55)),NA(),Sheet1!$O$5-(Sheet1!D55/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <f>Sheet1!I56</f>
+        <f>Sheet1!F56</f>
         <v/>
       </c>
       <c r="B56">
-        <f>IF(ISNA(Sheet1!G56),NA(),Sheet1!$O$5-(Sheet1!G56/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D56)),NA(),Sheet1!$O$5-(Sheet1!D56/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57">
-        <f>Sheet1!I57</f>
+        <f>Sheet1!F57</f>
         <v/>
       </c>
       <c r="B57">
-        <f>IF(ISNA(Sheet1!G57),NA(),Sheet1!$O$5-(Sheet1!G57/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D57)),NA(),Sheet1!$O$5-(Sheet1!D57/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <f>Sheet1!I58</f>
+        <f>Sheet1!F58</f>
         <v/>
       </c>
       <c r="B58">
-        <f>IF(ISNA(Sheet1!G58),NA(),Sheet1!$O$5-(Sheet1!G58/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D58)),NA(),Sheet1!$O$5-(Sheet1!D58/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59">
-        <f>Sheet1!I59</f>
+        <f>Sheet1!F59</f>
         <v/>
       </c>
       <c r="B59">
-        <f>IF(ISNA(Sheet1!G59),NA(),Sheet1!$O$5-(Sheet1!G59/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D59)),NA(),Sheet1!$O$5-(Sheet1!D59/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60">
-        <f>Sheet1!I60</f>
+        <f>Sheet1!F60</f>
         <v/>
       </c>
       <c r="B60">
-        <f>IF(ISNA(Sheet1!G60),NA(),Sheet1!$O$5-(Sheet1!G60/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D60)),NA(),Sheet1!$O$5-(Sheet1!D60/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61">
-        <f>Sheet1!I61</f>
+        <f>Sheet1!F61</f>
         <v/>
       </c>
       <c r="B61">
-        <f>IF(ISNA(Sheet1!G61),NA(),Sheet1!$O$5-(Sheet1!G61/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D61)),NA(),Sheet1!$O$5-(Sheet1!D61/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62">
-        <f>Sheet1!I62</f>
+        <f>Sheet1!F62</f>
         <v/>
       </c>
       <c r="B62">
-        <f>IF(ISNA(Sheet1!G62),NA(),Sheet1!$O$5-(Sheet1!G62/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D62)),NA(),Sheet1!$O$5-(Sheet1!D62/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <f>Sheet1!I63</f>
+        <f>Sheet1!F63</f>
         <v/>
       </c>
       <c r="B63">
-        <f>IF(ISNA(Sheet1!G63),NA(),Sheet1!$O$5-(Sheet1!G63/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D63)),NA(),Sheet1!$O$5-(Sheet1!D63/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <f>Sheet1!I64</f>
+        <f>Sheet1!F64</f>
         <v/>
       </c>
       <c r="B64">
-        <f>IF(ISNA(Sheet1!G64),NA(),Sheet1!$O$5-(Sheet1!G64/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D64)),NA(),Sheet1!$O$5-(Sheet1!D64/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65">
-        <f>Sheet1!I65</f>
+        <f>Sheet1!F65</f>
         <v/>
       </c>
       <c r="B65">
-        <f>IF(ISNA(Sheet1!G65),NA(),Sheet1!$O$5-(Sheet1!G65/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D65)),NA(),Sheet1!$O$5-(Sheet1!D65/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66">
-        <f>Sheet1!I66</f>
+        <f>Sheet1!F66</f>
         <v/>
       </c>
       <c r="B66">
-        <f>IF(ISNA(Sheet1!G66),NA(),Sheet1!$O$5-(Sheet1!G66/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D66)),NA(),Sheet1!$O$5-(Sheet1!D66/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67">
-        <f>Sheet1!I67</f>
+        <f>Sheet1!F67</f>
         <v/>
       </c>
       <c r="B67">
-        <f>IF(ISNA(Sheet1!G67),NA(),Sheet1!$O$5-(Sheet1!G67/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D67)),NA(),Sheet1!$O$5-(Sheet1!D67/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68">
-        <f>Sheet1!I68</f>
+        <f>Sheet1!F68</f>
         <v/>
       </c>
       <c r="B68">
-        <f>IF(ISNA(Sheet1!G68),NA(),Sheet1!$O$5-(Sheet1!G68/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D68)),NA(),Sheet1!$O$5-(Sheet1!D68/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69">
-        <f>Sheet1!I69</f>
+        <f>Sheet1!F69</f>
         <v/>
       </c>
       <c r="B69">
-        <f>IF(ISNA(Sheet1!G69),NA(),Sheet1!$O$5-(Sheet1!G69/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D69)),NA(),Sheet1!$O$5-(Sheet1!D69/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70">
-        <f>Sheet1!I70</f>
+        <f>Sheet1!F70</f>
         <v/>
       </c>
       <c r="B70">
-        <f>IF(ISNA(Sheet1!G70),NA(),Sheet1!$O$5-(Sheet1!G70/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D70)),NA(),Sheet1!$O$5-(Sheet1!D70/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71">
-        <f>Sheet1!I71</f>
+        <f>Sheet1!F71</f>
         <v/>
       </c>
       <c r="B71">
-        <f>IF(ISNA(Sheet1!G71),NA(),Sheet1!$O$5-(Sheet1!G71/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D71)),NA(),Sheet1!$O$5-(Sheet1!D71/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72">
-        <f>Sheet1!I72</f>
+        <f>Sheet1!F72</f>
         <v/>
       </c>
       <c r="B72">
-        <f>IF(ISNA(Sheet1!G72),NA(),Sheet1!$O$5-(Sheet1!G72/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D72)),NA(),Sheet1!$O$5-(Sheet1!D72/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73">
-        <f>Sheet1!I73</f>
+        <f>Sheet1!F73</f>
         <v/>
       </c>
       <c r="B73">
-        <f>IF(ISNA(Sheet1!G73),NA(),Sheet1!$O$5-(Sheet1!G73/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D73)),NA(),Sheet1!$O$5-(Sheet1!D73/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74">
-        <f>Sheet1!I74</f>
+        <f>Sheet1!F74</f>
         <v/>
       </c>
       <c r="B74">
-        <f>IF(ISNA(Sheet1!G74),NA(),Sheet1!$O$5-(Sheet1!G74/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D74)),NA(),Sheet1!$O$5-(Sheet1!D74/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75">
-        <f>Sheet1!I75</f>
+        <f>Sheet1!F75</f>
         <v/>
       </c>
       <c r="B75">
-        <f>IF(ISNA(Sheet1!G75),NA(),Sheet1!$O$5-(Sheet1!G75/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D75)),NA(),Sheet1!$O$5-(Sheet1!D75/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76">
-        <f>Sheet1!I76</f>
+        <f>Sheet1!F76</f>
         <v/>
       </c>
       <c r="B76">
-        <f>IF(ISNA(Sheet1!G76),NA(),Sheet1!$O$5-(Sheet1!G76/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D76)),NA(),Sheet1!$O$5-(Sheet1!D76/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77">
-        <f>Sheet1!I77</f>
+        <f>Sheet1!F77</f>
         <v/>
       </c>
       <c r="B77">
-        <f>IF(ISNA(Sheet1!G77),NA(),Sheet1!$O$5-(Sheet1!G77/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D77)),NA(),Sheet1!$O$5-(Sheet1!D77/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78">
-        <f>Sheet1!I78</f>
+        <f>Sheet1!F78</f>
         <v/>
       </c>
       <c r="B78">
-        <f>IF(ISNA(Sheet1!G78),NA(),Sheet1!$O$5-(Sheet1!G78/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D78)),NA(),Sheet1!$O$5-(Sheet1!D78/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79">
-        <f>Sheet1!I79</f>
+        <f>Sheet1!F79</f>
         <v/>
       </c>
       <c r="B79">
-        <f>IF(ISNA(Sheet1!G79),NA(),Sheet1!$O$5-(Sheet1!G79/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D79)),NA(),Sheet1!$O$5-(Sheet1!D79/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80">
-        <f>Sheet1!I80</f>
+        <f>Sheet1!F80</f>
         <v/>
       </c>
       <c r="B80">
-        <f>IF(ISNA(Sheet1!G80),NA(),Sheet1!$O$5-(Sheet1!G80/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D80)),NA(),Sheet1!$O$5-(Sheet1!D80/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81">
-        <f>Sheet1!I81</f>
+        <f>Sheet1!F81</f>
         <v/>
       </c>
       <c r="B81">
-        <f>IF(ISNA(Sheet1!G81),NA(),Sheet1!$O$5-(Sheet1!G81/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D81)),NA(),Sheet1!$O$5-(Sheet1!D81/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82">
-        <f>Sheet1!I82</f>
+        <f>Sheet1!F82</f>
         <v/>
       </c>
       <c r="B82">
-        <f>IF(ISNA(Sheet1!G82),NA(),Sheet1!$O$5-(Sheet1!G82/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D82)),NA(),Sheet1!$O$5-(Sheet1!D82/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83">
-        <f>Sheet1!I83</f>
+        <f>Sheet1!F83</f>
         <v/>
       </c>
       <c r="B83">
-        <f>IF(ISNA(Sheet1!G83),NA(),Sheet1!$O$5-(Sheet1!G83/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D83)),NA(),Sheet1!$O$5-(Sheet1!D83/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84">
-        <f>Sheet1!I84</f>
+        <f>Sheet1!F84</f>
         <v/>
       </c>
       <c r="B84">
-        <f>IF(ISNA(Sheet1!G84),NA(),Sheet1!$O$5-(Sheet1!G84/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D84)),NA(),Sheet1!$O$5-(Sheet1!D84/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85">
-        <f>Sheet1!I85</f>
+        <f>Sheet1!F85</f>
         <v/>
       </c>
       <c r="B85">
-        <f>IF(ISNA(Sheet1!G85),NA(),Sheet1!$O$5-(Sheet1!G85/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D85)),NA(),Sheet1!$O$5-(Sheet1!D85/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86">
-        <f>Sheet1!I86</f>
+        <f>Sheet1!F86</f>
         <v/>
       </c>
       <c r="B86">
-        <f>IF(ISNA(Sheet1!G86),NA(),Sheet1!$O$5-(Sheet1!G86/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D86)),NA(),Sheet1!$O$5-(Sheet1!D86/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87">
-        <f>Sheet1!I87</f>
+        <f>Sheet1!F87</f>
         <v/>
       </c>
       <c r="B87">
-        <f>IF(ISNA(Sheet1!G87),NA(),Sheet1!$O$5-(Sheet1!G87/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D87)),NA(),Sheet1!$O$5-(Sheet1!D87/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88">
-        <f>Sheet1!I88</f>
+        <f>Sheet1!F88</f>
         <v/>
       </c>
       <c r="B88">
-        <f>IF(ISNA(Sheet1!G88),NA(),Sheet1!$O$5-(Sheet1!G88/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D88)),NA(),Sheet1!$O$5-(Sheet1!D88/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89">
-        <f>Sheet1!I89</f>
+        <f>Sheet1!F89</f>
         <v/>
       </c>
       <c r="B89">
-        <f>IF(ISNA(Sheet1!G89),NA(),Sheet1!$O$5-(Sheet1!G89/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D89)),NA(),Sheet1!$O$5-(Sheet1!D89/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="90">
       <c r="A90">
-        <f>Sheet1!I90</f>
+        <f>Sheet1!F90</f>
         <v/>
       </c>
       <c r="B90">
-        <f>IF(ISNA(Sheet1!G90),NA(),Sheet1!$O$5-(Sheet1!G90/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D90)),NA(),Sheet1!$O$5-(Sheet1!D90/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="91">
       <c r="A91">
-        <f>Sheet1!I91</f>
+        <f>Sheet1!F91</f>
         <v/>
       </c>
       <c r="B91">
-        <f>IF(ISNA(Sheet1!G91),NA(),Sheet1!$O$5-(Sheet1!G91/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D91)),NA(),Sheet1!$O$5-(Sheet1!D91/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92">
-        <f>Sheet1!I92</f>
+        <f>Sheet1!F92</f>
         <v/>
       </c>
       <c r="B92">
-        <f>IF(ISNA(Sheet1!G92),NA(),Sheet1!$O$5-(Sheet1!G92/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D92)),NA(),Sheet1!$O$5-(Sheet1!D92/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93">
-        <f>Sheet1!I93</f>
+        <f>Sheet1!F93</f>
         <v/>
       </c>
       <c r="B93">
-        <f>IF(ISNA(Sheet1!G93),NA(),Sheet1!$O$5-(Sheet1!G93/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D93)),NA(),Sheet1!$O$5-(Sheet1!D93/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94">
-        <f>Sheet1!I94</f>
+        <f>Sheet1!F94</f>
         <v/>
       </c>
       <c r="B94">
-        <f>IF(ISNA(Sheet1!G94),NA(),Sheet1!$O$5-(Sheet1!G94/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D94)),NA(),Sheet1!$O$5-(Sheet1!D94/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95">
-        <f>Sheet1!I95</f>
+        <f>Sheet1!F95</f>
         <v/>
       </c>
       <c r="B95">
-        <f>IF(ISNA(Sheet1!G95),NA(),Sheet1!$O$5-(Sheet1!G95/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D95)),NA(),Sheet1!$O$5-(Sheet1!D95/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="96">
       <c r="A96">
-        <f>Sheet1!I96</f>
+        <f>Sheet1!F96</f>
         <v/>
       </c>
       <c r="B96">
-        <f>IF(ISNA(Sheet1!G96),NA(),Sheet1!$O$5-(Sheet1!G96/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D96)),NA(),Sheet1!$O$5-(Sheet1!D96/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97">
-        <f>Sheet1!I97</f>
+        <f>Sheet1!F97</f>
         <v/>
       </c>
       <c r="B97">
-        <f>IF(ISNA(Sheet1!G97),NA(),Sheet1!$O$5-(Sheet1!G97/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D97)),NA(),Sheet1!$O$5-(Sheet1!D97/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98">
-        <f>Sheet1!I98</f>
+        <f>Sheet1!F98</f>
         <v/>
       </c>
       <c r="B98">
-        <f>IF(ISNA(Sheet1!G98),NA(),Sheet1!$O$5-(Sheet1!G98/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D98)),NA(),Sheet1!$O$5-(Sheet1!D98/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="99">
       <c r="A99">
-        <f>Sheet1!I99</f>
+        <f>Sheet1!F99</f>
         <v/>
       </c>
       <c r="B99">
-        <f>IF(ISNA(Sheet1!G99),NA(),Sheet1!$O$5-(Sheet1!G99/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D99)),NA(),Sheet1!$O$5-(Sheet1!D99/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100">
-        <f>Sheet1!I100</f>
+        <f>Sheet1!F100</f>
         <v/>
       </c>
       <c r="B100">
-        <f>IF(ISNA(Sheet1!G100),NA(),Sheet1!$O$5-(Sheet1!G100/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D100)),NA(),Sheet1!$O$5-(Sheet1!D100/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101">
-        <f>Sheet1!I101</f>
+        <f>Sheet1!F101</f>
         <v/>
       </c>
       <c r="B101">
-        <f>IF(ISNA(Sheet1!G101),NA(),Sheet1!$O$5-(Sheet1!G101/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D101)),NA(),Sheet1!$O$5-(Sheet1!D101/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102">
-        <f>Sheet1!I102</f>
+        <f>Sheet1!F102</f>
         <v/>
       </c>
       <c r="B102">
-        <f>IF(ISNA(Sheet1!G102),NA(),Sheet1!$O$5-(Sheet1!G102/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D102)),NA(),Sheet1!$O$5-(Sheet1!D102/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="103">
       <c r="A103">
-        <f>Sheet1!I103</f>
+        <f>Sheet1!F103</f>
         <v/>
       </c>
       <c r="B103">
-        <f>IF(ISNA(Sheet1!G103),NA(),Sheet1!$O$5-(Sheet1!G103/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D103)),NA(),Sheet1!$O$5-(Sheet1!D103/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="104">
       <c r="A104">
-        <f>Sheet1!I104</f>
+        <f>Sheet1!F104</f>
         <v/>
       </c>
       <c r="B104">
-        <f>IF(ISNA(Sheet1!G104),NA(),Sheet1!$O$5-(Sheet1!G104/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D104)),NA(),Sheet1!$O$5-(Sheet1!D104/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105">
-        <f>Sheet1!I105</f>
+        <f>Sheet1!F105</f>
         <v/>
       </c>
       <c r="B105">
-        <f>IF(ISNA(Sheet1!G105),NA(),Sheet1!$O$5-(Sheet1!G105/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D105)),NA(),Sheet1!$O$5-(Sheet1!D105/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106">
-        <f>Sheet1!I106</f>
+        <f>Sheet1!F106</f>
         <v/>
       </c>
       <c r="B106">
-        <f>IF(ISNA(Sheet1!G106),NA(),Sheet1!$O$5-(Sheet1!G106/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D106)),NA(),Sheet1!$O$5-(Sheet1!D106/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107">
-        <f>Sheet1!I107</f>
+        <f>Sheet1!F107</f>
         <v/>
       </c>
       <c r="B107">
-        <f>IF(ISNA(Sheet1!G107),NA(),Sheet1!$O$5-(Sheet1!G107/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D107)),NA(),Sheet1!$O$5-(Sheet1!D107/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="108">
       <c r="A108">
-        <f>Sheet1!I108</f>
+        <f>Sheet1!F108</f>
         <v/>
       </c>
       <c r="B108">
-        <f>IF(ISNA(Sheet1!G108),NA(),Sheet1!$O$5-(Sheet1!G108/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D108)),NA(),Sheet1!$O$5-(Sheet1!D108/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="109">
       <c r="A109">
-        <f>Sheet1!I109</f>
+        <f>Sheet1!F109</f>
         <v/>
       </c>
       <c r="B109">
-        <f>IF(ISNA(Sheet1!G109),NA(),Sheet1!$O$5-(Sheet1!G109/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D109)),NA(),Sheet1!$O$5-(Sheet1!D109/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110">
-        <f>Sheet1!I110</f>
+        <f>Sheet1!F110</f>
         <v/>
       </c>
       <c r="B110">
-        <f>IF(ISNA(Sheet1!G110),NA(),Sheet1!$O$5-(Sheet1!G110/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D110)),NA(),Sheet1!$O$5-(Sheet1!D110/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="111">
       <c r="A111">
-        <f>Sheet1!I111</f>
+        <f>Sheet1!F111</f>
         <v/>
       </c>
       <c r="B111">
-        <f>IF(ISNA(Sheet1!G111),NA(),Sheet1!$O$5-(Sheet1!G111/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D111)),NA(),Sheet1!$O$5-(Sheet1!D111/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="112">
       <c r="A112">
-        <f>Sheet1!I112</f>
+        <f>Sheet1!F112</f>
         <v/>
       </c>
       <c r="B112">
-        <f>IF(ISNA(Sheet1!G112),NA(),Sheet1!$O$5-(Sheet1!G112/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D112)),NA(),Sheet1!$O$5-(Sheet1!D112/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="113">
       <c r="A113">
-        <f>Sheet1!I113</f>
+        <f>Sheet1!F113</f>
         <v/>
       </c>
       <c r="B113">
-        <f>IF(ISNA(Sheet1!G113),NA(),Sheet1!$O$5-(Sheet1!G113/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D113)),NA(),Sheet1!$O$5-(Sheet1!D113/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="114">
       <c r="A114">
-        <f>Sheet1!I114</f>
+        <f>Sheet1!F114</f>
         <v/>
       </c>
       <c r="B114">
-        <f>IF(ISNA(Sheet1!G114),NA(),Sheet1!$O$5-(Sheet1!G114/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D114)),NA(),Sheet1!$O$5-(Sheet1!D114/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="115">
       <c r="A115">
-        <f>Sheet1!I115</f>
+        <f>Sheet1!F115</f>
         <v/>
       </c>
       <c r="B115">
-        <f>IF(ISNA(Sheet1!G115),NA(),Sheet1!$O$5-(Sheet1!G115/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D115)),NA(),Sheet1!$O$5-(Sheet1!D115/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
     <row r="116">
       <c r="A116">
-        <f>Sheet1!I116</f>
+        <f>Sheet1!F116</f>
         <v/>
       </c>
       <c r="B116">
-        <f>IF(ISNA(Sheet1!G116),NA(),Sheet1!$O$5-(Sheet1!G116/Sheet1!$O$6))</f>
+        <f>IF(NOT(ISNUMBER(Sheet1!D116)),NA(),Sheet1!$O$5-(Sheet1!D116/Sheet1!$O$6))</f>
         <v/>
       </c>
     </row>
